--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,410 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7280300</v>
+        <v>7519500</v>
       </c>
       <c r="E8" s="3">
-        <v>7026200</v>
+        <v>7390000</v>
       </c>
       <c r="F8" s="3">
-        <v>6929100</v>
+        <v>7132000</v>
       </c>
       <c r="G8" s="3">
-        <v>7524100</v>
+        <v>7033500</v>
       </c>
       <c r="H8" s="3">
-        <v>7241500</v>
+        <v>7637400</v>
       </c>
       <c r="I8" s="3">
-        <v>6609000</v>
+        <v>7350500</v>
       </c>
       <c r="J8" s="3">
+        <v>6708500</v>
+      </c>
+      <c r="K8" s="3">
         <v>5916300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5800300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5820400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5756600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5156000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5065500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5774300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4752500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6217800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8048800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8122100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8168200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8151300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9212700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8349700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8322400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4507000</v>
+        <v>4652000</v>
       </c>
       <c r="E9" s="3">
-        <v>4311600</v>
+        <v>4574900</v>
       </c>
       <c r="F9" s="3">
-        <v>4269000</v>
+        <v>4376500</v>
       </c>
       <c r="G9" s="3">
-        <v>4605000</v>
+        <v>4333300</v>
       </c>
       <c r="H9" s="3">
-        <v>4438000</v>
+        <v>4674300</v>
       </c>
       <c r="I9" s="3">
-        <v>4053800</v>
+        <v>4504800</v>
       </c>
       <c r="J9" s="3">
+        <v>4114800</v>
+      </c>
+      <c r="K9" s="3">
         <v>3615000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3318300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3396300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3395600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3069100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2818700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3709400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3230500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3894700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5024300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4951200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5149100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5094700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5770100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5275700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5136800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2773300</v>
+        <v>2867500</v>
       </c>
       <c r="E10" s="3">
-        <v>2714600</v>
+        <v>2815100</v>
       </c>
       <c r="F10" s="3">
-        <v>2660100</v>
+        <v>2755500</v>
       </c>
       <c r="G10" s="3">
-        <v>2919100</v>
+        <v>2700200</v>
       </c>
       <c r="H10" s="3">
-        <v>2803500</v>
+        <v>2963100</v>
       </c>
       <c r="I10" s="3">
-        <v>2555200</v>
+        <v>2845700</v>
       </c>
       <c r="J10" s="3">
+        <v>2593700</v>
+      </c>
+      <c r="K10" s="3">
         <v>2301300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2482000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2424100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2361000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2086900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2246800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2064900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1522000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2323200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3024500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3170900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3019100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3056600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3442500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3074000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3185600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,100 +1105,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>200400</v>
+        <v>219500</v>
       </c>
       <c r="E12" s="3">
-        <v>196400</v>
+        <v>203400</v>
       </c>
       <c r="F12" s="3">
-        <v>197100</v>
+        <v>199300</v>
       </c>
       <c r="G12" s="3">
-        <v>202200</v>
+        <v>200000</v>
       </c>
       <c r="H12" s="3">
+        <v>205300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>189100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>184100</v>
+      </c>
+      <c r="K12" s="3">
+        <v>175100</v>
+      </c>
+      <c r="L12" s="3">
+        <v>157300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>163000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>168300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>159200</v>
+      </c>
+      <c r="P12" s="3">
+        <v>126200</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>173000</v>
+      </c>
+      <c r="R12" s="3">
         <v>186300</v>
       </c>
-      <c r="I12" s="3">
-        <v>181300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>175100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>157300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>163000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>168300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>159200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>126200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>173000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>186300</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>229200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>252500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>235800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>252200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>243000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>269400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>238200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>228100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>220800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>241900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>216700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>232200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>207300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>215600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1276,192 +1293,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-6000</v>
+        <v>104100</v>
       </c>
       <c r="E14" s="3">
-        <v>-29700</v>
+        <v>-6100</v>
       </c>
       <c r="F14" s="3">
-        <v>8800</v>
+        <v>-30100</v>
       </c>
       <c r="G14" s="3">
-        <v>43400</v>
+        <v>8900</v>
       </c>
       <c r="H14" s="3">
-        <v>13200</v>
+        <v>179000</v>
       </c>
       <c r="I14" s="3">
-        <v>5500</v>
+        <v>13400</v>
       </c>
       <c r="J14" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K14" s="3">
         <v>85700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>49900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>26900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>39800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>487000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>682000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>383400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>47500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>190200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>41600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-103500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-280400</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3">
         <v>99800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>58400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>39200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>193400</v>
+        <v>201500</v>
       </c>
       <c r="E15" s="3">
-        <v>183300</v>
+        <v>196300</v>
       </c>
       <c r="F15" s="3">
-        <v>174000</v>
+        <v>186000</v>
       </c>
       <c r="G15" s="3">
-        <v>175700</v>
+        <v>176600</v>
       </c>
       <c r="H15" s="3">
-        <v>180100</v>
+        <v>178400</v>
       </c>
       <c r="I15" s="3">
-        <v>163300</v>
+        <v>182800</v>
       </c>
       <c r="J15" s="3">
+        <v>165700</v>
+      </c>
+      <c r="K15" s="3">
         <v>154300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>158200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>161700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>161900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>156500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>159000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>171800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>179100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>193000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>312700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>310900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>200000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>203500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>85000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>84700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>79500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>78600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>80500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>76300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>73000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>72800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>71300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1491,192 +1517,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6449200</v>
+        <v>6805200</v>
       </c>
       <c r="E17" s="3">
-        <v>6208700</v>
+        <v>6546300</v>
       </c>
       <c r="F17" s="3">
-        <v>6082500</v>
+        <v>6302200</v>
       </c>
       <c r="G17" s="3">
-        <v>6633900</v>
+        <v>6174100</v>
       </c>
       <c r="H17" s="3">
-        <v>6356800</v>
+        <v>6733800</v>
       </c>
       <c r="I17" s="3">
-        <v>6035600</v>
+        <v>6452500</v>
       </c>
       <c r="J17" s="3">
+        <v>6126500</v>
+      </c>
+      <c r="K17" s="3">
         <v>5334400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5037600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5098300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5071600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4565000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4771800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5669200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5164900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5873400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7408900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6921500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7573700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7348300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8154600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7219900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7417600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>831200</v>
+        <v>714300</v>
       </c>
       <c r="E18" s="3">
-        <v>817500</v>
+        <v>843700</v>
       </c>
       <c r="F18" s="3">
-        <v>846600</v>
+        <v>829800</v>
       </c>
       <c r="G18" s="3">
-        <v>890200</v>
+        <v>859400</v>
       </c>
       <c r="H18" s="3">
-        <v>884700</v>
+        <v>903600</v>
       </c>
       <c r="I18" s="3">
-        <v>573400</v>
+        <v>898000</v>
       </c>
       <c r="J18" s="3">
+        <v>582100</v>
+      </c>
+      <c r="K18" s="3">
         <v>581900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>762800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>722100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>684900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>591000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>293700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>105100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-412500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>344400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>640000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1200600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>594400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>803000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1058100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1129800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>904800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>908100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>978800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>874100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>888200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>855800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1709,468 +1742,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-48200</v>
+        <v>-86800</v>
       </c>
       <c r="E20" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2100</v>
       </c>
-      <c r="F20" s="3">
-        <v>25700</v>
-      </c>
       <c r="G20" s="3">
-        <v>-72100</v>
+        <v>26000</v>
       </c>
       <c r="H20" s="3">
-        <v>-34400</v>
+        <v>-73200</v>
       </c>
       <c r="I20" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>25800</v>
+      </c>
+      <c r="K20" s="3">
+        <v>56400</v>
+      </c>
+      <c r="L20" s="3">
+        <v>32100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>13800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>17500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>23500</v>
+      </c>
+      <c r="P20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>9400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="T20" s="3">
+        <v>76900</v>
+      </c>
+      <c r="U20" s="3">
+        <v>12700</v>
+      </c>
+      <c r="V20" s="3">
+        <v>18700</v>
+      </c>
+      <c r="W20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="X20" s="3">
+        <v>109100</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>19900</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>231400</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>77600</v>
+      </c>
+      <c r="AD20" s="3">
         <v>25400</v>
       </c>
-      <c r="J20" s="3">
-        <v>56400</v>
-      </c>
-      <c r="K20" s="3">
-        <v>32100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>13800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>17500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>23500</v>
-      </c>
-      <c r="O20" s="3">
-        <v>3700</v>
-      </c>
-      <c r="P20" s="3">
-        <v>9400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-23300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>76900</v>
-      </c>
-      <c r="T20" s="3">
-        <v>12700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>18700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>6000</v>
-      </c>
-      <c r="W20" s="3">
-        <v>109100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>19900</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-33000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>231400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>77600</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>25400</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>47400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1319900</v>
+        <v>1155100</v>
       </c>
       <c r="E21" s="3">
-        <v>1309700</v>
+        <v>1339700</v>
       </c>
       <c r="F21" s="3">
-        <v>1351900</v>
+        <v>1329400</v>
       </c>
       <c r="G21" s="3">
-        <v>1299900</v>
+        <v>1372300</v>
       </c>
       <c r="H21" s="3">
-        <v>1352000</v>
+        <v>1319500</v>
       </c>
       <c r="I21" s="3">
-        <v>1052700</v>
+        <v>1372400</v>
       </c>
       <c r="J21" s="3">
+        <v>1068500</v>
+      </c>
+      <c r="K21" s="3">
         <v>1074100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1239400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1197600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1145300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1050200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>795700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>631400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>129400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>909400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1339200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1831800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1238200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1442400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1646500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1608300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1369100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>35400</v>
+        <v>40500</v>
       </c>
       <c r="E22" s="3">
-        <v>33600</v>
+        <v>35900</v>
       </c>
       <c r="F22" s="3">
-        <v>30800</v>
+        <v>34100</v>
       </c>
       <c r="G22" s="3">
-        <v>26900</v>
+        <v>31200</v>
       </c>
       <c r="H22" s="3">
-        <v>26000</v>
+        <v>27300</v>
       </c>
       <c r="I22" s="3">
-        <v>20800</v>
+        <v>26400</v>
       </c>
       <c r="J22" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>31800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>32800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>57400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>66700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>27700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>34100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>31600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>38200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>28500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>17900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>747600</v>
+        <v>587000</v>
       </c>
       <c r="E23" s="3">
-        <v>781800</v>
+        <v>758800</v>
       </c>
       <c r="F23" s="3">
-        <v>841500</v>
+        <v>793600</v>
       </c>
       <c r="G23" s="3">
-        <v>791200</v>
+        <v>854200</v>
       </c>
       <c r="H23" s="3">
-        <v>824300</v>
+        <v>803100</v>
       </c>
       <c r="I23" s="3">
-        <v>578000</v>
+        <v>836700</v>
       </c>
       <c r="J23" s="3">
+        <v>586800</v>
+      </c>
+      <c r="K23" s="3">
         <v>618200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>773800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>715000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>683500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>596000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>278300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>90600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-467600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>287500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>659500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1153400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>546500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>749100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1142600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1077300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>890600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>843500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>927100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>885100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>801000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>185000</v>
+        <v>169500</v>
       </c>
       <c r="E24" s="3">
-        <v>155700</v>
+        <v>187800</v>
       </c>
       <c r="F24" s="3">
-        <v>230500</v>
+        <v>158100</v>
       </c>
       <c r="G24" s="3">
-        <v>198600</v>
+        <v>234000</v>
       </c>
       <c r="H24" s="3">
-        <v>150500</v>
+        <v>202000</v>
       </c>
       <c r="I24" s="3">
-        <v>220700</v>
+        <v>152800</v>
       </c>
       <c r="J24" s="3">
+        <v>224100</v>
+      </c>
+      <c r="K24" s="3">
         <v>176800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-25800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>178100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>172500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>130600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>123500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>154300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-54500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>117800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>184000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>311900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>138400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>192000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>447300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>269000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>226900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>242800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>331900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>307100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>212300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>255800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>298900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2261,192 +2310,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>562600</v>
+        <v>417500</v>
       </c>
       <c r="E26" s="3">
-        <v>626100</v>
+        <v>571000</v>
       </c>
       <c r="F26" s="3">
-        <v>610900</v>
+        <v>635600</v>
       </c>
       <c r="G26" s="3">
-        <v>592600</v>
+        <v>620100</v>
       </c>
       <c r="H26" s="3">
-        <v>673800</v>
+        <v>601100</v>
       </c>
       <c r="I26" s="3">
-        <v>357300</v>
+        <v>684000</v>
       </c>
       <c r="J26" s="3">
+        <v>362700</v>
+      </c>
+      <c r="K26" s="3">
         <v>441400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>799600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>536900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>511000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>465400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>154800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-63700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-413100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>169800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>475500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>841500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>408100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>557100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>695400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>808300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>663700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>600600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>840100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>620100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>672800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>545200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>755300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>546900</v>
+        <v>412900</v>
       </c>
       <c r="E27" s="3">
-        <v>615100</v>
+        <v>555200</v>
       </c>
       <c r="F27" s="3">
-        <v>602000</v>
+        <v>624400</v>
       </c>
       <c r="G27" s="3">
-        <v>586400</v>
+        <v>611000</v>
       </c>
       <c r="H27" s="3">
-        <v>661300</v>
+        <v>594800</v>
       </c>
       <c r="I27" s="3">
-        <v>346500</v>
+        <v>671300</v>
       </c>
       <c r="J27" s="3">
+        <v>351700</v>
+      </c>
+      <c r="K27" s="3">
         <v>434400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>789800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>527900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>448400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>148300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-76400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>147700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>469700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>825800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>393100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>536100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>681400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>788200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>647300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>576300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>818200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>596000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>656300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>525400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>731700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2537,64 +2595,67 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>11400</v>
+        <v>22300</v>
       </c>
       <c r="E29" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F29" s="3">
         <v>-3300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1100</v>
       </c>
-      <c r="G29" s="3">
-        <v>154800</v>
-      </c>
       <c r="H29" s="3">
-        <v>-25200</v>
+        <v>157100</v>
       </c>
       <c r="I29" s="3">
-        <v>-86800</v>
+        <v>-25600</v>
       </c>
       <c r="J29" s="3">
+        <v>-88100</v>
+      </c>
+      <c r="K29" s="3">
         <v>-76900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-987700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-19400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-7500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>1574000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-142300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>60300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>46600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>23900</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2629,8 +2690,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2721,8 +2785,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2813,192 +2880,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>48200</v>
+        <v>86800</v>
       </c>
       <c r="E32" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F32" s="3">
         <v>2100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-25700</v>
-      </c>
       <c r="G32" s="3">
-        <v>72100</v>
+        <v>-26000</v>
       </c>
       <c r="H32" s="3">
-        <v>34400</v>
+        <v>73200</v>
       </c>
       <c r="I32" s="3">
+        <v>34900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-56400</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>23300</v>
+      </c>
+      <c r="S32" s="3">
+        <v>24000</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-109100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>24800</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-231400</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-25400</v>
       </c>
-      <c r="J32" s="3">
-        <v>-56400</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-32100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-23500</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>23300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>24000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-76900</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-109100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>24800</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-19900</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>33000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-231400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-77600</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>36800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>558400</v>
+        <v>435200</v>
       </c>
       <c r="E33" s="3">
-        <v>611800</v>
+        <v>566800</v>
       </c>
       <c r="F33" s="3">
-        <v>600900</v>
+        <v>621100</v>
       </c>
       <c r="G33" s="3">
-        <v>741200</v>
+        <v>610000</v>
       </c>
       <c r="H33" s="3">
-        <v>636100</v>
+        <v>751900</v>
       </c>
       <c r="I33" s="3">
-        <v>259700</v>
+        <v>645700</v>
       </c>
       <c r="J33" s="3">
+        <v>263600</v>
+      </c>
+      <c r="K33" s="3">
         <v>357500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-197900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>508500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>493000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2022400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-354100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>171600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>469700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>825800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>393100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>536100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>681400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>788200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>647300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>576300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>818200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>596000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>656300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>525400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>731700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3089,197 +3165,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>558400</v>
+        <v>435200</v>
       </c>
       <c r="E35" s="3">
-        <v>611800</v>
+        <v>566800</v>
       </c>
       <c r="F35" s="3">
-        <v>600900</v>
+        <v>621100</v>
       </c>
       <c r="G35" s="3">
-        <v>741200</v>
+        <v>610000</v>
       </c>
       <c r="H35" s="3">
-        <v>636100</v>
+        <v>751900</v>
       </c>
       <c r="I35" s="3">
-        <v>259700</v>
+        <v>645700</v>
       </c>
       <c r="J35" s="3">
+        <v>263600</v>
+      </c>
+      <c r="K35" s="3">
         <v>357500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-197900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>508500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>493000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2022400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-354100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>171600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>469700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>825800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>393100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>536100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>681400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>788200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>647300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>576300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>818200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>596000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>656300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>525400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>731700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3312,8 +3397,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3346,836 +3432,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4281200</v>
+        <v>4883800</v>
       </c>
       <c r="E41" s="3">
-        <v>4047200</v>
+        <v>4345700</v>
       </c>
       <c r="F41" s="3">
-        <v>3433000</v>
+        <v>4108200</v>
       </c>
       <c r="G41" s="3">
-        <v>3445500</v>
+        <v>3484700</v>
       </c>
       <c r="H41" s="3">
-        <v>3483100</v>
+        <v>3497400</v>
       </c>
       <c r="I41" s="3">
-        <v>4120000</v>
+        <v>3535500</v>
       </c>
       <c r="J41" s="3">
+        <v>4182100</v>
+      </c>
+      <c r="K41" s="3">
         <v>4506600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5410400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6130200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7004500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8436200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5941300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5150000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5362800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3123800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3943900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2740700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3982700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3636300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4157200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3618500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3839700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>56900</v>
+        <v>72700</v>
       </c>
       <c r="E42" s="3">
-        <v>108800</v>
+        <v>57800</v>
       </c>
       <c r="F42" s="3">
-        <v>56900</v>
+        <v>110500</v>
       </c>
       <c r="G42" s="3">
-        <v>100300</v>
+        <v>57700</v>
       </c>
       <c r="H42" s="3">
-        <v>152100</v>
+        <v>101800</v>
       </c>
       <c r="I42" s="3">
-        <v>62100</v>
+        <v>154400</v>
       </c>
       <c r="J42" s="3">
+        <v>63000</v>
+      </c>
+      <c r="K42" s="3">
         <v>65700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>80900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>54100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>51600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>45100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>51500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>86200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>155300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1369700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1356600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1323100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1240800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1452400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1538000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1440600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6886600</v>
+        <v>6418500</v>
       </c>
       <c r="E43" s="3">
-        <v>6660000</v>
+        <v>6990300</v>
       </c>
       <c r="F43" s="3">
-        <v>6244300</v>
+        <v>6760300</v>
       </c>
       <c r="G43" s="3">
-        <v>6285500</v>
+        <v>6338400</v>
       </c>
       <c r="H43" s="3">
-        <v>6488500</v>
+        <v>6380100</v>
       </c>
       <c r="I43" s="3">
-        <v>5853400</v>
+        <v>6586200</v>
       </c>
       <c r="J43" s="3">
+        <v>5941600</v>
+      </c>
+      <c r="K43" s="3">
         <v>5292500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5094900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5021400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4848000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4560700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4894700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5247200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5166800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5957200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11999600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5330100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5120200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5535200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5472300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5235300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4915100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6471500</v>
+        <v>5854200</v>
       </c>
       <c r="E44" s="3">
-        <v>6560800</v>
+        <v>6569000</v>
       </c>
       <c r="F44" s="3">
-        <v>6125300</v>
+        <v>6659700</v>
       </c>
       <c r="G44" s="3">
-        <v>5878400</v>
+        <v>6217600</v>
       </c>
       <c r="H44" s="3">
-        <v>6261700</v>
+        <v>5967000</v>
       </c>
       <c r="I44" s="3">
-        <v>5642300</v>
+        <v>6356000</v>
       </c>
       <c r="J44" s="3">
+        <v>5727200</v>
+      </c>
+      <c r="K44" s="3">
         <v>4807600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4329100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4487800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4166700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3725300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3600800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4021000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5073500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5496700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>11174200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5646400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5756300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6145500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5826700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6012000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5542800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>924800</v>
+        <v>951400</v>
       </c>
       <c r="E45" s="3">
-        <v>919000</v>
+        <v>938800</v>
       </c>
       <c r="F45" s="3">
-        <v>908600</v>
+        <v>932900</v>
       </c>
       <c r="G45" s="3">
-        <v>974300</v>
+        <v>922300</v>
       </c>
       <c r="H45" s="3">
-        <v>1072100</v>
+        <v>988900</v>
       </c>
       <c r="I45" s="3">
-        <v>1214000</v>
+        <v>1088200</v>
       </c>
       <c r="J45" s="3">
+        <v>1232300</v>
+      </c>
+      <c r="K45" s="3">
         <v>911400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>836800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>635600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>649000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>587400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>569600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>679500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>648300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>643800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>780500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1290500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1233600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1217000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1145000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1780200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1605900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18621100</v>
+        <v>18180700</v>
       </c>
       <c r="E46" s="3">
-        <v>18295900</v>
+        <v>18901600</v>
       </c>
       <c r="F46" s="3">
-        <v>16768100</v>
+        <v>18571500</v>
       </c>
       <c r="G46" s="3">
-        <v>16684000</v>
+        <v>17020600</v>
       </c>
       <c r="H46" s="3">
-        <v>17457600</v>
+        <v>16935300</v>
       </c>
       <c r="I46" s="3">
-        <v>16891800</v>
+        <v>17720500</v>
       </c>
       <c r="J46" s="3">
+        <v>17146200</v>
+      </c>
+      <c r="K46" s="3">
         <v>15583800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15752000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16329200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16719800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17354700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15059700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15149100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16337500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15376800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17476700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16364300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17415900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17774800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18053400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18184000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17344100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1100900</v>
+        <v>1161900</v>
       </c>
       <c r="E47" s="3">
-        <v>1024100</v>
+        <v>1117500</v>
       </c>
       <c r="F47" s="3">
-        <v>1000900</v>
+        <v>1039500</v>
       </c>
       <c r="G47" s="3">
-        <v>952200</v>
+        <v>1016000</v>
       </c>
       <c r="H47" s="3">
-        <v>1031800</v>
+        <v>966500</v>
       </c>
       <c r="I47" s="3">
-        <v>1091400</v>
+        <v>1047400</v>
       </c>
       <c r="J47" s="3">
+        <v>1107900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1065600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1137000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1145100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1145500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1050000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1009800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1054200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1276800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1505300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2990000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1752500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1842600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2137000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2062100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2715400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2197500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13411500</v>
+        <v>13868500</v>
       </c>
       <c r="E48" s="3">
-        <v>13226400</v>
+        <v>13613400</v>
       </c>
       <c r="F48" s="3">
-        <v>12355200</v>
+        <v>13425600</v>
       </c>
       <c r="G48" s="3">
-        <v>12336700</v>
+        <v>12541200</v>
       </c>
       <c r="H48" s="3">
-        <v>12426300</v>
+        <v>12522500</v>
       </c>
       <c r="I48" s="3">
-        <v>12242400</v>
+        <v>12613400</v>
       </c>
       <c r="J48" s="3">
+        <v>12426800</v>
+      </c>
+      <c r="K48" s="3">
         <v>11674800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11829900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12035900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12457000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12007200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12331000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13384700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15078000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15667800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31118800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13721000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13711500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14610900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13861400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13471900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12947700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2339300</v>
+        <v>2364700</v>
       </c>
       <c r="E49" s="3">
-        <v>2185100</v>
+        <v>2374600</v>
       </c>
       <c r="F49" s="3">
-        <v>2025800</v>
+        <v>2218000</v>
       </c>
       <c r="G49" s="3">
-        <v>1967600</v>
+        <v>2056400</v>
       </c>
       <c r="H49" s="3">
-        <v>2027700</v>
+        <v>1997200</v>
       </c>
       <c r="I49" s="3">
-        <v>1943100</v>
+        <v>2058200</v>
       </c>
       <c r="J49" s="3">
+        <v>1972300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1826000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1787000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1807800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1487700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1428300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1576900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1642100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1787900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1829400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3799400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1743200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1768700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>861500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>957700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>954200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>903400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>891800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>949500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>992600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>988400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>656000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>657700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4266,8 +4380,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4358,100 +4475,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1119000</v>
+        <v>1007600</v>
       </c>
       <c r="E52" s="3">
-        <v>1067000</v>
+        <v>1135900</v>
       </c>
       <c r="F52" s="3">
-        <v>1016400</v>
+        <v>1083000</v>
       </c>
       <c r="G52" s="3">
-        <v>1008500</v>
+        <v>1031700</v>
       </c>
       <c r="H52" s="3">
-        <v>1129100</v>
+        <v>1023700</v>
       </c>
       <c r="I52" s="3">
-        <v>1094400</v>
+        <v>1146100</v>
       </c>
       <c r="J52" s="3">
+        <v>1110900</v>
+      </c>
+      <c r="K52" s="3">
         <v>994800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>923600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>785600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>797700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>746000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>730400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>798900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>893400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>901800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1805500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1353500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1388500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1458400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1317400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1118100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1054100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>998600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>934800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>965000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4542,100 +4665,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36591800</v>
+        <v>36583500</v>
       </c>
       <c r="E54" s="3">
-        <v>35798500</v>
+        <v>37142900</v>
       </c>
       <c r="F54" s="3">
-        <v>33166400</v>
+        <v>36337600</v>
       </c>
       <c r="G54" s="3">
-        <v>32949000</v>
+        <v>33665900</v>
       </c>
       <c r="H54" s="3">
-        <v>34072500</v>
+        <v>33445200</v>
       </c>
       <c r="I54" s="3">
-        <v>33263200</v>
+        <v>34585600</v>
       </c>
       <c r="J54" s="3">
+        <v>33764200</v>
+      </c>
+      <c r="K54" s="3">
         <v>31145100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31429500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32103700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32607800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32586200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>30707800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32029000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>35373500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35281000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>38963600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34934500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>36127200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36842700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>36252100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36443600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34446800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4668,8 +4797,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4702,560 +4832,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3550900</v>
+        <v>4038900</v>
       </c>
       <c r="E57" s="3">
-        <v>3507900</v>
+        <v>3604300</v>
       </c>
       <c r="F57" s="3">
-        <v>3411500</v>
+        <v>3560700</v>
       </c>
       <c r="G57" s="3">
-        <v>4033800</v>
+        <v>3462900</v>
       </c>
       <c r="H57" s="3">
-        <v>3775100</v>
+        <v>4094500</v>
       </c>
       <c r="I57" s="3">
-        <v>3601600</v>
+        <v>3832000</v>
       </c>
       <c r="J57" s="3">
+        <v>3655800</v>
+      </c>
+      <c r="K57" s="3">
         <v>3255900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3551900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3032400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3076400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2733400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3079600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2599700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2589600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3128200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5968100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1835100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2026300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2185100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2208700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2243400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2116200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2249100</v>
+        <v>2152600</v>
       </c>
       <c r="E58" s="3">
-        <v>2231700</v>
+        <v>2283000</v>
       </c>
       <c r="F58" s="3">
-        <v>1446000</v>
+        <v>2265400</v>
       </c>
       <c r="G58" s="3">
-        <v>1804500</v>
+        <v>1467700</v>
       </c>
       <c r="H58" s="3">
-        <v>1186000</v>
+        <v>1831700</v>
       </c>
       <c r="I58" s="3">
-        <v>1024100</v>
+        <v>1203900</v>
       </c>
       <c r="J58" s="3">
+        <v>1039500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1302700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1407200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1552700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1560400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2710100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2550400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2969700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3632300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1617000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2949000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1745500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2089300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2235600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2774400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2216500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1276800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2793500</v>
+        <v>2333300</v>
       </c>
       <c r="E59" s="3">
-        <v>2533400</v>
+        <v>2835500</v>
       </c>
       <c r="F59" s="3">
-        <v>2324800</v>
+        <v>2571500</v>
       </c>
       <c r="G59" s="3">
-        <v>2087600</v>
+        <v>2359800</v>
       </c>
       <c r="H59" s="3">
-        <v>2636100</v>
+        <v>2119100</v>
       </c>
       <c r="I59" s="3">
-        <v>2650800</v>
+        <v>2675800</v>
       </c>
       <c r="J59" s="3">
+        <v>2690700</v>
+      </c>
+      <c r="K59" s="3">
         <v>2342100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2071700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2121400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2131300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2479300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2006000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2082500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1936300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2027200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6356000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3969500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4052700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4241900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4382200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3976300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3814200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8593500</v>
+        <v>8524800</v>
       </c>
       <c r="E60" s="3">
-        <v>8273000</v>
+        <v>8722900</v>
       </c>
       <c r="F60" s="3">
-        <v>7182300</v>
+        <v>8397600</v>
       </c>
       <c r="G60" s="3">
-        <v>7209700</v>
+        <v>7290400</v>
       </c>
       <c r="H60" s="3">
-        <v>7597300</v>
+        <v>7318300</v>
       </c>
       <c r="I60" s="3">
-        <v>7276500</v>
+        <v>7711700</v>
       </c>
       <c r="J60" s="3">
+        <v>7386100</v>
+      </c>
+      <c r="K60" s="3">
         <v>6900800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7030800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6706400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6768200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7922700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7636000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7651900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8158200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6772400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8156500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7550100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8168300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8662700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8374400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8436100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7207200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3416900</v>
+        <v>3442600</v>
       </c>
       <c r="E61" s="3">
-        <v>3380200</v>
+        <v>3468300</v>
       </c>
       <c r="F61" s="3">
-        <v>3881300</v>
+        <v>3431100</v>
       </c>
       <c r="G61" s="3">
-        <v>4005700</v>
+        <v>3939700</v>
       </c>
       <c r="H61" s="3">
-        <v>4119100</v>
+        <v>4066000</v>
       </c>
       <c r="I61" s="3">
-        <v>4112500</v>
+        <v>4181100</v>
       </c>
       <c r="J61" s="3">
+        <v>4174500</v>
+      </c>
+      <c r="K61" s="3">
         <v>4008900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4165300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4321900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4445000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4555600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4825000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5152000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5627300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5787000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5978000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4133900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4137000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2442500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2031700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1989500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2684500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1691800</v>
+        <v>1663600</v>
       </c>
       <c r="E62" s="3">
-        <v>1744700</v>
+        <v>1717300</v>
       </c>
       <c r="F62" s="3">
-        <v>1686200</v>
+        <v>1771000</v>
       </c>
       <c r="G62" s="3">
-        <v>1730600</v>
+        <v>1711600</v>
       </c>
       <c r="H62" s="3">
-        <v>1825200</v>
+        <v>1756700</v>
       </c>
       <c r="I62" s="3">
-        <v>1923700</v>
+        <v>1852700</v>
       </c>
       <c r="J62" s="3">
+        <v>1952700</v>
+      </c>
+      <c r="K62" s="3">
         <v>1847700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1853700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2048700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2108100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2041900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2155300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2277400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2570900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2755700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4777500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2594100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2650800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2918600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2848700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3083300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2898400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5346,8 +5495,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5438,8 +5590,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5530,100 +5685,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14043500</v>
+        <v>13980300</v>
       </c>
       <c r="E66" s="3">
-        <v>13729400</v>
+        <v>14255000</v>
       </c>
       <c r="F66" s="3">
-        <v>13076600</v>
+        <v>13936200</v>
       </c>
       <c r="G66" s="3">
-        <v>13255900</v>
+        <v>13273500</v>
       </c>
       <c r="H66" s="3">
-        <v>13863900</v>
+        <v>13455500</v>
       </c>
       <c r="I66" s="3">
-        <v>13634900</v>
+        <v>14072700</v>
       </c>
       <c r="J66" s="3">
+        <v>13840300</v>
+      </c>
+      <c r="K66" s="3">
         <v>13072000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13362200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13379600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13639700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14844900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14948600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15423000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16749200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15745300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17560800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14744100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15439800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14541300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13766400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13999700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13266900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5656,8 +5817,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5748,8 +5910,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5840,8 +6005,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5932,8 +6100,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6024,100 +6195,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>17590200</v>
+        <v>18273600</v>
       </c>
       <c r="E72" s="3">
-        <v>17486800</v>
+        <v>17855100</v>
       </c>
       <c r="F72" s="3">
-        <v>16818500</v>
+        <v>17750100</v>
       </c>
       <c r="G72" s="3">
-        <v>16607400</v>
+        <v>17071800</v>
       </c>
       <c r="H72" s="3">
-        <v>15821800</v>
+        <v>16857500</v>
       </c>
       <c r="I72" s="3">
-        <v>15569500</v>
+        <v>16060100</v>
       </c>
       <c r="J72" s="3">
+        <v>15804000</v>
+      </c>
+      <c r="K72" s="3">
         <v>15308800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15874300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16784800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17007300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15925300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14682900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15438900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17177700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>18111900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>44028300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>22532700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>22193000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22722500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22336800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21311700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>20630000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6208,8 +6385,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6300,8 +6480,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6392,100 +6575,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22548300</v>
+        <v>22603200</v>
       </c>
       <c r="E76" s="3">
-        <v>22069000</v>
+        <v>22887900</v>
       </c>
       <c r="F76" s="3">
-        <v>20089800</v>
+        <v>22401400</v>
       </c>
       <c r="G76" s="3">
-        <v>19693100</v>
+        <v>20392400</v>
       </c>
       <c r="H76" s="3">
-        <v>20208600</v>
+        <v>19989700</v>
       </c>
       <c r="I76" s="3">
-        <v>19628300</v>
+        <v>20512900</v>
       </c>
       <c r="J76" s="3">
+        <v>19923900</v>
+      </c>
+      <c r="K76" s="3">
         <v>18073100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18067300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18724100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18968100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17741300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15759200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16606100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18624400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19535800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>21402800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20190400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20687400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>22301400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22485700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22443800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21179900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6576,197 +6765,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>558400</v>
+        <v>435200</v>
       </c>
       <c r="E81" s="3">
-        <v>611800</v>
+        <v>566800</v>
       </c>
       <c r="F81" s="3">
-        <v>600900</v>
+        <v>621100</v>
       </c>
       <c r="G81" s="3">
-        <v>741200</v>
+        <v>610000</v>
       </c>
       <c r="H81" s="3">
-        <v>636100</v>
+        <v>751900</v>
       </c>
       <c r="I81" s="3">
-        <v>259700</v>
+        <v>645700</v>
       </c>
       <c r="J81" s="3">
+        <v>263600</v>
+      </c>
+      <c r="K81" s="3">
         <v>357500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-197900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>508500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>493000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2022400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-354100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>171600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>469700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>825800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>393100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>536100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>681400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>788200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>647300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>576300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>818200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>596000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>656300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>525400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>731700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6799,100 +6997,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>536900</v>
+        <v>527600</v>
       </c>
       <c r="E83" s="3">
-        <v>494200</v>
+        <v>544900</v>
       </c>
       <c r="F83" s="3">
-        <v>479700</v>
+        <v>501700</v>
       </c>
       <c r="G83" s="3">
-        <v>481800</v>
+        <v>486900</v>
       </c>
       <c r="H83" s="3">
-        <v>501700</v>
+        <v>489100</v>
       </c>
       <c r="I83" s="3">
-        <v>453900</v>
+        <v>509300</v>
       </c>
       <c r="J83" s="3">
+        <v>460700</v>
+      </c>
+      <c r="K83" s="3">
         <v>435800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>444600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>461700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>442800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>435700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>498300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>516900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>565200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>589000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>627500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>642000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>648500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>644800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>479300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>503300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>444400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>465300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>489800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>473600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>440100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>440600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>428800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6983,8 +7185,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7075,8 +7280,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7167,8 +7375,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7259,8 +7470,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7351,76 +7565,79 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1253800</v>
+        <v>1595900</v>
       </c>
       <c r="E89" s="3">
-        <v>772100</v>
+        <v>1272700</v>
       </c>
       <c r="F89" s="3">
-        <v>794900</v>
+        <v>783700</v>
       </c>
       <c r="G89" s="3">
-        <v>959300</v>
+        <v>806900</v>
       </c>
       <c r="H89" s="3">
-        <v>950900</v>
+        <v>973800</v>
       </c>
       <c r="I89" s="3">
-        <v>136100</v>
+        <v>965200</v>
       </c>
       <c r="J89" s="3">
+        <v>138100</v>
+      </c>
+      <c r="K89" s="3">
         <v>399400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>416000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>180000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>644200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1553400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1323100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>691700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>564600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1895100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>694900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>888100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1172900</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -7443,8 +7660,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7477,76 +7697,77 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103013000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-82364000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-65299000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-92261000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-196600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-349000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-376900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-364000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-325900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-566700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-626200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-678600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-523100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-680800</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -7569,8 +7790,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7661,8 +7885,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7753,76 +7980,79 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-472200</v>
+        <v>-661000</v>
       </c>
       <c r="E94" s="3">
-        <v>-321200</v>
+        <v>-479300</v>
       </c>
       <c r="F94" s="3">
-        <v>-532200</v>
+        <v>-326100</v>
       </c>
       <c r="G94" s="3">
-        <v>-402800</v>
+        <v>-540200</v>
       </c>
       <c r="H94" s="3">
-        <v>-1077400</v>
+        <v>-408900</v>
       </c>
       <c r="I94" s="3">
-        <v>-272500</v>
+        <v>-1093700</v>
       </c>
       <c r="J94" s="3">
+        <v>-276600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-491600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-352700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-598100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-175200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2055000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-292400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-382600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-522200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-44100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-358100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-694000</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -7845,8 +8075,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7879,71 +8112,72 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-453900</v>
+        <v>-600</v>
       </c>
       <c r="E96" s="3">
-        <v>-5200</v>
+        <v>-460800</v>
       </c>
       <c r="F96" s="3">
-        <v>-403700</v>
+        <v>-5300</v>
       </c>
       <c r="G96" s="3">
+        <v>-409800</v>
+      </c>
+      <c r="H96" s="3">
         <v>-600</v>
       </c>
-      <c r="H96" s="3">
-        <v>-392300</v>
-      </c>
       <c r="I96" s="3">
-        <v>-4000</v>
+        <v>-398200</v>
       </c>
       <c r="J96" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="K96" s="3">
         <v>-393400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-430900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-6100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-293600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-273700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-5900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-490000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-528100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-5400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-572200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7971,8 +8205,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8063,8 +8300,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8155,8 +8395,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8247,76 +8490,79 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-568900</v>
+        <v>-244200</v>
       </c>
       <c r="E100" s="3">
-        <v>-124100</v>
+        <v>-577500</v>
       </c>
       <c r="F100" s="3">
-        <v>-285900</v>
+        <v>-125900</v>
       </c>
       <c r="G100" s="3">
-        <v>-269700</v>
+        <v>-290200</v>
       </c>
       <c r="H100" s="3">
-        <v>-620000</v>
+        <v>-273800</v>
       </c>
       <c r="I100" s="3">
-        <v>-635600</v>
+        <v>-629300</v>
       </c>
       <c r="J100" s="3">
+        <v>-645100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-892400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-210100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-526400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-326200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-385600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-724900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1947000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-568400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-230900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1278300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1194800</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -8339,76 +8585,79 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>21300</v>
+        <v>-152500</v>
       </c>
       <c r="E101" s="3">
-        <v>287500</v>
+        <v>21600</v>
       </c>
       <c r="F101" s="3">
-        <v>10600</v>
+        <v>291800</v>
       </c>
       <c r="G101" s="3">
-        <v>-324400</v>
+        <v>10800</v>
       </c>
       <c r="H101" s="3">
-        <v>109700</v>
+        <v>-329200</v>
       </c>
       <c r="I101" s="3">
-        <v>385400</v>
+        <v>111300</v>
       </c>
       <c r="J101" s="3">
+        <v>391200</v>
+      </c>
+      <c r="K101" s="3">
         <v>262000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>110000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-32400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-57400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>316500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>28100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>82200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-164300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>102700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-89500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-56300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>67800</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8431,76 +8680,79 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>234000</v>
+        <v>539200</v>
       </c>
       <c r="E102" s="3">
-        <v>614300</v>
+        <v>237500</v>
       </c>
       <c r="F102" s="3">
-        <v>-12600</v>
+        <v>623500</v>
       </c>
       <c r="G102" s="3">
-        <v>-37500</v>
+        <v>-12800</v>
       </c>
       <c r="H102" s="3">
-        <v>-636900</v>
+        <v>-38100</v>
       </c>
       <c r="I102" s="3">
-        <v>-386600</v>
+        <v>-646500</v>
       </c>
       <c r="J102" s="3">
+        <v>-392400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-722700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-430700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-740900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2689400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1095400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>252500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2338300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-690300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1329100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>564100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-648100</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -8521,6 +8773,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -656,423 +656,435 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7519500</v>
+        <v>6789100</v>
       </c>
       <c r="E8" s="3">
-        <v>7390000</v>
+        <v>7117900</v>
       </c>
       <c r="F8" s="3">
-        <v>7132000</v>
+        <v>6995300</v>
       </c>
       <c r="G8" s="3">
-        <v>7033500</v>
+        <v>6751100</v>
       </c>
       <c r="H8" s="3">
-        <v>7637400</v>
+        <v>6657800</v>
       </c>
       <c r="I8" s="3">
-        <v>7350500</v>
+        <v>7229500</v>
       </c>
       <c r="J8" s="3">
+        <v>6957900</v>
+      </c>
+      <c r="K8" s="3">
         <v>6708500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5916300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5800300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5820400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5756600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5156000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5065500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5774300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4752500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6217800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8048800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8122100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8168200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8151300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9212700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8349700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4652000</v>
+        <v>4053200</v>
       </c>
       <c r="E9" s="3">
-        <v>4574900</v>
+        <v>4403500</v>
       </c>
       <c r="F9" s="3">
-        <v>4376500</v>
+        <v>4330500</v>
       </c>
       <c r="G9" s="3">
-        <v>4333300</v>
+        <v>4142800</v>
       </c>
       <c r="H9" s="3">
-        <v>4674300</v>
+        <v>4101800</v>
       </c>
       <c r="I9" s="3">
-        <v>4504800</v>
+        <v>4424600</v>
       </c>
       <c r="J9" s="3">
+        <v>4264200</v>
+      </c>
+      <c r="K9" s="3">
         <v>4114800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3615000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3318300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3396300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3395600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3069100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2818700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3709400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3230500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3894700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5024300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4951200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5149100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5094700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5770100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5275700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2867500</v>
+        <v>2735900</v>
       </c>
       <c r="E10" s="3">
-        <v>2815100</v>
+        <v>2714400</v>
       </c>
       <c r="F10" s="3">
-        <v>2755500</v>
+        <v>2664700</v>
       </c>
       <c r="G10" s="3">
-        <v>2700200</v>
+        <v>2608300</v>
       </c>
       <c r="H10" s="3">
-        <v>2963100</v>
+        <v>2556000</v>
       </c>
       <c r="I10" s="3">
-        <v>2845700</v>
+        <v>2804800</v>
       </c>
       <c r="J10" s="3">
+        <v>2693700</v>
+      </c>
+      <c r="K10" s="3">
         <v>2593700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2301300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2482000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2424100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2361000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2086900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2246800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2064900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1522000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2323200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3024500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3170900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3019100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3056600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3442500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3074000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1106,103 +1118,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>219500</v>
+        <v>203500</v>
       </c>
       <c r="E12" s="3">
-        <v>203400</v>
+        <v>207700</v>
       </c>
       <c r="F12" s="3">
-        <v>199300</v>
+        <v>192500</v>
       </c>
       <c r="G12" s="3">
-        <v>200000</v>
+        <v>188700</v>
       </c>
       <c r="H12" s="3">
-        <v>205300</v>
+        <v>189400</v>
       </c>
       <c r="I12" s="3">
-        <v>189100</v>
+        <v>194300</v>
       </c>
       <c r="J12" s="3">
+        <v>179000</v>
+      </c>
+      <c r="K12" s="3">
         <v>184100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>175100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>157300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>163000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>168300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>159200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>126200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>173000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>186300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>229200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>252500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>235800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>252200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>243000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>269400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>238200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>228100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>220800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>241900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>216700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>232200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>207300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>215600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1296,198 +1312,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>104100</v>
+        <v>22600</v>
       </c>
       <c r="E14" s="3">
-        <v>-6100</v>
+        <v>98500</v>
       </c>
       <c r="F14" s="3">
-        <v>-30100</v>
+        <v>-5700</v>
       </c>
       <c r="G14" s="3">
-        <v>8900</v>
+        <v>-28500</v>
       </c>
       <c r="H14" s="3">
-        <v>179000</v>
+        <v>8400</v>
       </c>
       <c r="I14" s="3">
-        <v>13400</v>
+        <v>32600</v>
       </c>
       <c r="J14" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K14" s="3">
         <v>5600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>85700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>49900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>26900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>39800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>487000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>682000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>383400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>47500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>190200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>41600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-103500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-280400</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3">
         <v>99800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>9300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>58400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>39200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>201500</v>
+        <v>200200</v>
       </c>
       <c r="E15" s="3">
-        <v>196300</v>
+        <v>190800</v>
       </c>
       <c r="F15" s="3">
-        <v>186000</v>
+        <v>185800</v>
       </c>
       <c r="G15" s="3">
-        <v>176600</v>
+        <v>176100</v>
       </c>
       <c r="H15" s="3">
-        <v>178400</v>
+        <v>167200</v>
       </c>
       <c r="I15" s="3">
-        <v>182800</v>
+        <v>168800</v>
       </c>
       <c r="J15" s="3">
+        <v>173000</v>
+      </c>
+      <c r="K15" s="3">
         <v>165700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>154300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>158200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>161700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>161900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>156500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>159000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>171800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>179100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>193000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>312700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>310900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>200000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>203500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>85000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>84700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>79500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>78600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>80500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>76300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>73000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>72800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>71300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1518,198 +1543,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6805200</v>
+        <v>6037800</v>
       </c>
       <c r="E17" s="3">
-        <v>6546300</v>
+        <v>6441700</v>
       </c>
       <c r="F17" s="3">
-        <v>6302200</v>
+        <v>6196700</v>
       </c>
       <c r="G17" s="3">
-        <v>6174100</v>
+        <v>5965600</v>
       </c>
       <c r="H17" s="3">
-        <v>6733800</v>
+        <v>5844300</v>
       </c>
       <c r="I17" s="3">
-        <v>6452500</v>
+        <v>6374100</v>
       </c>
       <c r="J17" s="3">
+        <v>6107900</v>
+      </c>
+      <c r="K17" s="3">
         <v>6126500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5334400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5037600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5098300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5071600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4565000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4771800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5669200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5164900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5873400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7408900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6921500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7573700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7348300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8154600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7219900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>714300</v>
+        <v>751300</v>
       </c>
       <c r="E18" s="3">
-        <v>843700</v>
+        <v>676200</v>
       </c>
       <c r="F18" s="3">
-        <v>829800</v>
+        <v>798600</v>
       </c>
       <c r="G18" s="3">
-        <v>859400</v>
+        <v>785500</v>
       </c>
       <c r="H18" s="3">
-        <v>903600</v>
+        <v>813500</v>
       </c>
       <c r="I18" s="3">
-        <v>898000</v>
+        <v>855400</v>
       </c>
       <c r="J18" s="3">
+        <v>850100</v>
+      </c>
+      <c r="K18" s="3">
         <v>582100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>581900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>762800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>722100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>684900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>591000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>293700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>105100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-412500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>344400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>640000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1200600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>594400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>803000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1058100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1129800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>904800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>908100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>978800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>874100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>888200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>855800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1743,483 +1775,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-86800</v>
+        <v>56500</v>
       </c>
       <c r="E20" s="3">
-        <v>-48900</v>
+        <v>-82200</v>
       </c>
       <c r="F20" s="3">
-        <v>-2100</v>
+        <v>-46300</v>
       </c>
       <c r="G20" s="3">
-        <v>26000</v>
+        <v>-2000</v>
       </c>
       <c r="H20" s="3">
-        <v>-73200</v>
+        <v>24700</v>
       </c>
       <c r="I20" s="3">
-        <v>-34900</v>
+        <v>-69300</v>
       </c>
       <c r="J20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="K20" s="3">
         <v>25800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>56400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>32100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>13800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>17500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>23500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-23300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-24000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>76900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>18700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>109100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>231400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>77600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>47400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1155100</v>
+        <v>1350400</v>
       </c>
       <c r="E21" s="3">
-        <v>1339700</v>
+        <v>1093400</v>
       </c>
       <c r="F21" s="3">
-        <v>1329400</v>
+        <v>1268200</v>
       </c>
       <c r="G21" s="3">
-        <v>1372300</v>
+        <v>1258400</v>
       </c>
       <c r="H21" s="3">
-        <v>1319500</v>
+        <v>1299000</v>
       </c>
       <c r="I21" s="3">
-        <v>1372400</v>
+        <v>1249000</v>
       </c>
       <c r="J21" s="3">
+        <v>1299100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1068500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1074100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1239400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1197600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1145300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1050200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>795700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>631400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>129400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>909400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1339200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1831800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1238200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1442400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1646500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1608300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>40500</v>
+        <v>41000</v>
       </c>
       <c r="E22" s="3">
-        <v>35900</v>
+        <v>38300</v>
       </c>
       <c r="F22" s="3">
+        <v>34000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>32300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>29600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>25900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>21100</v>
+      </c>
+      <c r="L22" s="3">
+        <v>20100</v>
+      </c>
+      <c r="M22" s="3">
+        <v>21100</v>
+      </c>
+      <c r="N22" s="3">
+        <v>20900</v>
+      </c>
+      <c r="O22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="P22" s="3">
+        <v>18500</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>19200</v>
+      </c>
+      <c r="R22" s="3">
+        <v>23900</v>
+      </c>
+      <c r="S22" s="3">
+        <v>31800</v>
+      </c>
+      <c r="T22" s="3">
+        <v>32800</v>
+      </c>
+      <c r="U22" s="3">
+        <v>57400</v>
+      </c>
+      <c r="V22" s="3">
+        <v>59900</v>
+      </c>
+      <c r="W22" s="3">
+        <v>66700</v>
+      </c>
+      <c r="X22" s="3">
+        <v>59900</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>24600</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>27700</v>
+      </c>
+      <c r="AA22" s="3">
         <v>34100</v>
       </c>
-      <c r="G22" s="3">
-        <v>31200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>27300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>26400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>21100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>20100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>21100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>19000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>18500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>19200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>23900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>31800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>32800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>57400</v>
-      </c>
-      <c r="U22" s="3">
-        <v>59900</v>
-      </c>
-      <c r="V22" s="3">
-        <v>66700</v>
-      </c>
-      <c r="W22" s="3">
-        <v>59900</v>
-      </c>
-      <c r="X22" s="3">
-        <v>24600</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>27700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>34100</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>31600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>38200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>28500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>17900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>587000</v>
+        <v>766700</v>
       </c>
       <c r="E23" s="3">
-        <v>758800</v>
+        <v>555600</v>
       </c>
       <c r="F23" s="3">
-        <v>793600</v>
+        <v>718300</v>
       </c>
       <c r="G23" s="3">
-        <v>854200</v>
+        <v>751200</v>
       </c>
       <c r="H23" s="3">
-        <v>803100</v>
+        <v>808500</v>
       </c>
       <c r="I23" s="3">
-        <v>836700</v>
+        <v>760200</v>
       </c>
       <c r="J23" s="3">
+        <v>792000</v>
+      </c>
+      <c r="K23" s="3">
         <v>586800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>618200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>773800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>715000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>683500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>596000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>278300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>90600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-467600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>287500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>659500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1153400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>546500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>749100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1142600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1077300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>890600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>843500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>927100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>885100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>801000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>169500</v>
+        <v>201000</v>
       </c>
       <c r="E24" s="3">
-        <v>187800</v>
+        <v>160400</v>
       </c>
       <c r="F24" s="3">
-        <v>158100</v>
+        <v>177800</v>
       </c>
       <c r="G24" s="3">
-        <v>234000</v>
+        <v>149600</v>
       </c>
       <c r="H24" s="3">
-        <v>202000</v>
+        <v>221500</v>
       </c>
       <c r="I24" s="3">
-        <v>152800</v>
+        <v>191200</v>
       </c>
       <c r="J24" s="3">
+        <v>144600</v>
+      </c>
+      <c r="K24" s="3">
         <v>224100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>176800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-25800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>178100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>172500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>130600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>123500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>154300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-54500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>117800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>184000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>311900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>138400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>192000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>447300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>269000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>226900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>242800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>331900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>307100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>212300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>255800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>298900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2313,198 +2361,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>417500</v>
+        <v>565700</v>
       </c>
       <c r="E26" s="3">
-        <v>571000</v>
+        <v>395200</v>
       </c>
       <c r="F26" s="3">
-        <v>635600</v>
+        <v>540500</v>
       </c>
       <c r="G26" s="3">
+        <v>601600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>587000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>569000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>647400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>362700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>441400</v>
+      </c>
+      <c r="M26" s="3">
+        <v>799600</v>
+      </c>
+      <c r="N26" s="3">
+        <v>536900</v>
+      </c>
+      <c r="O26" s="3">
+        <v>511000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>465400</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>154800</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-63700</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-413100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>169800</v>
+      </c>
+      <c r="U26" s="3">
+        <v>475500</v>
+      </c>
+      <c r="V26" s="3">
+        <v>841500</v>
+      </c>
+      <c r="W26" s="3">
+        <v>408100</v>
+      </c>
+      <c r="X26" s="3">
+        <v>557100</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>695400</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>808300</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>663700</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>600600</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>840100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>620100</v>
       </c>
-      <c r="H26" s="3">
-        <v>601100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>684000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>362700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>441400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>799600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>536900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>511000</v>
-      </c>
-      <c r="O26" s="3">
-        <v>465400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>154800</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-63700</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-413100</v>
-      </c>
-      <c r="S26" s="3">
-        <v>169800</v>
-      </c>
-      <c r="T26" s="3">
-        <v>475500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>841500</v>
-      </c>
-      <c r="V26" s="3">
-        <v>408100</v>
-      </c>
-      <c r="W26" s="3">
-        <v>557100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>695400</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>808300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>663700</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>600600</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>840100</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>620100</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>672800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>545200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>755300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>412900</v>
+        <v>552600</v>
       </c>
       <c r="E27" s="3">
-        <v>555200</v>
+        <v>390900</v>
       </c>
       <c r="F27" s="3">
-        <v>624400</v>
+        <v>525500</v>
       </c>
       <c r="G27" s="3">
-        <v>611000</v>
+        <v>591000</v>
       </c>
       <c r="H27" s="3">
-        <v>594800</v>
+        <v>578400</v>
       </c>
       <c r="I27" s="3">
-        <v>671300</v>
+        <v>563000</v>
       </c>
       <c r="J27" s="3">
+        <v>635400</v>
+      </c>
+      <c r="K27" s="3">
         <v>351700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>434400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>789800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>527900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>448400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>148300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-76400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>147700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>469700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>825800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>393100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>536100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>681400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>788200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>647300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>576300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>818200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>596000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>656300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>525400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>731700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2598,67 +2655,70 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>22300</v>
+        <v>-100</v>
       </c>
       <c r="E29" s="3">
-        <v>11600</v>
+        <v>21100</v>
       </c>
       <c r="F29" s="3">
-        <v>-3300</v>
+        <v>11000</v>
       </c>
       <c r="G29" s="3">
-        <v>-1100</v>
+        <v>-3200</v>
       </c>
       <c r="H29" s="3">
-        <v>157100</v>
+        <v>-1000</v>
       </c>
       <c r="I29" s="3">
-        <v>-25600</v>
+        <v>148700</v>
       </c>
       <c r="J29" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-88100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-76900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-987700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-19400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-7500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1574000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-142300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>60300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>46600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>23900</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2693,8 +2753,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2788,8 +2851,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2883,198 +2949,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>86800</v>
+        <v>-56500</v>
       </c>
       <c r="E32" s="3">
-        <v>48900</v>
+        <v>82200</v>
       </c>
       <c r="F32" s="3">
-        <v>2100</v>
+        <v>46300</v>
       </c>
       <c r="G32" s="3">
-        <v>-26000</v>
+        <v>2000</v>
       </c>
       <c r="H32" s="3">
-        <v>73200</v>
+        <v>-24700</v>
       </c>
       <c r="I32" s="3">
-        <v>34900</v>
+        <v>69300</v>
       </c>
       <c r="J32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-25800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-56400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-32100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-13800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-17500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-23500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>23300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>24000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-76900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-18700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-109100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>24800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>33000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>36800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>435200</v>
+        <v>552500</v>
       </c>
       <c r="E33" s="3">
-        <v>566800</v>
+        <v>412000</v>
       </c>
       <c r="F33" s="3">
-        <v>621100</v>
+        <v>536500</v>
       </c>
       <c r="G33" s="3">
-        <v>610000</v>
+        <v>587900</v>
       </c>
       <c r="H33" s="3">
-        <v>751900</v>
+        <v>577400</v>
       </c>
       <c r="I33" s="3">
-        <v>645700</v>
+        <v>711700</v>
       </c>
       <c r="J33" s="3">
+        <v>611200</v>
+      </c>
+      <c r="K33" s="3">
         <v>263600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>357500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-197900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>508500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>493000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2022400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-354100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>171600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>469700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>825800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>393100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>536100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>681400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>788200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>647300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>576300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>818200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>596000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>656300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>525400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>731700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3168,203 +3243,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>435200</v>
+        <v>552500</v>
       </c>
       <c r="E35" s="3">
-        <v>566800</v>
+        <v>412000</v>
       </c>
       <c r="F35" s="3">
-        <v>621100</v>
+        <v>536500</v>
       </c>
       <c r="G35" s="3">
-        <v>610000</v>
+        <v>587900</v>
       </c>
       <c r="H35" s="3">
-        <v>751900</v>
+        <v>577400</v>
       </c>
       <c r="I35" s="3">
-        <v>645700</v>
+        <v>711700</v>
       </c>
       <c r="J35" s="3">
+        <v>611200</v>
+      </c>
+      <c r="K35" s="3">
         <v>263600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>357500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-197900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>508500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>493000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2022400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-354100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>171600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>469700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>825800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>393100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>536100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>681400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>788200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>647300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>576300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>818200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>596000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>656300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>525400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>731700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3398,8 +3482,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3433,863 +3518,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4883800</v>
+        <v>4224000</v>
       </c>
       <c r="E41" s="3">
-        <v>4345700</v>
+        <v>4623000</v>
       </c>
       <c r="F41" s="3">
-        <v>4108200</v>
+        <v>4113600</v>
       </c>
       <c r="G41" s="3">
-        <v>3484700</v>
+        <v>3888700</v>
       </c>
       <c r="H41" s="3">
-        <v>3497400</v>
+        <v>3298500</v>
       </c>
       <c r="I41" s="3">
-        <v>3535500</v>
+        <v>3310600</v>
       </c>
       <c r="J41" s="3">
+        <v>3346700</v>
+      </c>
+      <c r="K41" s="3">
         <v>4182100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4506600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5410400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6130200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7004500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8436200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5941300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5150000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5362800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3123800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3943900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2740700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3982700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3636300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4157200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3618500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>72700</v>
+        <v>67000</v>
       </c>
       <c r="E42" s="3">
-        <v>57800</v>
+        <v>68900</v>
       </c>
       <c r="F42" s="3">
-        <v>110500</v>
+        <v>54700</v>
       </c>
       <c r="G42" s="3">
-        <v>57700</v>
+        <v>104600</v>
       </c>
       <c r="H42" s="3">
-        <v>101800</v>
+        <v>54700</v>
       </c>
       <c r="I42" s="3">
-        <v>154400</v>
+        <v>96400</v>
       </c>
       <c r="J42" s="3">
+        <v>146200</v>
+      </c>
+      <c r="K42" s="3">
         <v>63000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>65700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>80900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>54100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>51600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>45100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>53300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>51500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>86200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>155300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1369700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1356600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1323100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1240800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1452400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6418500</v>
+        <v>6259700</v>
       </c>
       <c r="E43" s="3">
-        <v>6990300</v>
+        <v>6075700</v>
       </c>
       <c r="F43" s="3">
-        <v>6760300</v>
+        <v>6616900</v>
       </c>
       <c r="G43" s="3">
-        <v>6338400</v>
+        <v>6399200</v>
       </c>
       <c r="H43" s="3">
-        <v>6380100</v>
+        <v>5999800</v>
       </c>
       <c r="I43" s="3">
-        <v>6586200</v>
+        <v>6039400</v>
       </c>
       <c r="J43" s="3">
+        <v>6234400</v>
+      </c>
+      <c r="K43" s="3">
         <v>5941600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5292500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5094900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5021400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4848000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4560700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4894700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5247200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5166800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5957200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>11999600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5330100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5120200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5535200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5472300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5235300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5854200</v>
+        <v>6013600</v>
       </c>
       <c r="E44" s="3">
-        <v>6569000</v>
+        <v>5541500</v>
       </c>
       <c r="F44" s="3">
-        <v>6659700</v>
+        <v>6218100</v>
       </c>
       <c r="G44" s="3">
-        <v>6217600</v>
+        <v>6303900</v>
       </c>
       <c r="H44" s="3">
-        <v>5967000</v>
+        <v>5885500</v>
       </c>
       <c r="I44" s="3">
-        <v>6356000</v>
+        <v>5648200</v>
       </c>
       <c r="J44" s="3">
+        <v>6016500</v>
+      </c>
+      <c r="K44" s="3">
         <v>5727200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4807600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4329100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4487800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4166700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3725300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3600800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4021000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5073500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5496700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11174200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5646400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5756300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6145500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5826700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6012000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>951400</v>
+        <v>945700</v>
       </c>
       <c r="E45" s="3">
-        <v>938800</v>
+        <v>900600</v>
       </c>
       <c r="F45" s="3">
-        <v>932900</v>
+        <v>888600</v>
       </c>
       <c r="G45" s="3">
-        <v>922300</v>
+        <v>883100</v>
       </c>
       <c r="H45" s="3">
-        <v>988900</v>
+        <v>873000</v>
       </c>
       <c r="I45" s="3">
-        <v>1088200</v>
+        <v>936100</v>
       </c>
       <c r="J45" s="3">
+        <v>1030100</v>
+      </c>
+      <c r="K45" s="3">
         <v>1232300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>911400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>836800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>635600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>649000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>587400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>569600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>679500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>648300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>643800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>780500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1290500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1233600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1217000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1145000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1780200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>18180700</v>
+        <v>17510100</v>
       </c>
       <c r="E46" s="3">
-        <v>18901600</v>
+        <v>17209600</v>
       </c>
       <c r="F46" s="3">
-        <v>18571500</v>
+        <v>17892000</v>
       </c>
       <c r="G46" s="3">
-        <v>17020600</v>
+        <v>17579500</v>
       </c>
       <c r="H46" s="3">
-        <v>16935300</v>
+        <v>16111500</v>
       </c>
       <c r="I46" s="3">
-        <v>17720500</v>
+        <v>16030700</v>
       </c>
       <c r="J46" s="3">
+        <v>16774000</v>
+      </c>
+      <c r="K46" s="3">
         <v>17146200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15583800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15752000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16329200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16719800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17354700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15059700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15149100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16337500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15376800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17476700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16364300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17415900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17774800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18053400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18184000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1161900</v>
+        <v>1272100</v>
       </c>
       <c r="E47" s="3">
-        <v>1117500</v>
+        <v>1099900</v>
       </c>
       <c r="F47" s="3">
-        <v>1039500</v>
+        <v>1057800</v>
       </c>
       <c r="G47" s="3">
-        <v>1016000</v>
+        <v>984000</v>
       </c>
       <c r="H47" s="3">
-        <v>966500</v>
+        <v>961800</v>
       </c>
       <c r="I47" s="3">
-        <v>1047400</v>
+        <v>914900</v>
       </c>
       <c r="J47" s="3">
+        <v>991400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1107900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1065600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1137000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1145100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1145500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1050000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1009800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1054200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1276800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1505300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2990000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1752500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1842600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2137000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2062100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2715400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13868500</v>
+        <v>13543900</v>
       </c>
       <c r="E48" s="3">
-        <v>13613400</v>
+        <v>13127700</v>
       </c>
       <c r="F48" s="3">
-        <v>13425600</v>
+        <v>12886300</v>
       </c>
       <c r="G48" s="3">
-        <v>12541200</v>
+        <v>12708500</v>
       </c>
       <c r="H48" s="3">
-        <v>12522500</v>
+        <v>11871400</v>
       </c>
       <c r="I48" s="3">
-        <v>12613400</v>
+        <v>11853700</v>
       </c>
       <c r="J48" s="3">
+        <v>11939700</v>
+      </c>
+      <c r="K48" s="3">
         <v>12426800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11674800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11829900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12035900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12457000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12007200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12331000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13384700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15078000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15667800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31118800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13721000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13711500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14610900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13861400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13471900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2364700</v>
+        <v>2373600</v>
       </c>
       <c r="E49" s="3">
-        <v>2374600</v>
+        <v>2238400</v>
       </c>
       <c r="F49" s="3">
-        <v>2218000</v>
+        <v>2247700</v>
       </c>
       <c r="G49" s="3">
-        <v>2056400</v>
+        <v>2099500</v>
       </c>
       <c r="H49" s="3">
-        <v>1997200</v>
+        <v>1946500</v>
       </c>
       <c r="I49" s="3">
-        <v>2058200</v>
+        <v>1890600</v>
       </c>
       <c r="J49" s="3">
+        <v>1948300</v>
+      </c>
+      <c r="K49" s="3">
         <v>1972300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1826000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1787000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1807800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1487700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1428300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1576900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1642100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1787900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1829400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3799400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1743200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1768700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>861500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>957700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>954200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>903400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>891800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>949500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>992600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>988400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>656000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>657700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4383,8 +4496,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4478,103 +4594,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1007600</v>
+        <v>973600</v>
       </c>
       <c r="E52" s="3">
-        <v>1135900</v>
+        <v>953800</v>
       </c>
       <c r="F52" s="3">
-        <v>1083000</v>
+        <v>1075200</v>
       </c>
       <c r="G52" s="3">
-        <v>1031700</v>
+        <v>1025200</v>
       </c>
       <c r="H52" s="3">
-        <v>1023700</v>
+        <v>976600</v>
       </c>
       <c r="I52" s="3">
-        <v>1146100</v>
+        <v>969000</v>
       </c>
       <c r="J52" s="3">
+        <v>1084900</v>
+      </c>
+      <c r="K52" s="3">
         <v>1110900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>994800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>923600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>785600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>797700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>746000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>730400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>798900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>893400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>901800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1805500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1353500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1388500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1458400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1317400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1118100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>998600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>934800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>965000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4668,103 +4790,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36583500</v>
+        <v>35673300</v>
       </c>
       <c r="E54" s="3">
-        <v>37142900</v>
+        <v>34629400</v>
       </c>
       <c r="F54" s="3">
-        <v>36337600</v>
+        <v>35159000</v>
       </c>
       <c r="G54" s="3">
-        <v>33665900</v>
+        <v>34396700</v>
       </c>
       <c r="H54" s="3">
-        <v>33445200</v>
+        <v>31867700</v>
       </c>
       <c r="I54" s="3">
-        <v>34585600</v>
+        <v>31658900</v>
       </c>
       <c r="J54" s="3">
+        <v>32738300</v>
+      </c>
+      <c r="K54" s="3">
         <v>33764200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31145100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31429500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32103700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32607800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32586200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30707800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32029000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35373500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35281000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>38963600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34934500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>36127200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>36842700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36252100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36443600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4798,8 +4926,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4833,578 +4962,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4038900</v>
+        <v>3578200</v>
       </c>
       <c r="E57" s="3">
-        <v>3604300</v>
+        <v>3823200</v>
       </c>
       <c r="F57" s="3">
-        <v>3560700</v>
+        <v>3411800</v>
       </c>
       <c r="G57" s="3">
-        <v>3462900</v>
+        <v>3370500</v>
       </c>
       <c r="H57" s="3">
-        <v>4094500</v>
+        <v>3277900</v>
       </c>
       <c r="I57" s="3">
-        <v>3832000</v>
+        <v>3875800</v>
       </c>
       <c r="J57" s="3">
+        <v>3627300</v>
+      </c>
+      <c r="K57" s="3">
         <v>3655800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3255900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3551900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3032400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3076400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2733400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3079600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2599700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2589600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3128200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5968100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1835100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2026300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2185100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2208700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2243400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2152600</v>
+        <v>1925800</v>
       </c>
       <c r="E58" s="3">
-        <v>2283000</v>
+        <v>2037700</v>
       </c>
       <c r="F58" s="3">
-        <v>2265400</v>
+        <v>2161000</v>
       </c>
       <c r="G58" s="3">
-        <v>1467700</v>
+        <v>2144400</v>
       </c>
       <c r="H58" s="3">
-        <v>1831700</v>
+        <v>1389400</v>
       </c>
       <c r="I58" s="3">
-        <v>1203900</v>
+        <v>1733900</v>
       </c>
       <c r="J58" s="3">
+        <v>1139600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1039500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1302700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1407200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1552700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1560400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2710100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2550400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2969700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3632300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1617000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2949000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1745500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2089300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2235600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2774400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2216500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2333300</v>
+        <v>2326100</v>
       </c>
       <c r="E59" s="3">
-        <v>2835500</v>
+        <v>2208700</v>
       </c>
       <c r="F59" s="3">
-        <v>2571500</v>
+        <v>2684100</v>
       </c>
       <c r="G59" s="3">
-        <v>2359800</v>
+        <v>2434200</v>
       </c>
       <c r="H59" s="3">
-        <v>2119100</v>
+        <v>2233700</v>
       </c>
       <c r="I59" s="3">
-        <v>2675800</v>
+        <v>2005900</v>
       </c>
       <c r="J59" s="3">
+        <v>2532900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2690700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2342100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2071700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2121400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2131300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2479300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2006000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2082500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1936300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2027200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6356000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3969500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4052700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4241900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4382200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3976300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8524800</v>
+        <v>7830100</v>
       </c>
       <c r="E60" s="3">
-        <v>8722900</v>
+        <v>8069500</v>
       </c>
       <c r="F60" s="3">
-        <v>8397600</v>
+        <v>8257000</v>
       </c>
       <c r="G60" s="3">
-        <v>7290400</v>
+        <v>7949100</v>
       </c>
       <c r="H60" s="3">
-        <v>7318300</v>
+        <v>6901000</v>
       </c>
       <c r="I60" s="3">
-        <v>7711700</v>
+        <v>6927400</v>
       </c>
       <c r="J60" s="3">
+        <v>7299800</v>
+      </c>
+      <c r="K60" s="3">
         <v>7386100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6900800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7030800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6706400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6768200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7922700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7636000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7651900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8158200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6772400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8156500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7550100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8168300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8662700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8374400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8436100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3442600</v>
+        <v>3352700</v>
       </c>
       <c r="E61" s="3">
-        <v>3468300</v>
+        <v>3258800</v>
       </c>
       <c r="F61" s="3">
-        <v>3431100</v>
+        <v>3283100</v>
       </c>
       <c r="G61" s="3">
-        <v>3939700</v>
+        <v>3247800</v>
       </c>
       <c r="H61" s="3">
-        <v>4066000</v>
+        <v>3729300</v>
       </c>
       <c r="I61" s="3">
-        <v>4181100</v>
+        <v>3848800</v>
       </c>
       <c r="J61" s="3">
+        <v>3957800</v>
+      </c>
+      <c r="K61" s="3">
         <v>4174500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4008900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4165300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4321900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4445000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4555600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4825000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5152000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5627300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5787000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5978000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4133900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4137000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2442500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2031700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1989500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1663600</v>
+        <v>1597600</v>
       </c>
       <c r="E62" s="3">
-        <v>1717300</v>
+        <v>1574800</v>
       </c>
       <c r="F62" s="3">
-        <v>1771000</v>
+        <v>1625600</v>
       </c>
       <c r="G62" s="3">
-        <v>1711600</v>
+        <v>1676400</v>
       </c>
       <c r="H62" s="3">
-        <v>1756700</v>
+        <v>1620200</v>
       </c>
       <c r="I62" s="3">
-        <v>1852700</v>
+        <v>1662800</v>
       </c>
       <c r="J62" s="3">
+        <v>1753800</v>
+      </c>
+      <c r="K62" s="3">
         <v>1952700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1847700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1853700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2048700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2108100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2041900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2155300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2277400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2570900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2755700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4777500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2594100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2650800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2918600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2848700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3083300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5498,8 +5646,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5593,8 +5744,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5688,103 +5842,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13980300</v>
+        <v>13116600</v>
       </c>
       <c r="E66" s="3">
-        <v>14255000</v>
+        <v>13233500</v>
       </c>
       <c r="F66" s="3">
-        <v>13936200</v>
+        <v>13493600</v>
       </c>
       <c r="G66" s="3">
-        <v>13273500</v>
+        <v>13191800</v>
       </c>
       <c r="H66" s="3">
-        <v>13455500</v>
+        <v>12564600</v>
       </c>
       <c r="I66" s="3">
-        <v>14072700</v>
+        <v>12736800</v>
       </c>
       <c r="J66" s="3">
+        <v>13321000</v>
+      </c>
+      <c r="K66" s="3">
         <v>13840300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13072000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13362200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13379600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13639700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14844900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14948600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15423000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16749200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15745300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17560800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14744100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15439800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14541300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13766400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13999700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5818,8 +5978,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5913,8 +6074,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6008,8 +6172,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6103,8 +6270,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6198,103 +6368,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18273600</v>
+        <v>17430000</v>
       </c>
       <c r="E72" s="3">
-        <v>17855100</v>
+        <v>17312300</v>
       </c>
       <c r="F72" s="3">
-        <v>17750100</v>
+        <v>16901400</v>
       </c>
       <c r="G72" s="3">
-        <v>17071800</v>
+        <v>16802000</v>
       </c>
       <c r="H72" s="3">
-        <v>16857500</v>
+        <v>16159900</v>
       </c>
       <c r="I72" s="3">
-        <v>16060100</v>
+        <v>15955900</v>
       </c>
       <c r="J72" s="3">
+        <v>15202300</v>
+      </c>
+      <c r="K72" s="3">
         <v>15804000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15308800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15874300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16784800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17007300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15925300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14682900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15438900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17177700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18111900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>44028300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>22532700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22193000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22722500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22336800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>21311700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6388,8 +6564,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6483,8 +6662,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6578,103 +6760,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22603200</v>
+        <v>22556600</v>
       </c>
       <c r="E76" s="3">
-        <v>22887900</v>
+        <v>21395900</v>
       </c>
       <c r="F76" s="3">
-        <v>22401400</v>
+        <v>21665400</v>
       </c>
       <c r="G76" s="3">
-        <v>20392400</v>
+        <v>21204900</v>
       </c>
       <c r="H76" s="3">
-        <v>19989700</v>
+        <v>19303200</v>
       </c>
       <c r="I76" s="3">
-        <v>20512900</v>
+        <v>18922000</v>
       </c>
       <c r="J76" s="3">
+        <v>19417300</v>
+      </c>
+      <c r="K76" s="3">
         <v>19923900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18073100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18067300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18724100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18968100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17741300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15759200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16606100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18624400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19535800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>21402800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>20190400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20687400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>22301400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22485700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22443800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6768,203 +6956,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>435200</v>
+        <v>552500</v>
       </c>
       <c r="E81" s="3">
-        <v>566800</v>
+        <v>412000</v>
       </c>
       <c r="F81" s="3">
-        <v>621100</v>
+        <v>536500</v>
       </c>
       <c r="G81" s="3">
-        <v>610000</v>
+        <v>587900</v>
       </c>
       <c r="H81" s="3">
-        <v>751900</v>
+        <v>577400</v>
       </c>
       <c r="I81" s="3">
-        <v>645700</v>
+        <v>711700</v>
       </c>
       <c r="J81" s="3">
+        <v>611200</v>
+      </c>
+      <c r="K81" s="3">
         <v>263600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>357500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-197900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>508500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>493000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2022400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-354100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>171600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>469700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>825800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>393100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>536100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>681400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>788200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>647300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>576300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>818200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>596000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>656300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>525400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>731700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6998,103 +7195,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>527600</v>
+        <v>542700</v>
       </c>
       <c r="E83" s="3">
-        <v>544900</v>
+        <v>499400</v>
       </c>
       <c r="F83" s="3">
-        <v>501700</v>
+        <v>515800</v>
       </c>
       <c r="G83" s="3">
-        <v>486900</v>
+        <v>474900</v>
       </c>
       <c r="H83" s="3">
-        <v>489100</v>
+        <v>460900</v>
       </c>
       <c r="I83" s="3">
-        <v>509300</v>
+        <v>462900</v>
       </c>
       <c r="J83" s="3">
+        <v>482100</v>
+      </c>
+      <c r="K83" s="3">
         <v>460700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>435800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>444600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>461700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>442800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>435700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>498300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>516900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>565200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>589000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>627500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>642000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>648500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>644800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>479300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>503300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>444400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>465300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>489800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>473600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>440100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>440600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>428800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7188,8 +7389,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7283,8 +7487,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7378,8 +7585,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7473,8 +7683,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7568,79 +7781,82 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1595900</v>
+        <v>818900</v>
       </c>
       <c r="E89" s="3">
-        <v>1272700</v>
+        <v>1510600</v>
       </c>
       <c r="F89" s="3">
-        <v>783700</v>
+        <v>1204700</v>
       </c>
       <c r="G89" s="3">
-        <v>806900</v>
+        <v>741900</v>
       </c>
       <c r="H89" s="3">
-        <v>973800</v>
+        <v>763800</v>
       </c>
       <c r="I89" s="3">
-        <v>965200</v>
+        <v>921800</v>
       </c>
       <c r="J89" s="3">
+        <v>913600</v>
+      </c>
+      <c r="K89" s="3">
         <v>138100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>399400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>416000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>180000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>644200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1553400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1323100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>691700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>564600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1895100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>694900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>888100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1172900</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -7663,8 +7879,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7698,79 +7917,80 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103495000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103013000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-82364000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-65299000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-92261000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-196600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-349000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-376900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-364000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-325900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-566700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-626200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-678600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-523100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-680800</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7793,8 +8013,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7888,8 +8111,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7983,79 +8209,82 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-661000</v>
+        <v>-623100</v>
       </c>
       <c r="E94" s="3">
-        <v>-479300</v>
+        <v>-625700</v>
       </c>
       <c r="F94" s="3">
-        <v>-326100</v>
+        <v>-453700</v>
       </c>
       <c r="G94" s="3">
-        <v>-540200</v>
+        <v>-308600</v>
       </c>
       <c r="H94" s="3">
-        <v>-408900</v>
+        <v>-511400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1093700</v>
+        <v>-387100</v>
       </c>
       <c r="J94" s="3">
+        <v>-1035300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-276600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-491600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-352700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-598100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-175200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>2055000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-292400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-382600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-522200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-44100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-358100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-694000</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -8078,8 +8307,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8113,74 +8345,75 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-431700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-600</v>
       </c>
-      <c r="E96" s="3">
-        <v>-460800</v>
-      </c>
       <c r="F96" s="3">
-        <v>-5300</v>
+        <v>-436200</v>
       </c>
       <c r="G96" s="3">
-        <v>-409800</v>
+        <v>-5000</v>
       </c>
       <c r="H96" s="3">
+        <v>-387900</v>
+      </c>
+      <c r="I96" s="3">
         <v>-600</v>
       </c>
-      <c r="I96" s="3">
-        <v>-398200</v>
-      </c>
       <c r="J96" s="3">
+        <v>-376900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-4100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-393400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-430900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-6100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-293600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-273700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-5900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-490000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-528100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-572200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8208,8 +8441,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8303,8 +8539,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8398,8 +8637,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8493,79 +8735,82 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-244200</v>
+        <v>-729900</v>
       </c>
       <c r="E100" s="3">
-        <v>-577500</v>
+        <v>-231200</v>
       </c>
       <c r="F100" s="3">
-        <v>-125900</v>
+        <v>-546600</v>
       </c>
       <c r="G100" s="3">
-        <v>-290200</v>
+        <v>-119200</v>
       </c>
       <c r="H100" s="3">
-        <v>-273800</v>
+        <v>-274700</v>
       </c>
       <c r="I100" s="3">
-        <v>-629300</v>
+        <v>-259100</v>
       </c>
       <c r="J100" s="3">
+        <v>-595700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-645100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-892400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-210100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-526400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-326200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-385600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-724900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1947000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-568400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-230900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1278300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1194800</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8588,79 +8833,82 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-152500</v>
+        <v>135000</v>
       </c>
       <c r="E101" s="3">
-        <v>21600</v>
+        <v>-144300</v>
       </c>
       <c r="F101" s="3">
-        <v>291800</v>
+        <v>20400</v>
       </c>
       <c r="G101" s="3">
-        <v>10800</v>
+        <v>276200</v>
       </c>
       <c r="H101" s="3">
-        <v>-329200</v>
+        <v>10200</v>
       </c>
       <c r="I101" s="3">
-        <v>111300</v>
+        <v>-311700</v>
       </c>
       <c r="J101" s="3">
+        <v>105400</v>
+      </c>
+      <c r="K101" s="3">
         <v>391200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>262000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>110000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-32400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-57400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>316500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>28100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-53300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>82200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-164300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>102700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-89500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-56300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>67800</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8683,79 +8931,82 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>539200</v>
+        <v>-398900</v>
       </c>
       <c r="E102" s="3">
-        <v>237500</v>
+        <v>509400</v>
       </c>
       <c r="F102" s="3">
-        <v>623500</v>
+        <v>224800</v>
       </c>
       <c r="G102" s="3">
-        <v>-12800</v>
+        <v>590200</v>
       </c>
       <c r="H102" s="3">
-        <v>-38100</v>
+        <v>-12100</v>
       </c>
       <c r="I102" s="3">
-        <v>-646500</v>
+        <v>-36100</v>
       </c>
       <c r="J102" s="3">
+        <v>-612000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-392400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-722700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-430700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-740900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2689400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1095400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>252500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2338300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-690300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1329100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>564100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-648100</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -8776,6 +9027,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -656,435 +656,448 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6789100</v>
+        <v>7899900</v>
       </c>
       <c r="E8" s="3">
-        <v>7117900</v>
+        <v>7555200</v>
       </c>
       <c r="F8" s="3">
-        <v>6995300</v>
+        <v>7921200</v>
       </c>
       <c r="G8" s="3">
-        <v>6751100</v>
+        <v>7784700</v>
       </c>
       <c r="H8" s="3">
-        <v>6657800</v>
+        <v>7513000</v>
       </c>
       <c r="I8" s="3">
-        <v>7229500</v>
+        <v>7409100</v>
       </c>
       <c r="J8" s="3">
+        <v>8045300</v>
+      </c>
+      <c r="K8" s="3">
         <v>6957900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6708500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5916300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5800300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5820400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5756600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5156000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5065500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5774300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4752500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6217800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8048800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8122100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8168200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8151300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9212700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4053200</v>
+        <v>4858700</v>
       </c>
       <c r="E9" s="3">
-        <v>4403500</v>
+        <v>4510600</v>
       </c>
       <c r="F9" s="3">
-        <v>4330500</v>
+        <v>4900500</v>
       </c>
       <c r="G9" s="3">
-        <v>4142800</v>
+        <v>4819200</v>
       </c>
       <c r="H9" s="3">
-        <v>4101800</v>
+        <v>4610300</v>
       </c>
       <c r="I9" s="3">
-        <v>4424600</v>
+        <v>4564700</v>
       </c>
       <c r="J9" s="3">
+        <v>4924000</v>
+      </c>
+      <c r="K9" s="3">
         <v>4264200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4114800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3615000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3318300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3396300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3395600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3069100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2818700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3709400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3230500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3894700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5024300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4951200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5149100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5094700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5770100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2735900</v>
+        <v>3041200</v>
       </c>
       <c r="E10" s="3">
-        <v>2714400</v>
+        <v>3044600</v>
       </c>
       <c r="F10" s="3">
-        <v>2664700</v>
+        <v>3020700</v>
       </c>
       <c r="G10" s="3">
-        <v>2608300</v>
+        <v>2965500</v>
       </c>
       <c r="H10" s="3">
-        <v>2556000</v>
+        <v>2902700</v>
       </c>
       <c r="I10" s="3">
-        <v>2804800</v>
+        <v>2844400</v>
       </c>
       <c r="J10" s="3">
+        <v>3121400</v>
+      </c>
+      <c r="K10" s="3">
         <v>2693700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2593700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2301300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2482000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2424100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2361000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2086900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2246800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2064900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1522000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2323200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3024500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3170900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3019100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3056600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3442500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1119,106 +1132,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>203500</v>
+        <v>216500</v>
       </c>
       <c r="E12" s="3">
-        <v>207700</v>
+        <v>226500</v>
       </c>
       <c r="F12" s="3">
-        <v>192500</v>
+        <v>231200</v>
       </c>
       <c r="G12" s="3">
-        <v>188700</v>
+        <v>214300</v>
       </c>
       <c r="H12" s="3">
-        <v>189400</v>
+        <v>210000</v>
       </c>
       <c r="I12" s="3">
-        <v>194300</v>
+        <v>210700</v>
       </c>
       <c r="J12" s="3">
+        <v>216200</v>
+      </c>
+      <c r="K12" s="3">
         <v>179000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>184100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>175100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>157300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>163000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>168300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>159200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>126200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>173000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>186300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>229200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>252500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>235800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>252200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>243000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>269400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>238200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>228100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>220800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>241900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>216700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>232200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>207300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>215600</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1315,204 +1332,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>22600</v>
+        <v>34300</v>
       </c>
       <c r="E14" s="3">
-        <v>98500</v>
+        <v>25100</v>
       </c>
       <c r="F14" s="3">
-        <v>-5700</v>
+        <v>109700</v>
       </c>
       <c r="G14" s="3">
-        <v>-28500</v>
+        <v>-6400</v>
       </c>
       <c r="H14" s="3">
-        <v>8400</v>
+        <v>-31700</v>
       </c>
       <c r="I14" s="3">
-        <v>32600</v>
+        <v>9400</v>
       </c>
       <c r="J14" s="3">
+        <v>36300</v>
+      </c>
+      <c r="K14" s="3">
         <v>12700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>85700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>49900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>26900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>39800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>487000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>682000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>383400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>47500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>190200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>41600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-103500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-280400</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>99800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>9300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>58400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>39200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200200</v>
+        <v>233300</v>
       </c>
       <c r="E15" s="3">
-        <v>190800</v>
+        <v>222800</v>
       </c>
       <c r="F15" s="3">
-        <v>185800</v>
+        <v>212300</v>
       </c>
       <c r="G15" s="3">
-        <v>176100</v>
+        <v>206800</v>
       </c>
       <c r="H15" s="3">
-        <v>167200</v>
+        <v>196000</v>
       </c>
       <c r="I15" s="3">
-        <v>168800</v>
+        <v>186100</v>
       </c>
       <c r="J15" s="3">
+        <v>187900</v>
+      </c>
+      <c r="K15" s="3">
         <v>173000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>165700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>154300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>158200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>161700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>161900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>156500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>159000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>171800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>179100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>193000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>312700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>310900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>200000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>203500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>85000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>84700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>79500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>78600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>80500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>76300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>73000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>72800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>71300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1544,204 +1570,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6037800</v>
+        <v>6745000</v>
       </c>
       <c r="E17" s="3">
-        <v>6441700</v>
+        <v>6719200</v>
       </c>
       <c r="F17" s="3">
-        <v>6196700</v>
+        <v>7168700</v>
       </c>
       <c r="G17" s="3">
-        <v>5965600</v>
+        <v>6896000</v>
       </c>
       <c r="H17" s="3">
-        <v>5844300</v>
+        <v>6638800</v>
       </c>
       <c r="I17" s="3">
-        <v>6374100</v>
+        <v>6503900</v>
       </c>
       <c r="J17" s="3">
+        <v>7093500</v>
+      </c>
+      <c r="K17" s="3">
         <v>6107900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6126500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5334400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5037600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5098300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5071600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4565000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4771800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5669200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5164900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5873400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7408900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6921500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7573700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7348300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8154600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>751300</v>
+        <v>1154900</v>
       </c>
       <c r="E18" s="3">
-        <v>676200</v>
+        <v>836100</v>
       </c>
       <c r="F18" s="3">
-        <v>798600</v>
+        <v>752500</v>
       </c>
       <c r="G18" s="3">
-        <v>785500</v>
+        <v>888700</v>
       </c>
       <c r="H18" s="3">
-        <v>813500</v>
+        <v>874100</v>
       </c>
       <c r="I18" s="3">
-        <v>855400</v>
+        <v>905300</v>
       </c>
       <c r="J18" s="3">
+        <v>951900</v>
+      </c>
+      <c r="K18" s="3">
         <v>850100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>582100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>581900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>762800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>722100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>684900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>591000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>293700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>105100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-412500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>344400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>640000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1200600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>594400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>803000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1058100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>904800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>908100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>978800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>874100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>888200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>855800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1776,498 +1809,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>56500</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
-        <v>-82200</v>
+        <v>62800</v>
       </c>
       <c r="F20" s="3">
-        <v>-46300</v>
+        <v>-91500</v>
       </c>
       <c r="G20" s="3">
-        <v>-2000</v>
+        <v>-51500</v>
       </c>
       <c r="H20" s="3">
-        <v>24700</v>
+        <v>-2200</v>
       </c>
       <c r="I20" s="3">
-        <v>-69300</v>
+        <v>27400</v>
       </c>
       <c r="J20" s="3">
+        <v>-77100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-33000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>56400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>32100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>17500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-23300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-24000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>76900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>18700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>109100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>231400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>77600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>25400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>47400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1350400</v>
+        <v>1776700</v>
       </c>
       <c r="E21" s="3">
-        <v>1093400</v>
+        <v>1502800</v>
       </c>
       <c r="F21" s="3">
-        <v>1268200</v>
+        <v>1216700</v>
       </c>
       <c r="G21" s="3">
-        <v>1258400</v>
+        <v>1411300</v>
       </c>
       <c r="H21" s="3">
-        <v>1299000</v>
+        <v>1400400</v>
       </c>
       <c r="I21" s="3">
-        <v>1249000</v>
+        <v>1445600</v>
       </c>
       <c r="J21" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1299100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1068500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1074100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1239400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1197600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1145300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1050200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>795700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>631400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>129400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>909400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1339200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1831800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1238200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1442400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1646500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="E22" s="3">
-        <v>38300</v>
+        <v>45600</v>
       </c>
       <c r="F22" s="3">
-        <v>34000</v>
+        <v>42600</v>
       </c>
       <c r="G22" s="3">
-        <v>32300</v>
+        <v>37900</v>
       </c>
       <c r="H22" s="3">
-        <v>29600</v>
+        <v>35900</v>
       </c>
       <c r="I22" s="3">
-        <v>25900</v>
+        <v>32900</v>
       </c>
       <c r="J22" s="3">
+        <v>28800</v>
+      </c>
+      <c r="K22" s="3">
         <v>25000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>31800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>32800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>57400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>66700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>27700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>34100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>31600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>38200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>28500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>766700</v>
+        <v>1112500</v>
       </c>
       <c r="E23" s="3">
-        <v>555600</v>
+        <v>853300</v>
       </c>
       <c r="F23" s="3">
-        <v>718300</v>
+        <v>618300</v>
       </c>
       <c r="G23" s="3">
-        <v>751200</v>
+        <v>799400</v>
       </c>
       <c r="H23" s="3">
-        <v>808500</v>
+        <v>836000</v>
       </c>
       <c r="I23" s="3">
-        <v>760200</v>
+        <v>899800</v>
       </c>
       <c r="J23" s="3">
+        <v>846000</v>
+      </c>
+      <c r="K23" s="3">
         <v>792000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>586800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>618200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>773800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>715000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>683500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>596000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>278300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>90600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-467600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>287500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>659500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1153400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>546500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>749100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1142600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>890600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>843500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>927100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>885100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>801000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>201000</v>
+        <v>299900</v>
       </c>
       <c r="E24" s="3">
-        <v>160400</v>
+        <v>223700</v>
       </c>
       <c r="F24" s="3">
-        <v>177800</v>
+        <v>178500</v>
       </c>
       <c r="G24" s="3">
-        <v>149600</v>
+        <v>197800</v>
       </c>
       <c r="H24" s="3">
-        <v>221500</v>
+        <v>166500</v>
       </c>
       <c r="I24" s="3">
-        <v>191200</v>
+        <v>246500</v>
       </c>
       <c r="J24" s="3">
+        <v>212800</v>
+      </c>
+      <c r="K24" s="3">
         <v>144600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>224100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>176800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-25800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>178100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>172500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>130600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>123500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>154300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-54500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>117800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>184000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>311900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>138400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>192000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>447300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>269000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>226900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>242800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>331900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>307100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>212300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>255800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>298900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2364,204 +2413,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>565700</v>
+        <v>812500</v>
       </c>
       <c r="E26" s="3">
-        <v>395200</v>
+        <v>629500</v>
       </c>
       <c r="F26" s="3">
-        <v>540500</v>
+        <v>439800</v>
       </c>
       <c r="G26" s="3">
-        <v>601600</v>
+        <v>601500</v>
       </c>
       <c r="H26" s="3">
-        <v>587000</v>
+        <v>669500</v>
       </c>
       <c r="I26" s="3">
-        <v>569000</v>
+        <v>653300</v>
       </c>
       <c r="J26" s="3">
+        <v>633200</v>
+      </c>
+      <c r="K26" s="3">
         <v>647400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>362700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>441400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>799600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>536900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>511000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>465400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>154800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-63700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-413100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>169800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>475500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>841500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>408100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>557100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>695400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>808300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>663700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>600600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>840100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>620100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>672800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>545200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>755300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>552600</v>
+        <v>798800</v>
       </c>
       <c r="E27" s="3">
-        <v>390900</v>
+        <v>615000</v>
       </c>
       <c r="F27" s="3">
-        <v>525500</v>
+        <v>435000</v>
       </c>
       <c r="G27" s="3">
-        <v>591000</v>
+        <v>584800</v>
       </c>
       <c r="H27" s="3">
-        <v>578400</v>
+        <v>657700</v>
       </c>
       <c r="I27" s="3">
-        <v>563000</v>
+        <v>643700</v>
       </c>
       <c r="J27" s="3">
+        <v>626600</v>
+      </c>
+      <c r="K27" s="3">
         <v>635400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>351700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>434400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>789800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>527900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>448400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>148300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-76400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>147700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>469700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>825800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>393100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>536100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>681400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>788200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>647300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>576300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>818200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>596000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>656300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>525400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>731700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2658,70 +2716,73 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E29" s="3">
         <v>-100</v>
       </c>
-      <c r="E29" s="3">
-        <v>21100</v>
-      </c>
       <c r="F29" s="3">
-        <v>11000</v>
+        <v>23500</v>
       </c>
       <c r="G29" s="3">
-        <v>-3200</v>
+        <v>12200</v>
       </c>
       <c r="H29" s="3">
-        <v>-1000</v>
+        <v>-3500</v>
       </c>
       <c r="I29" s="3">
-        <v>148700</v>
+        <v>-1100</v>
       </c>
       <c r="J29" s="3">
+        <v>165500</v>
+      </c>
+      <c r="K29" s="3">
         <v>-24200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-88100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-76900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-987700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-19400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-7500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1574000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-142300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>60300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>46600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>23900</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2756,8 +2817,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2854,8 +2918,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2952,204 +3019,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-56500</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
-        <v>82200</v>
+        <v>-62800</v>
       </c>
       <c r="F32" s="3">
-        <v>46300</v>
+        <v>91500</v>
       </c>
       <c r="G32" s="3">
-        <v>2000</v>
+        <v>51500</v>
       </c>
       <c r="H32" s="3">
-        <v>-24700</v>
+        <v>2200</v>
       </c>
       <c r="I32" s="3">
-        <v>69300</v>
+        <v>-27400</v>
       </c>
       <c r="J32" s="3">
+        <v>77100</v>
+      </c>
+      <c r="K32" s="3">
         <v>33000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-56400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-32100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-17500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>23300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>24000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-76900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-18700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-109100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>33000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>36800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>552500</v>
+        <v>798600</v>
       </c>
       <c r="E33" s="3">
-        <v>412000</v>
+        <v>614900</v>
       </c>
       <c r="F33" s="3">
-        <v>536500</v>
+        <v>458500</v>
       </c>
       <c r="G33" s="3">
-        <v>587900</v>
+        <v>597000</v>
       </c>
       <c r="H33" s="3">
-        <v>577400</v>
+        <v>654200</v>
       </c>
       <c r="I33" s="3">
-        <v>711700</v>
+        <v>642500</v>
       </c>
       <c r="J33" s="3">
+        <v>792100</v>
+      </c>
+      <c r="K33" s="3">
         <v>611200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>263600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>357500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-197900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>508500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>493000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2022400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-354100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>171600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>469700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>825800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>393100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>536100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>681400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>788200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>647300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>576300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>818200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>596000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>656300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>525400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>731700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3246,209 +3322,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>552500</v>
+        <v>798600</v>
       </c>
       <c r="E35" s="3">
-        <v>412000</v>
+        <v>614900</v>
       </c>
       <c r="F35" s="3">
-        <v>536500</v>
+        <v>458500</v>
       </c>
       <c r="G35" s="3">
-        <v>587900</v>
+        <v>597000</v>
       </c>
       <c r="H35" s="3">
-        <v>577400</v>
+        <v>654200</v>
       </c>
       <c r="I35" s="3">
-        <v>711700</v>
+        <v>642500</v>
       </c>
       <c r="J35" s="3">
+        <v>792100</v>
+      </c>
+      <c r="K35" s="3">
         <v>611200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>263600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>357500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-197900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>508500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>493000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2022400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-354100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>171600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>469700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>825800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>393100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>536100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>681400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>788200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>647300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>576300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>818200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>596000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>656300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>525400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>731700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3483,8 +3568,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3519,890 +3605,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4224000</v>
+        <v>4608900</v>
       </c>
       <c r="E41" s="3">
-        <v>4623000</v>
+        <v>4700700</v>
       </c>
       <c r="F41" s="3">
-        <v>4113600</v>
+        <v>5144700</v>
       </c>
       <c r="G41" s="3">
-        <v>3888700</v>
+        <v>4577800</v>
       </c>
       <c r="H41" s="3">
-        <v>3298500</v>
+        <v>4327600</v>
       </c>
       <c r="I41" s="3">
-        <v>3310600</v>
+        <v>3670800</v>
       </c>
       <c r="J41" s="3">
+        <v>3684200</v>
+      </c>
+      <c r="K41" s="3">
         <v>3346700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4182100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4506600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5410400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6130200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7004500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8436200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5941300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5150000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5362800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3123800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3943900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2740700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3982700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3636300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4157200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>67000</v>
+        <v>66500</v>
       </c>
       <c r="E42" s="3">
-        <v>68900</v>
+        <v>74600</v>
       </c>
       <c r="F42" s="3">
-        <v>54700</v>
+        <v>76600</v>
       </c>
       <c r="G42" s="3">
-        <v>104600</v>
+        <v>60900</v>
       </c>
       <c r="H42" s="3">
-        <v>54700</v>
+        <v>116400</v>
       </c>
       <c r="I42" s="3">
-        <v>96400</v>
+        <v>60800</v>
       </c>
       <c r="J42" s="3">
+        <v>107300</v>
+      </c>
+      <c r="K42" s="3">
         <v>146200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>63000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>65700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>80900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>54100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>51600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>45100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>53300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>51500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>86200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>155300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1369700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1356600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1323100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1240800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1452400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6259700</v>
+        <v>7538500</v>
       </c>
       <c r="E43" s="3">
-        <v>6075700</v>
+        <v>6966100</v>
       </c>
       <c r="F43" s="3">
-        <v>6616900</v>
+        <v>6761400</v>
       </c>
       <c r="G43" s="3">
-        <v>6399200</v>
+        <v>7363700</v>
       </c>
       <c r="H43" s="3">
-        <v>5999800</v>
+        <v>7121300</v>
       </c>
       <c r="I43" s="3">
-        <v>6039400</v>
+        <v>6676900</v>
       </c>
       <c r="J43" s="3">
+        <v>6720900</v>
+      </c>
+      <c r="K43" s="3">
         <v>6234400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5941600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5292500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5094900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5021400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4848000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4560700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4894700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5247200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5166800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5957200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11999600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5330100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5120200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5535200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5472300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6013600</v>
+        <v>7184900</v>
       </c>
       <c r="E44" s="3">
-        <v>5541500</v>
+        <v>6692300</v>
       </c>
       <c r="F44" s="3">
-        <v>6218100</v>
+        <v>6166900</v>
       </c>
       <c r="G44" s="3">
-        <v>6303900</v>
+        <v>6919900</v>
       </c>
       <c r="H44" s="3">
-        <v>5885500</v>
+        <v>7015400</v>
       </c>
       <c r="I44" s="3">
-        <v>5648200</v>
+        <v>6549700</v>
       </c>
       <c r="J44" s="3">
+        <v>6285700</v>
+      </c>
+      <c r="K44" s="3">
         <v>6016500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5727200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4807600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4329100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4487800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4166700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3725300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3600800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4021000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5073500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5496700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11174200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5646400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5756300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6145500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5826700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>945700</v>
+        <v>1201400</v>
       </c>
       <c r="E45" s="3">
-        <v>900600</v>
+        <v>1052500</v>
       </c>
       <c r="F45" s="3">
-        <v>888600</v>
+        <v>1002200</v>
       </c>
       <c r="G45" s="3">
-        <v>883100</v>
+        <v>988900</v>
       </c>
       <c r="H45" s="3">
-        <v>873000</v>
+        <v>982700</v>
       </c>
       <c r="I45" s="3">
-        <v>936100</v>
+        <v>971500</v>
       </c>
       <c r="J45" s="3">
+        <v>1041700</v>
+      </c>
+      <c r="K45" s="3">
         <v>1030100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1232300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>911400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>836800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>635600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>649000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>587400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>569600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>679500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>648300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>643800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>780500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1290500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1233600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1217000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1145000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17510100</v>
+        <v>20600200</v>
       </c>
       <c r="E46" s="3">
-        <v>17209600</v>
+        <v>19486200</v>
       </c>
       <c r="F46" s="3">
-        <v>17892000</v>
+        <v>19151800</v>
       </c>
       <c r="G46" s="3">
-        <v>17579500</v>
+        <v>19911100</v>
       </c>
       <c r="H46" s="3">
-        <v>16111500</v>
+        <v>19563400</v>
       </c>
       <c r="I46" s="3">
-        <v>16030700</v>
+        <v>17929700</v>
       </c>
       <c r="J46" s="3">
+        <v>17839800</v>
+      </c>
+      <c r="K46" s="3">
         <v>16774000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17146200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15583800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15752000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16329200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16719800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17354700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15059700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15149100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16337500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15376800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17476700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16364300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17415900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17774800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18053400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1272100</v>
+        <v>1399100</v>
       </c>
       <c r="E47" s="3">
-        <v>1099900</v>
+        <v>1415700</v>
       </c>
       <c r="F47" s="3">
-        <v>1057800</v>
+        <v>1224000</v>
       </c>
       <c r="G47" s="3">
-        <v>984000</v>
+        <v>1177200</v>
       </c>
       <c r="H47" s="3">
-        <v>961800</v>
+        <v>1095100</v>
       </c>
       <c r="I47" s="3">
-        <v>914900</v>
+        <v>1070300</v>
       </c>
       <c r="J47" s="3">
+        <v>1018200</v>
+      </c>
+      <c r="K47" s="3">
         <v>991400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1107900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1065600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1137000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1145100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1145500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1050000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1009800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1054200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1276800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1505300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2990000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1752500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1842600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2137000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2062100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13543900</v>
+        <v>15697600</v>
       </c>
       <c r="E48" s="3">
-        <v>13127700</v>
+        <v>15072300</v>
       </c>
       <c r="F48" s="3">
-        <v>12886300</v>
+        <v>14609300</v>
       </c>
       <c r="G48" s="3">
-        <v>12708500</v>
+        <v>14340600</v>
       </c>
       <c r="H48" s="3">
-        <v>11871400</v>
+        <v>14142700</v>
       </c>
       <c r="I48" s="3">
-        <v>11853700</v>
+        <v>13211100</v>
       </c>
       <c r="J48" s="3">
+        <v>13191400</v>
+      </c>
+      <c r="K48" s="3">
         <v>11939700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12426800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11674800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11829900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12035900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12457000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12007200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12331000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13384700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15078000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15667800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>31118800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13721000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13711500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14610900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13861400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2373600</v>
+        <v>2747700</v>
       </c>
       <c r="E49" s="3">
-        <v>2238400</v>
+        <v>2641400</v>
       </c>
       <c r="F49" s="3">
-        <v>2247700</v>
+        <v>2491000</v>
       </c>
       <c r="G49" s="3">
-        <v>2099500</v>
+        <v>2501400</v>
       </c>
       <c r="H49" s="3">
-        <v>1946500</v>
+        <v>2336500</v>
       </c>
       <c r="I49" s="3">
-        <v>1890600</v>
+        <v>2166200</v>
       </c>
       <c r="J49" s="3">
+        <v>2103900</v>
+      </c>
+      <c r="K49" s="3">
         <v>1948300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1972300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1826000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1787000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1807800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1487700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1428300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1576900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1642100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1787900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1829400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3799400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1743200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1768700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>861500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>957700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>954200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>903400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>891800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>949500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>992600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>988400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>656000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>657700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4499,8 +4613,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4597,106 +4714,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>973600</v>
+        <v>1202100</v>
       </c>
       <c r="E52" s="3">
-        <v>953800</v>
+        <v>1083500</v>
       </c>
       <c r="F52" s="3">
-        <v>1075200</v>
+        <v>1061400</v>
       </c>
       <c r="G52" s="3">
-        <v>1025200</v>
+        <v>1196600</v>
       </c>
       <c r="H52" s="3">
-        <v>976600</v>
+        <v>1140900</v>
       </c>
       <c r="I52" s="3">
-        <v>969000</v>
+        <v>1086800</v>
       </c>
       <c r="J52" s="3">
+        <v>1078400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1084900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1110900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>994800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>923600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>785600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>797700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>746000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>730400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>798900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>893400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>901800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1805500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1353500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1388500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1458400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1317400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>998600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>934800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>965000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4793,106 +4916,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35673300</v>
+        <v>41646700</v>
       </c>
       <c r="E54" s="3">
-        <v>34629400</v>
+        <v>39699100</v>
       </c>
       <c r="F54" s="3">
-        <v>35159000</v>
+        <v>38537500</v>
       </c>
       <c r="G54" s="3">
-        <v>34396700</v>
+        <v>39126800</v>
       </c>
       <c r="H54" s="3">
-        <v>31867700</v>
+        <v>38278500</v>
       </c>
       <c r="I54" s="3">
-        <v>31658900</v>
+        <v>35464100</v>
       </c>
       <c r="J54" s="3">
+        <v>35231600</v>
+      </c>
+      <c r="K54" s="3">
         <v>32738300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33764200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31145100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31429500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32103700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32607800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32586200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30707800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32029000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>35373500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35281000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38963600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34934500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>36127200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36842700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36252100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4927,8 +5056,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4963,596 +5093,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3578200</v>
+        <v>4257600</v>
       </c>
       <c r="E57" s="3">
-        <v>3823200</v>
+        <v>3982000</v>
       </c>
       <c r="F57" s="3">
-        <v>3411800</v>
+        <v>4254600</v>
       </c>
       <c r="G57" s="3">
-        <v>3370500</v>
+        <v>3796900</v>
       </c>
       <c r="H57" s="3">
-        <v>3277900</v>
+        <v>3750900</v>
       </c>
       <c r="I57" s="3">
-        <v>3875800</v>
+        <v>3647900</v>
       </c>
       <c r="J57" s="3">
+        <v>4313200</v>
+      </c>
+      <c r="K57" s="3">
         <v>3627300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3655800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3255900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3551900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3032400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3076400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2733400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3079600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2599700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2589600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3128200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5968100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1835100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2026300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2185100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2208700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1925800</v>
+        <v>1505300</v>
       </c>
       <c r="E58" s="3">
-        <v>2037700</v>
+        <v>2143200</v>
       </c>
       <c r="F58" s="3">
-        <v>2161000</v>
+        <v>2267600</v>
       </c>
       <c r="G58" s="3">
-        <v>2144400</v>
+        <v>2404900</v>
       </c>
       <c r="H58" s="3">
-        <v>1389400</v>
+        <v>2386400</v>
       </c>
       <c r="I58" s="3">
-        <v>1733900</v>
+        <v>1546100</v>
       </c>
       <c r="J58" s="3">
+        <v>1929500</v>
+      </c>
+      <c r="K58" s="3">
         <v>1139600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1039500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1302700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1407200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1552700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1560400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2710100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2550400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2969700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3632300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1617000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2949000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1745500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2089300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2235600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2774400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2326100</v>
+        <v>2851200</v>
       </c>
       <c r="E59" s="3">
-        <v>2208700</v>
+        <v>2588600</v>
       </c>
       <c r="F59" s="3">
-        <v>2684100</v>
+        <v>2457900</v>
       </c>
       <c r="G59" s="3">
-        <v>2434200</v>
+        <v>2987000</v>
       </c>
       <c r="H59" s="3">
-        <v>2233700</v>
+        <v>2708900</v>
       </c>
       <c r="I59" s="3">
-        <v>2005900</v>
+        <v>2485800</v>
       </c>
       <c r="J59" s="3">
+        <v>2232300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2532900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2690700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2342100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2071700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2121400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2131300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2479300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2006000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2082500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1936300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2027200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6356000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3969500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4052700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4241900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4382200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7830100</v>
+        <v>8614200</v>
       </c>
       <c r="E60" s="3">
-        <v>8069500</v>
+        <v>8713700</v>
       </c>
       <c r="F60" s="3">
-        <v>8257000</v>
+        <v>8980200</v>
       </c>
       <c r="G60" s="3">
-        <v>7949100</v>
+        <v>9188800</v>
       </c>
       <c r="H60" s="3">
-        <v>6901000</v>
+        <v>8846100</v>
       </c>
       <c r="I60" s="3">
-        <v>6927400</v>
+        <v>7679800</v>
       </c>
       <c r="J60" s="3">
+        <v>7709200</v>
+      </c>
+      <c r="K60" s="3">
         <v>7299800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7386100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6900800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7030800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6706400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6768200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7922700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7636000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7651900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8158200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6772400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8156500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7550100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8168300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8662700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8374400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3352700</v>
+        <v>3831400</v>
       </c>
       <c r="E61" s="3">
-        <v>3258800</v>
+        <v>3731100</v>
       </c>
       <c r="F61" s="3">
-        <v>3283100</v>
+        <v>3626500</v>
       </c>
       <c r="G61" s="3">
-        <v>3247800</v>
+        <v>3653600</v>
       </c>
       <c r="H61" s="3">
-        <v>3729300</v>
+        <v>3614300</v>
       </c>
       <c r="I61" s="3">
-        <v>3848800</v>
+        <v>4150200</v>
       </c>
       <c r="J61" s="3">
+        <v>4283200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3957800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4174500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4008900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4165300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4321900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4445000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4555600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4825000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5152000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5627300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5787000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5978000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4133900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4137000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2442500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2031700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1597600</v>
+        <v>1848400</v>
       </c>
       <c r="E62" s="3">
-        <v>1574800</v>
+        <v>1777900</v>
       </c>
       <c r="F62" s="3">
-        <v>1625600</v>
+        <v>1752500</v>
       </c>
       <c r="G62" s="3">
-        <v>1676400</v>
+        <v>1809000</v>
       </c>
       <c r="H62" s="3">
-        <v>1620200</v>
+        <v>1865600</v>
       </c>
       <c r="I62" s="3">
-        <v>1662800</v>
+        <v>1803000</v>
       </c>
       <c r="J62" s="3">
+        <v>1850500</v>
+      </c>
+      <c r="K62" s="3">
         <v>1753800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1952700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1847700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1853700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2048700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2108100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2041900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2155300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2277400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2570900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2755700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4777500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2594100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2650800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2918600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2848700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5649,8 +5798,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5747,8 +5899,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5845,106 +6000,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13116600</v>
+        <v>14661500</v>
       </c>
       <c r="E66" s="3">
-        <v>13233500</v>
+        <v>14596900</v>
       </c>
       <c r="F66" s="3">
-        <v>13493600</v>
+        <v>14727000</v>
       </c>
       <c r="G66" s="3">
-        <v>13191800</v>
+        <v>15016400</v>
       </c>
       <c r="H66" s="3">
-        <v>12564600</v>
+        <v>14680600</v>
       </c>
       <c r="I66" s="3">
-        <v>12736800</v>
+        <v>13982500</v>
       </c>
       <c r="J66" s="3">
+        <v>14174200</v>
+      </c>
+      <c r="K66" s="3">
         <v>13321000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13840300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13072000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13362200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13379600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13639700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14844900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14948600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15423000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16749200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15745300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17560800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14744100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15439800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14541300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13766400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5979,8 +6140,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6077,8 +6239,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6175,8 +6340,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6273,8 +6441,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6371,106 +6542,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>17430000</v>
+        <v>20202000</v>
       </c>
       <c r="E72" s="3">
-        <v>17312300</v>
+        <v>19397000</v>
       </c>
       <c r="F72" s="3">
-        <v>16901400</v>
+        <v>19266000</v>
       </c>
       <c r="G72" s="3">
-        <v>16802000</v>
+        <v>18808700</v>
       </c>
       <c r="H72" s="3">
-        <v>16159900</v>
+        <v>18698200</v>
       </c>
       <c r="I72" s="3">
-        <v>15955900</v>
+        <v>17983600</v>
       </c>
       <c r="J72" s="3">
+        <v>17756600</v>
+      </c>
+      <c r="K72" s="3">
         <v>15202300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15804000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15308800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15874300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16784800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17007300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15925300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14682900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15438900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17177700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18111900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44028300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>22532700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22193000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22722500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22336800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6567,8 +6744,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6665,8 +6845,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6763,106 +6946,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22556600</v>
+        <v>26985300</v>
       </c>
       <c r="E76" s="3">
-        <v>21395900</v>
+        <v>25102200</v>
       </c>
       <c r="F76" s="3">
-        <v>21665400</v>
+        <v>23810500</v>
       </c>
       <c r="G76" s="3">
-        <v>21204900</v>
+        <v>24110400</v>
       </c>
       <c r="H76" s="3">
-        <v>19303200</v>
+        <v>23597900</v>
       </c>
       <c r="I76" s="3">
-        <v>18922000</v>
+        <v>21481600</v>
       </c>
       <c r="J76" s="3">
+        <v>21057400</v>
+      </c>
+      <c r="K76" s="3">
         <v>19417300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19923900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18073100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18067300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18724100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18968100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17741300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15759200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16606100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18624400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19535800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>21402800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>20190400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20687400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>22301400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22485700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6959,209 +7148,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>552500</v>
+        <v>798600</v>
       </c>
       <c r="E81" s="3">
-        <v>412000</v>
+        <v>614900</v>
       </c>
       <c r="F81" s="3">
-        <v>536500</v>
+        <v>458500</v>
       </c>
       <c r="G81" s="3">
-        <v>587900</v>
+        <v>597000</v>
       </c>
       <c r="H81" s="3">
-        <v>577400</v>
+        <v>654200</v>
       </c>
       <c r="I81" s="3">
-        <v>711700</v>
+        <v>642500</v>
       </c>
       <c r="J81" s="3">
+        <v>792100</v>
+      </c>
+      <c r="K81" s="3">
         <v>611200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>263600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>357500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-197900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>508500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>493000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2022400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-354100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>171600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>469700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>825800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>393100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>536100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>681400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>788200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>647300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>576300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>818200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>596000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>656300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>525400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>731700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7196,106 +7394,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>542700</v>
+        <v>622200</v>
       </c>
       <c r="E83" s="3">
-        <v>499400</v>
+        <v>603900</v>
       </c>
       <c r="F83" s="3">
-        <v>515800</v>
+        <v>555800</v>
       </c>
       <c r="G83" s="3">
-        <v>474900</v>
+        <v>574000</v>
       </c>
       <c r="H83" s="3">
-        <v>460900</v>
+        <v>528500</v>
       </c>
       <c r="I83" s="3">
-        <v>462900</v>
+        <v>512900</v>
       </c>
       <c r="J83" s="3">
+        <v>515200</v>
+      </c>
+      <c r="K83" s="3">
         <v>482100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>460700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>435800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>444600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>461700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>442800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>435700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>498300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>516900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>565200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>589000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>627500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>642000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>648500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>644800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>479300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>503300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>444400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>465300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>489800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>473600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>440100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>440600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>428800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7392,8 +7594,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7490,8 +7695,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7588,8 +7796,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7686,8 +7897,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7784,82 +7998,85 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>818900</v>
+        <v>586900</v>
       </c>
       <c r="E89" s="3">
-        <v>1510600</v>
+        <v>911300</v>
       </c>
       <c r="F89" s="3">
-        <v>1204700</v>
+        <v>1681100</v>
       </c>
       <c r="G89" s="3">
-        <v>741900</v>
+        <v>1340700</v>
       </c>
       <c r="H89" s="3">
-        <v>763800</v>
+        <v>825600</v>
       </c>
       <c r="I89" s="3">
-        <v>921800</v>
+        <v>850000</v>
       </c>
       <c r="J89" s="3">
+        <v>1025800</v>
+      </c>
+      <c r="K89" s="3">
         <v>913600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>138100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>399400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>416000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>180000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>644200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1553400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1323100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>691700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>564600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1895100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>694900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>888100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1172900</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -7882,8 +8099,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7918,82 +8138,83 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67195000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103495000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-103013000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-82364000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-65299000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-92261000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-196600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-349000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-376900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-364000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-325900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-566700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-626200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-678600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-523100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-680800</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8016,8 +8237,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8114,8 +8338,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8212,82 +8439,85 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-623100</v>
+        <v>-35500</v>
       </c>
       <c r="E94" s="3">
-        <v>-625700</v>
+        <v>-693400</v>
       </c>
       <c r="F94" s="3">
-        <v>-453700</v>
+        <v>-696300</v>
       </c>
       <c r="G94" s="3">
-        <v>-308600</v>
+        <v>-504900</v>
       </c>
       <c r="H94" s="3">
-        <v>-511400</v>
+        <v>-343500</v>
       </c>
       <c r="I94" s="3">
-        <v>-387100</v>
+        <v>-569100</v>
       </c>
       <c r="J94" s="3">
+        <v>-430700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-276600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-491600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-352700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-598100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-175200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2055000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-292400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-382600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-522200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-44100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-358100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-694000</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -8310,8 +8540,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8346,77 +8579,78 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-480400</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G96" s="3">
+        <v>-485400</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I96" s="3">
         <v>-431700</v>
       </c>
-      <c r="E96" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-436200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-387900</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-600</v>
-      </c>
       <c r="J96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-376900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-4100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-393400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-430900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-293600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-273700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-5900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-490000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-528100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-5400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-572200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8444,8 +8678,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8542,8 +8779,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8640,8 +8880,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8738,82 +8981,85 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-729900</v>
+        <v>-872200</v>
       </c>
       <c r="E100" s="3">
-        <v>-231200</v>
+        <v>-812200</v>
       </c>
       <c r="F100" s="3">
-        <v>-546600</v>
+        <v>-257200</v>
       </c>
       <c r="G100" s="3">
-        <v>-119200</v>
+        <v>-608300</v>
       </c>
       <c r="H100" s="3">
-        <v>-274700</v>
+        <v>-132700</v>
       </c>
       <c r="I100" s="3">
-        <v>-259100</v>
+        <v>-305700</v>
       </c>
       <c r="J100" s="3">
+        <v>-288400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-595700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-645100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-892400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-210100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-526400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-326200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-385600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-724900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1947000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-568400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-230900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1278300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1194800</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -8836,82 +9082,85 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>135000</v>
+        <v>228900</v>
       </c>
       <c r="E101" s="3">
-        <v>-144300</v>
+        <v>150300</v>
       </c>
       <c r="F101" s="3">
-        <v>20400</v>
+        <v>-160600</v>
       </c>
       <c r="G101" s="3">
-        <v>276200</v>
+        <v>22700</v>
       </c>
       <c r="H101" s="3">
-        <v>10200</v>
+        <v>307400</v>
       </c>
       <c r="I101" s="3">
-        <v>-311700</v>
+        <v>11400</v>
       </c>
       <c r="J101" s="3">
+        <v>-346800</v>
+      </c>
+      <c r="K101" s="3">
         <v>105400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>391200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>262000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>110000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-32400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-57400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>316500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>28100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-53300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>82200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-164300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>102700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-89500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-56300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>67800</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8934,82 +9183,85 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-398900</v>
+        <v>-91800</v>
       </c>
       <c r="E102" s="3">
-        <v>509400</v>
+        <v>-444000</v>
       </c>
       <c r="F102" s="3">
-        <v>224800</v>
+        <v>566900</v>
       </c>
       <c r="G102" s="3">
-        <v>590200</v>
+        <v>250200</v>
       </c>
       <c r="H102" s="3">
-        <v>-12100</v>
+        <v>656800</v>
       </c>
       <c r="I102" s="3">
-        <v>-36100</v>
+        <v>-13500</v>
       </c>
       <c r="J102" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-612000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-392400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-722700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-430700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-740900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2689400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1095400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>252500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2338300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-690300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1329100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>564100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-648100</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -9030,6 +9282,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,448 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>7899900</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7555200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>7921200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7784700</v>
-      </c>
-      <c r="H8" s="3">
-        <v>7513000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7409100</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="3">
         <v>8045300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6957900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6708500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5916300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5800300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5820400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5756600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5156000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5065500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5774300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4752500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6217800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8048800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8122100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8168200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8151300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>4858700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>4510600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4900500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4819200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4610300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4564700</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="3">
         <v>4924000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4264200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4114800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3615000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3318300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3396300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3395600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3069100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2818700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3709400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3230500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3894700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5024300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4951200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5149100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5094700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>3041200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3044600</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3020700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2965500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2902700</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2844400</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="3">
         <v>3121400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2693700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2593700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2301300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2482000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2424100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2361000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2086900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2246800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2064900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1522000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2323200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3024500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3170900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3019100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3056600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1133,109 +1149,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>216500</v>
-      </c>
-      <c r="E12" s="3">
-        <v>226500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>231200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>214300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>210000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>210700</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3">
         <v>216200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>179000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>184100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>175100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>157300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>163000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>168300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>159200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>126200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>173000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>186300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>229200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>252500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>235800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>252200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>243000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>269400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>238200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>228100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>220800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>241900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>216700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>232200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>207300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>215600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1335,210 +1355,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>34300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>25100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>109700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-31700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="3">
         <v>36300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>85700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>49900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>39800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>487000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>682000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>383400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>47500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>190200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>41600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-103500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="3">
         <v>99800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>9300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>58400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>39200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>233300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>222800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>212300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>206800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>196000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>186100</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="3">
         <v>187900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>173000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>165700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>154300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>158200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>161700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>161900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>156500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>159000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>171800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>179100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>193000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>312700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>310900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>200000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>203500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>85000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>84700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>79500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>78600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>80500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>76300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>73000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>72800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>71300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1571,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>6745000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6719200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>7168700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6896000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>6638800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6503900</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="3">
         <v>7093500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6107900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6126500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5334400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5037600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5098300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5071600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4565000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4771800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5669200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5164900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5873400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7408900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6921500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7573700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7348300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1154900</v>
-      </c>
-      <c r="E18" s="3">
-        <v>836100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>752500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>888700</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="3">
+        <v>951900</v>
+      </c>
+      <c r="L18" s="3">
+        <v>850100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>582100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>581900</v>
+      </c>
+      <c r="O18" s="3">
+        <v>762800</v>
+      </c>
+      <c r="P18" s="3">
+        <v>722100</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>684900</v>
+      </c>
+      <c r="R18" s="3">
+        <v>591000</v>
+      </c>
+      <c r="S18" s="3">
+        <v>293700</v>
+      </c>
+      <c r="T18" s="3">
+        <v>105100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-412500</v>
+      </c>
+      <c r="V18" s="3">
+        <v>344400</v>
+      </c>
+      <c r="W18" s="3">
+        <v>640000</v>
+      </c>
+      <c r="X18" s="3">
+        <v>1200600</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>594400</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>803000</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>1058100</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>1129800</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>904800</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>908100</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>978800</v>
+      </c>
+      <c r="AF18" s="3">
         <v>874100</v>
       </c>
-      <c r="I18" s="3">
-        <v>905300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>951900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>850100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>582100</v>
-      </c>
-      <c r="M18" s="3">
-        <v>581900</v>
-      </c>
-      <c r="N18" s="3">
-        <v>762800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>722100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>684900</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>591000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>293700</v>
-      </c>
-      <c r="S18" s="3">
-        <v>105100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-412500</v>
-      </c>
-      <c r="U18" s="3">
-        <v>344400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>640000</v>
-      </c>
-      <c r="W18" s="3">
-        <v>1200600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>594400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>803000</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>1058100</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>1129800</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>904800</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>908100</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>978800</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>874100</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>888200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>855800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1810,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>62800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-91500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>27400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="3">
         <v>-77100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-33000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>17500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>23500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-24000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>76900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>18700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>109100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>231400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>77600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>47400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1776700</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1502800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1216700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1411300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1400400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1445600</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="3">
         <v>1390000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1299100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1068500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1074100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1239400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1197600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1145300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1050200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>795700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>631400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>129400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>909400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1339200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1831800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1238200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1442400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>42000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>45600</v>
-      </c>
-      <c r="F22" s="3">
-        <v>42600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>37900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>35900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>32900</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>28800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>31800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>32800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>57400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>66700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>34100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>31600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>38200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>28500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>17900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>19500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1112500</v>
-      </c>
-      <c r="E23" s="3">
-        <v>853300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>618300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>799400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>836000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>899800</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K23" s="3">
         <v>846000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>792000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>586800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>618200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>773800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>715000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>683500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>596000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>278300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>90600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-467600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>287500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>659500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1153400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>546500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>749100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>890600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>843500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>927100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>885100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>801000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>299900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>223700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>178500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>197800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>166500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>246500</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K24" s="3">
         <v>212800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>144600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>224100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>176800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-25800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>178100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>172500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>130600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>123500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>154300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-54500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>117800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>184000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>311900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>138400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>192000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>447300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>269000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>226900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>242800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>331900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>307100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>212300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>255800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>298900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2416,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>812500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>629500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>439800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>601500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>669500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>653300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K26" s="3">
         <v>633200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>647400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>362700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>441400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>799600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>536900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>511000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>465400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>154800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-63700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-413100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>169800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>475500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>841500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>408100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>557100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>695400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>808300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>663700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>600600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>840100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>620100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>672800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>545200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>755300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>798800</v>
-      </c>
-      <c r="E27" s="3">
-        <v>615000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>435000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>584800</v>
-      </c>
-      <c r="H27" s="3">
-        <v>657700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>643700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K27" s="3">
         <v>626600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>635400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>351700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>434400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>789800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>527900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>448400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>148300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-76400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>147700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>469700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>825800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>393100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>536100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>681400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>788200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>647300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>576300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>818200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>596000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>656300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>525400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>731700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2719,73 +2780,76 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="3">
-        <v>23500</v>
-      </c>
-      <c r="G29" s="3">
-        <v>12200</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29" s="3">
         <v>165500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-24200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-88100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-76900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-987700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-19400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1574000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-142300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>60300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>46600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>23900</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2820,8 +2884,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2921,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3022,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-62800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>91500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>51500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-27400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="3">
         <v>77100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>33000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-23500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>24000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-76900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>24800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>33000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>36800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>798600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>614900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>458500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>597000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>654200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>642500</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="3">
         <v>792100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>611200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>263600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>357500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-197900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>508500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>493000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2022400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-354100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>171600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>469700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>825800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>393100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>536100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>681400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>788200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>647300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>576300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>818200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>596000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>656300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>525400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>731700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3325,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>798600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>614900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>458500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>597000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>654200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>642500</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35" s="3">
         <v>792100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>611200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>263600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>357500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-197900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>508500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>493000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2022400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-354100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>171600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>469700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>825800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>393100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>536100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>681400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>788200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>647300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>576300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>818200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>596000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>656300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>525400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>731700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3569,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3606,917 +3695,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4608900</v>
+        <v>3883400</v>
       </c>
       <c r="E41" s="3">
-        <v>4700700</v>
+        <v>4035300</v>
       </c>
       <c r="F41" s="3">
-        <v>5144700</v>
+        <v>4377200</v>
       </c>
       <c r="G41" s="3">
-        <v>4577800</v>
+        <v>5140400</v>
       </c>
       <c r="H41" s="3">
-        <v>4327600</v>
+        <v>4316800</v>
       </c>
       <c r="I41" s="3">
-        <v>3670800</v>
+        <v>4215700</v>
       </c>
       <c r="J41" s="3">
+        <v>3889200</v>
+      </c>
+      <c r="K41" s="3">
         <v>3684200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3346700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4182100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4506600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5410400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6130200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7004500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8436200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5941300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5150000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5362800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3123800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3943900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2740700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3982700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3636300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>66500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>74600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>76600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>60900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>116400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>60800</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>107300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>146200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>63000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>65700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>80900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>54100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>51600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>45100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>53300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>51500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>86200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>155300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1369700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1356600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1323100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1240800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7538500</v>
+        <v>6885100</v>
       </c>
       <c r="E43" s="3">
-        <v>6966100</v>
+        <v>6600300</v>
       </c>
       <c r="F43" s="3">
-        <v>6761400</v>
+        <v>6486700</v>
       </c>
       <c r="G43" s="3">
-        <v>7363700</v>
+        <v>7081000</v>
       </c>
       <c r="H43" s="3">
-        <v>7121300</v>
+        <v>6943800</v>
       </c>
       <c r="I43" s="3">
-        <v>6676900</v>
+        <v>6937100</v>
       </c>
       <c r="J43" s="3">
+        <v>7074300</v>
+      </c>
+      <c r="K43" s="3">
         <v>6720900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6234400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5941600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5292500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5094900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5021400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4848000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4560700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4894700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5247200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5166800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5957200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11999600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5330100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5120200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5535200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7184900</v>
+        <v>6580400</v>
       </c>
       <c r="E44" s="3">
-        <v>6692300</v>
+        <v>6290700</v>
       </c>
       <c r="F44" s="3">
-        <v>6166900</v>
+        <v>6231700</v>
       </c>
       <c r="G44" s="3">
-        <v>6919900</v>
+        <v>6161800</v>
       </c>
       <c r="H44" s="3">
-        <v>7015400</v>
+        <v>6525300</v>
       </c>
       <c r="I44" s="3">
-        <v>6549700</v>
+        <v>6833900</v>
       </c>
       <c r="J44" s="3">
+        <v>6939500</v>
+      </c>
+      <c r="K44" s="3">
         <v>6285700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6016500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5727200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4807600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4329100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4487800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4166700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3725300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3600800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4021000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5073500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5496700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11174200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5646400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5756300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6145500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1201400</v>
+        <v>1175700</v>
       </c>
       <c r="E45" s="3">
-        <v>1052500</v>
+        <v>1110100</v>
       </c>
       <c r="F45" s="3">
-        <v>1002200</v>
+        <v>1049500</v>
       </c>
       <c r="G45" s="3">
-        <v>988900</v>
+        <v>388100</v>
       </c>
       <c r="H45" s="3">
-        <v>982700</v>
+        <v>989900</v>
       </c>
       <c r="I45" s="3">
-        <v>971500</v>
+        <v>1070700</v>
       </c>
       <c r="J45" s="3">
+        <v>1093800</v>
+      </c>
+      <c r="K45" s="3">
         <v>1041700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1030100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1232300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>911400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>836800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>635600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>649000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>587400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>569600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>679500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>648300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>643800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>780500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1290500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1233600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1217000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20600200</v>
+        <v>18524700</v>
       </c>
       <c r="E46" s="3">
-        <v>19486200</v>
+        <v>18036300</v>
       </c>
       <c r="F46" s="3">
-        <v>19151800</v>
+        <v>18145000</v>
       </c>
       <c r="G46" s="3">
-        <v>19911100</v>
+        <v>19135900</v>
       </c>
       <c r="H46" s="3">
-        <v>19563400</v>
+        <v>18775800</v>
       </c>
       <c r="I46" s="3">
-        <v>17929700</v>
+        <v>19057400</v>
       </c>
       <c r="J46" s="3">
+        <v>18996800</v>
+      </c>
+      <c r="K46" s="3">
         <v>17839800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16774000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17146200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15583800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15752000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16329200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16719800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>17354700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15059700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15149100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16337500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15376800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17476700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16364300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17415900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17774800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1399100</v>
+        <v>1726500</v>
       </c>
       <c r="E47" s="3">
-        <v>1415700</v>
+        <v>1675400</v>
       </c>
       <c r="F47" s="3">
-        <v>1224000</v>
+        <v>1754900</v>
       </c>
       <c r="G47" s="3">
-        <v>1177200</v>
+        <v>1658200</v>
       </c>
       <c r="H47" s="3">
-        <v>1095100</v>
+        <v>1527400</v>
       </c>
       <c r="I47" s="3">
-        <v>1070300</v>
+        <v>1458100</v>
       </c>
       <c r="J47" s="3">
+        <v>1613300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1018200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>991400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1107900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1065600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1137000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1145100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1145500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1050000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1009800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1054200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1276800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1505300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2990000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1752500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1842600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2137000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15697600</v>
+        <v>14208000</v>
       </c>
       <c r="E48" s="3">
-        <v>15072300</v>
+        <v>13743900</v>
       </c>
       <c r="F48" s="3">
-        <v>14609300</v>
+        <v>14035000</v>
       </c>
       <c r="G48" s="3">
-        <v>14340600</v>
+        <v>14597100</v>
       </c>
       <c r="H48" s="3">
-        <v>14142700</v>
+        <v>13522800</v>
       </c>
       <c r="I48" s="3">
-        <v>13211100</v>
+        <v>13776800</v>
       </c>
       <c r="J48" s="3">
+        <v>13997300</v>
+      </c>
+      <c r="K48" s="3">
         <v>13191400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>11939700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12426800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11674800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11829900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12035900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12457000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12007200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12331000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13384700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15078000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15667800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>31118800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13721000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13711500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14610900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2747700</v>
+        <v>2449000</v>
       </c>
       <c r="E49" s="3">
-        <v>2641400</v>
+        <v>2405800</v>
       </c>
       <c r="F49" s="3">
-        <v>2491000</v>
+        <v>2459600</v>
       </c>
       <c r="G49" s="3">
-        <v>2501400</v>
+        <v>2489000</v>
       </c>
       <c r="H49" s="3">
-        <v>2336500</v>
+        <v>2358800</v>
       </c>
       <c r="I49" s="3">
-        <v>2166200</v>
+        <v>2276000</v>
       </c>
       <c r="J49" s="3">
+        <v>2295100</v>
+      </c>
+      <c r="K49" s="3">
         <v>2103900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1948300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1972300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1826000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1787000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1807800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1487700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1428300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1576900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1642100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1787900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1829400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3799400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1743200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1768700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>861500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>957700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>954200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>903400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>891800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>949500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>992600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>988400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>656000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>657700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4616,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4717,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1202100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1083500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1061400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1196600</v>
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H52" s="3">
-        <v>1140900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1086800</v>
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>1078400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1084900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1110900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>994800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>923600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>785600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>797700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>746000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>730400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>798900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>893400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>901800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1805500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1353500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1388500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1458400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>998600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>934800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>965000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4919,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>41646700</v>
+        <v>37559200</v>
       </c>
       <c r="E54" s="3">
-        <v>39699100</v>
+        <v>36463500</v>
       </c>
       <c r="F54" s="3">
-        <v>38537500</v>
+        <v>36966900</v>
       </c>
       <c r="G54" s="3">
-        <v>39126800</v>
+        <v>38505500</v>
       </c>
       <c r="H54" s="3">
-        <v>38278500</v>
+        <v>36895700</v>
       </c>
       <c r="I54" s="3">
-        <v>35464100</v>
+        <v>37288300</v>
       </c>
       <c r="J54" s="3">
+        <v>37574600</v>
+      </c>
+      <c r="K54" s="3">
         <v>35231600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32738300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33764200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31145100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31429500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32103700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32607800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32586200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>30707800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32029000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>35373500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35281000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38963600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34934500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>36127200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36842700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5057,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5094,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4257600</v>
+        <v>3551700</v>
       </c>
       <c r="E57" s="3">
-        <v>3982000</v>
+        <v>3727700</v>
       </c>
       <c r="F57" s="3">
-        <v>4254600</v>
+        <v>3708000</v>
       </c>
       <c r="G57" s="3">
-        <v>3796900</v>
+        <v>4251100</v>
       </c>
       <c r="H57" s="3">
-        <v>3750900</v>
+        <v>3580400</v>
       </c>
       <c r="I57" s="3">
-        <v>3647900</v>
+        <v>3653900</v>
       </c>
       <c r="J57" s="3">
+        <v>3864900</v>
+      </c>
+      <c r="K57" s="3">
         <v>4313200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3627300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3655800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3255900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3551900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3032400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3076400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2733400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3079600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2599700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2589600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3128200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5968100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1835100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2026300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2185100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1505300</v>
+        <v>1485700</v>
       </c>
       <c r="E58" s="3">
-        <v>2143200</v>
+        <v>1318000</v>
       </c>
       <c r="F58" s="3">
-        <v>2267600</v>
+        <v>1995700</v>
       </c>
       <c r="G58" s="3">
-        <v>2404900</v>
+        <v>2265700</v>
       </c>
       <c r="H58" s="3">
-        <v>2386400</v>
+        <v>2267800</v>
       </c>
       <c r="I58" s="3">
-        <v>1546100</v>
+        <v>2324600</v>
       </c>
       <c r="J58" s="3">
+        <v>1638200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1929500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1139600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1039500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1302700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1407200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1552700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1560400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2710100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2550400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2969700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3632300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1617000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2949000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1745500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2089300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2235600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2851200</v>
+        <v>2693900</v>
       </c>
       <c r="E59" s="3">
-        <v>2588600</v>
+        <v>2489000</v>
       </c>
       <c r="F59" s="3">
-        <v>2457900</v>
+        <v>2403000</v>
       </c>
       <c r="G59" s="3">
-        <v>2987000</v>
+        <v>1971100</v>
       </c>
       <c r="H59" s="3">
-        <v>2708900</v>
+        <v>2810500</v>
       </c>
       <c r="I59" s="3">
-        <v>2485800</v>
+        <v>2626300</v>
       </c>
       <c r="J59" s="3">
+        <v>2624300</v>
+      </c>
+      <c r="K59" s="3">
         <v>2232300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2532900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2690700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2342100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2071700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2121400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2131300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2479300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2006000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2082500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1936300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2027200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6356000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3969500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4052700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4241900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8614200</v>
+        <v>7731300</v>
       </c>
       <c r="E60" s="3">
-        <v>8713700</v>
+        <v>7534600</v>
       </c>
       <c r="F60" s="3">
-        <v>8980200</v>
+        <v>8106600</v>
       </c>
       <c r="G60" s="3">
-        <v>9188800</v>
+        <v>8965200</v>
       </c>
       <c r="H60" s="3">
-        <v>8846100</v>
+        <v>8658600</v>
       </c>
       <c r="I60" s="3">
-        <v>7679800</v>
+        <v>8604800</v>
       </c>
       <c r="J60" s="3">
+        <v>8127400</v>
+      </c>
+      <c r="K60" s="3">
         <v>7709200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7299800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7386100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6900800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7030800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6706400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6768200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7922700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7636000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7651900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8158200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6772400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8156500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7550100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8168300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8662700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3831400</v>
+        <v>3549000</v>
       </c>
       <c r="E61" s="3">
-        <v>3731100</v>
+        <v>3354600</v>
       </c>
       <c r="F61" s="3">
-        <v>3626500</v>
+        <v>3474300</v>
       </c>
       <c r="G61" s="3">
-        <v>3653600</v>
+        <v>3623500</v>
       </c>
       <c r="H61" s="3">
-        <v>3614300</v>
+        <v>3445300</v>
       </c>
       <c r="I61" s="3">
-        <v>4150200</v>
+        <v>3520800</v>
       </c>
       <c r="J61" s="3">
+        <v>4397200</v>
+      </c>
+      <c r="K61" s="3">
         <v>4283200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3957800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4174500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4008900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4165300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4321900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4445000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4555600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4825000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5152000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5627300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5787000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5978000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4133900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4137000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2442500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1848400</v>
+        <v>417200</v>
       </c>
       <c r="E62" s="3">
-        <v>1777900</v>
+        <v>410000</v>
       </c>
       <c r="F62" s="3">
-        <v>1752500</v>
+        <v>416600</v>
       </c>
       <c r="G62" s="3">
-        <v>1809000</v>
+        <v>450000</v>
       </c>
       <c r="H62" s="3">
-        <v>1865600</v>
+        <v>428800</v>
       </c>
       <c r="I62" s="3">
-        <v>1803000</v>
+        <v>460400</v>
       </c>
       <c r="J62" s="3">
+        <v>448000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1850500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1753800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1952700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1847700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1853700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2048700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2108100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2041900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2155300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2277400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2570900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2755700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4777500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2594100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2650800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2918600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5801,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5902,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6003,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>14661500</v>
+        <v>12939500</v>
       </c>
       <c r="E66" s="3">
-        <v>14596900</v>
+        <v>12515000</v>
       </c>
       <c r="F66" s="3">
-        <v>14727000</v>
+        <v>13243900</v>
       </c>
       <c r="G66" s="3">
-        <v>15016400</v>
+        <v>14347300</v>
       </c>
       <c r="H66" s="3">
-        <v>14680600</v>
+        <v>13816000</v>
       </c>
       <c r="I66" s="3">
-        <v>13982500</v>
+        <v>13955500</v>
       </c>
       <c r="J66" s="3">
+        <v>14444400</v>
+      </c>
+      <c r="K66" s="3">
         <v>14174200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13321000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13840300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13072000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13362200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13379600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13639700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14844900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14948600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15423000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16749200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15745300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17560800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>14744100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15439800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14541300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6141,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6242,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6343,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6444,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6545,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>20202000</v>
+        <v>19720800</v>
       </c>
       <c r="E72" s="3">
-        <v>19397000</v>
+        <v>17674400</v>
       </c>
       <c r="F72" s="3">
-        <v>19266000</v>
+        <v>18047000</v>
       </c>
       <c r="G72" s="3">
-        <v>18808700</v>
+        <v>19233700</v>
       </c>
       <c r="H72" s="3">
-        <v>18698200</v>
+        <v>17720300</v>
       </c>
       <c r="I72" s="3">
-        <v>17983600</v>
+        <v>18197900</v>
       </c>
       <c r="J72" s="3">
+        <v>19034300</v>
+      </c>
+      <c r="K72" s="3">
         <v>17756600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15202300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15804000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15308800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15874300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16784800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>17007300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15925300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14682900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15438900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17177700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18111900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>44028300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22532700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22193000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22722500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6747,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6848,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6949,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>26985300</v>
+        <v>24275400</v>
       </c>
       <c r="E76" s="3">
-        <v>25102200</v>
+        <v>23626800</v>
       </c>
       <c r="F76" s="3">
-        <v>23810500</v>
+        <v>23374600</v>
       </c>
       <c r="G76" s="3">
-        <v>24110400</v>
+        <v>23790800</v>
       </c>
       <c r="H76" s="3">
-        <v>23597900</v>
+        <v>22735600</v>
       </c>
       <c r="I76" s="3">
-        <v>21481600</v>
+        <v>22987500</v>
       </c>
       <c r="J76" s="3">
+        <v>22760000</v>
+      </c>
+      <c r="K76" s="3">
         <v>21057400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19417300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19923900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18073100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18067300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18724100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18968100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17741300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15759200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16606100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18624400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19535800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21402800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20190400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20687400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22301400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7151,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>798600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>614900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>458500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>597000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>654200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>642500</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K81" s="3">
         <v>792100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>611200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>263600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>357500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-197900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>508500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>493000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2022400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-354100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>171600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>469700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>825800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>393100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>536100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>681400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>788200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>647300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>576300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>818200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>596000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>656300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>525400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>731700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7395,109 +7596,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>622200</v>
+        <v>541300</v>
       </c>
       <c r="E83" s="3">
-        <v>603900</v>
+        <v>514800</v>
       </c>
       <c r="F83" s="3">
-        <v>555800</v>
+        <v>543400</v>
       </c>
       <c r="G83" s="3">
-        <v>574000</v>
+        <v>550200</v>
       </c>
       <c r="H83" s="3">
-        <v>528500</v>
+        <v>522200</v>
       </c>
       <c r="I83" s="3">
-        <v>512900</v>
+        <v>503000</v>
       </c>
       <c r="J83" s="3">
+        <v>540500</v>
+      </c>
+      <c r="K83" s="3">
         <v>515200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>482100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>460700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>435800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>444600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>461700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>442800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>435700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>498300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>516900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>565200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>589000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>627500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>642000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>648500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>644800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>479300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>503300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>444400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>465300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>489800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>473600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>440100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>440600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>428800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7597,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7698,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7799,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7900,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8001,85 +8218,88 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>586900</v>
+        <v>760500</v>
       </c>
       <c r="E89" s="3">
-        <v>911300</v>
+        <v>515700</v>
       </c>
       <c r="F89" s="3">
-        <v>1681100</v>
+        <v>850100</v>
       </c>
       <c r="G89" s="3">
-        <v>1340700</v>
+        <v>1681000</v>
       </c>
       <c r="H89" s="3">
-        <v>825600</v>
+        <v>1259200</v>
       </c>
       <c r="I89" s="3">
-        <v>850000</v>
+        <v>806300</v>
       </c>
       <c r="J89" s="3">
+        <v>901400</v>
+      </c>
+      <c r="K89" s="3">
         <v>1025800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>913600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>138100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>399400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>416000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>180000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>644200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1553400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1323100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>691700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>564600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1895100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>694900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>888100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1172900</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -8102,8 +8322,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8139,85 +8362,86 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-67195000</v>
+        <v>-454400</v>
       </c>
       <c r="E91" s="3">
-        <v>-103495000</v>
+        <v>-361100</v>
       </c>
       <c r="F91" s="3">
-        <v>-103013000</v>
+        <v>-599100</v>
       </c>
       <c r="G91" s="3">
-        <v>-82364000</v>
+        <v>-616800</v>
       </c>
       <c r="H91" s="3">
-        <v>-65299000</v>
+        <v>-392100</v>
       </c>
       <c r="I91" s="3">
-        <v>-92261000</v>
+        <v>-376300</v>
       </c>
       <c r="J91" s="3">
+        <v>-620900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-196600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-349000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-376900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-364000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-325900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-566700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-626200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-678600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-523100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-680800</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -8240,8 +8464,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8341,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8442,85 +8672,88 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-35500</v>
+        <v>-502100</v>
       </c>
       <c r="E94" s="3">
-        <v>-693400</v>
+        <v>-31100</v>
       </c>
       <c r="F94" s="3">
-        <v>-696300</v>
+        <v>-645700</v>
       </c>
       <c r="G94" s="3">
-        <v>-504900</v>
+        <v>-695800</v>
       </c>
       <c r="H94" s="3">
-        <v>-343500</v>
+        <v>-476100</v>
       </c>
       <c r="I94" s="3">
-        <v>-569100</v>
+        <v>-334600</v>
       </c>
       <c r="J94" s="3">
+        <v>-602900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-430700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-276600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-491600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-352700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-598100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-175200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2055000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-292400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-382600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-522200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-44100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-358100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-694000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -8543,8 +8776,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8580,80 +8816,81 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-480400</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-485400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-431700</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
         <v>-700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-376900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-4100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-393400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-430900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-293600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-273700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-5900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-490000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-528100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-572200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8681,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8782,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8883,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8984,85 +9230,88 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-872200</v>
+        <v>-511900</v>
       </c>
       <c r="E100" s="3">
-        <v>-812200</v>
+        <v>-763600</v>
       </c>
       <c r="F100" s="3">
-        <v>-257200</v>
+        <v>-756300</v>
       </c>
       <c r="G100" s="3">
-        <v>-608300</v>
+        <v>-257000</v>
       </c>
       <c r="H100" s="3">
-        <v>-132700</v>
+        <v>-573600</v>
       </c>
       <c r="I100" s="3">
-        <v>-305700</v>
+        <v>-129200</v>
       </c>
       <c r="J100" s="3">
+        <v>-323900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-288400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-595700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-645100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-892400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-210100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-526400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-326200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-385600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-724900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1947000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-568400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-230900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1278300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -9085,85 +9334,88 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>228900</v>
+        <v>21500</v>
       </c>
       <c r="E101" s="3">
-        <v>150300</v>
+        <v>299400</v>
       </c>
       <c r="F101" s="3">
-        <v>-160600</v>
+        <v>12100</v>
       </c>
       <c r="G101" s="3">
-        <v>22700</v>
+        <v>-370400</v>
       </c>
       <c r="H101" s="3">
-        <v>307400</v>
+        <v>114100</v>
       </c>
       <c r="I101" s="3">
-        <v>11400</v>
+        <v>427100</v>
       </c>
       <c r="J101" s="3">
+        <v>324900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-346800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>105400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>391200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>262000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>110000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-32400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-57400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>316500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>28100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-53300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>82200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-164300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>102700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-89500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-56300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>67800</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -9186,85 +9438,88 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-91800</v>
+        <v>-649200</v>
       </c>
       <c r="E102" s="3">
-        <v>-444000</v>
+        <v>-78600</v>
       </c>
       <c r="F102" s="3">
-        <v>566900</v>
+        <v>-411900</v>
       </c>
       <c r="G102" s="3">
-        <v>250200</v>
+        <v>567700</v>
       </c>
       <c r="H102" s="3">
-        <v>656800</v>
+        <v>230900</v>
       </c>
       <c r="I102" s="3">
-        <v>-13500</v>
+        <v>641900</v>
       </c>
       <c r="J102" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-40200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-612000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-392400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-722700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-430700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-740900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2689400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1095400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>252500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2338300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-690300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1329100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>564100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-648100</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -9285,6 +9540,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -826,86 +829,89 @@
       <c r="J8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
         <v>8045300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6957900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6708500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5916300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5800300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5820400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5756600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5156000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5065500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5774300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4752500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6217800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8048800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8122100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8168200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8151300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -930,86 +936,89 @@
       <c r="J9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
         <v>4924000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4264200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4114800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3615000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3318300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3396300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3395600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3069100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2818700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3709400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3230500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3894700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5024300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4951200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5149100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5094700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1034,86 +1043,89 @@
       <c r="J10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
         <v>3121400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2693700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2593700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2301300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2482000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2424100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2361000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2086900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2246800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2064900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1522000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2323200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3024500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3170900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3019100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3056600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1176,86 +1189,89 @@
       <c r="J12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
         <v>216200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>179000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>184100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>175100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>157300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>163000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>168300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>159200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>126200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>173000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>186300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>229200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>252500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>235800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>252200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>243000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>269400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>238200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>228100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>220800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>241900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>216700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>232200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>207300</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>215600</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1358,8 +1374,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1384,86 +1403,89 @@
       <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
         <v>36300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>85700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>49900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>39800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>487000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>682000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>383400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>47500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>190200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>41600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-103500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3">
         <v>99800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>9300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>58400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1488,86 +1510,89 @@
       <c r="J15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="3">
         <v>187900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>173000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>165700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>154300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>158200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>161700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>161900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>156500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>159000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>171800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>179100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>193000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>312700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>310900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>200000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>203500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>85000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>84700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>79500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>78600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>80500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>76300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>73000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>72800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>71300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,8 +1626,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1627,86 +1653,89 @@
       <c r="J17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3">
         <v>7093500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6107900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6126500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5334400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5037600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5098300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5071600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4565000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4771800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5669200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5164900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5873400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7408900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6921500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7573700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7348300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1731,86 +1760,89 @@
       <c r="J18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
         <v>951900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>850100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>582100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>581900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>762800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>722100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>684900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>591000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>293700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>105100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-412500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>344400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>640000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1200600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>594400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>803000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1058100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>904800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>908100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>978800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>874100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>888200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>855800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,8 +1879,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1873,86 +1906,89 @@
       <c r="J20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
         <v>-77100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-33000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>17500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>23500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-23300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-24000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>76900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>18700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>109100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>19900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>231400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>77600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1977,86 +2013,89 @@
       <c r="J21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
         <v>1390000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1299100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1068500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1074100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1239400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1197600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1145300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1050200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>795700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>631400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>129400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>909400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1339200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1831800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1238200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1442400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2081,86 +2120,89 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>28800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>31800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>32800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>57400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>66700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>27700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>34100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>31600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>38200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>28500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>17900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2185,86 +2227,89 @@
       <c r="J23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="3">
         <v>846000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>792000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>586800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>618200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>773800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>715000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>683500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>596000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>278300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>90600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-467600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>287500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>659500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1153400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>546500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>749100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>890600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>843500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>927100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>885100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>801000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2289,86 +2334,89 @@
       <c r="J24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3">
         <v>212800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>144600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>224100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>176800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-25800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>178100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>172500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>130600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>123500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>154300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-54500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>117800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>184000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>311900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>138400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>192000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>447300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>269000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>226900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>242800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>331900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>307100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>212300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>255800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>298900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,8 +2519,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2497,86 +2548,89 @@
       <c r="J26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="3">
         <v>633200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>647400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>362700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>441400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>799600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>536900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>511000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>465400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>154800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-63700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-413100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>169800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>475500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>841500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>408100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>557100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>695400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>808300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>663700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>600600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>840100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>620100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>672800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>545200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>755300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2601,86 +2655,89 @@
       <c r="J27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
         <v>626600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>635400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>351700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>434400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>789800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>527900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>448400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>148300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-76400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>147700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>469700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>825800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>393100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>536100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>681400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>788200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>647300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>576300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>818200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>596000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>656300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>525400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>731700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,50 +2869,50 @@
       <c r="J29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="3">
         <v>165500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-24200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-88100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-76900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-987700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-7500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1574000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-142300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>60300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>46600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>23900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,8 +3161,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3121,86 +3190,89 @@
       <c r="J32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
         <v>77100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>33000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-17500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-23500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>23300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>24000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-76900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>24800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>33000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>36800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3225,86 +3297,89 @@
       <c r="J33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L33" s="3">
         <v>792100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>611200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>263600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>357500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-197900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>508500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>493000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2022400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-354100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>171600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>469700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>825800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>393100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>536100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>681400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>788200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>647300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>576300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>818200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>596000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>656300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>525400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>731700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,8 +3482,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3433,195 +3511,201 @@
       <c r="J35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="3">
         <v>792100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>611200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>263600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>357500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-197900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>508500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>493000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2022400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-354100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>171600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>469700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>825800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>393100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>536100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>681400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>788200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>647300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>576300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>818200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>596000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>656300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>525400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>731700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,112 +3781,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4495200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3883400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4035300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4377200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5140400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4316800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4215700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3889200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3684200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3346700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4182100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4506600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5410400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6130200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7004500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8436200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5941300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5150000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5362800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3123800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3943900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2740700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3982700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3636300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3827,813 +3916,837 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>107300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>146200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>63000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>65700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>80900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>54100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>51600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>45100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>53300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>51500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>86200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>155300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1369700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1356600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1323100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1240800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6598000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6885100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6600300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6486700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7081000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6943800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6937100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7074300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6720900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6234400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5941600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5292500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5094900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5021400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4848000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4560700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4894700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5247200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5166800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5957200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>11999600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5330100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5120200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5535200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6012500</v>
+      </c>
+      <c r="E44" s="3">
         <v>6580400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6290700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6231700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6161800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6525300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6833900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6939500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6285700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6016500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5727200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4807600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4329100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4487800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4166700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3725300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3600800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4021000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5073500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5496700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11174200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5646400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5756300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6145500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1108400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1175700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1110100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1049500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>388100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>989900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1070700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1093800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1041700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1030100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1232300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>911400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>836800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>635600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>649000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>587400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>569600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>679500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>648300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>643800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>780500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1290500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1233600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1217000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18214200</v>
+      </c>
+      <c r="E46" s="3">
         <v>18524700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18036300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18145000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19135900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18775800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19057400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18996800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17839800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16774000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17146200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15583800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15752000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16329200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16719800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17354700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15059700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15149100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16337500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15376800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17476700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16364300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17415900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17774800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1469900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1726500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1675400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1754900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1658200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1527400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1458100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1613300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1018200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>991400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1107900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1065600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1137000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1145100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1145500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1050000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1009800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1054200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1276800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1505300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2990000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1752500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1842600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2137000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13795100</v>
+      </c>
+      <c r="E48" s="3">
         <v>14208000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13743900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14035000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14597100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13522800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13776800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13997300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13191400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11939700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12426800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11674800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11829900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12035900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12457000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12007200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12331000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13384700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15078000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15667800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31118800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13721000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13711500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14610900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2314700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2449000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2405800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2459600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2489000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2358800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2276000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2295100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2103900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1948300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1972300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1826000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1787000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1807800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1487700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1428300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1576900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1642100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1787900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1829400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3799400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1743200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1768700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>861500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>957700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>954200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>903400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>891800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>949500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>992600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>988400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>656000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>657700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,16 +4956,19 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>10</v>
@@ -4857,95 +4976,98 @@
       <c r="G52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>1078400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1084900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1110900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>994800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>923600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>785600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>797700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>746000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>730400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>798900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>893400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>901800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1805500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1353500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1388500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>998600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>934800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>965000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36404500</v>
+      </c>
+      <c r="E54" s="3">
         <v>37559200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36463500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36966900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38505500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36895700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37288300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37574600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35231600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32738300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33764200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31145100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31429500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32103700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32607800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32586200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>30707800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32029000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>35373500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35281000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>38963600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34934500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>36127200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36842700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3884400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3551700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3727700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3708000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4251100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3580400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3653900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3864900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4313200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3627300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3655800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3255900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3551900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3032400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3076400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2733400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3079600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2599700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2589600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3128200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5968100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1835100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2026300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2185100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1306800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1485700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1318000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1995700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2265700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2267800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2324600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1638200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1929500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1139600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1039500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1302700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1407200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1552700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1560400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2710100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2550400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2969700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3632300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1617000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2949000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1745500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2089300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2235600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2280500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2693900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2489000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2403000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1971100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2810500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2626300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2624300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2232300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2532900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2690700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2342100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2071700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2121400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2131300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2479300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2006000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2082500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1936300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2027200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6356000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3969500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4052700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4241900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7471700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7731300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7534600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8106600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8965200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8658600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8604800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8127400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7709200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7299800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7386100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6900800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7030800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6706400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6768200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7922700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7636000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7651900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8158200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6772400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8156500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7550100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8168300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8662700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3321900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3549000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3354600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3474300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3623500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3445300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3520800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4397200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4283200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3957800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4174500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4008900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4165300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4321900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4445000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4555600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4825000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5152000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5627300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5787000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5978000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4133900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4137000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2442500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E62" s="3">
         <v>417200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>410000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>416600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>450000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>428800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>460400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>448000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1850500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1753800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1952700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1847700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1853700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2048700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2108100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2041900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2155300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2277400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2570900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2755700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4777500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2594100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2650800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2918600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12320500</v>
+      </c>
+      <c r="E66" s="3">
         <v>12939500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12515000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13243900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14347300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13816000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13955500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14444400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14174200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13321000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13840300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13072000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13362200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13379600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13639700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14844900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14948600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15423000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16749200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15745300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17560800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14744100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15439800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14541300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18247200</v>
+      </c>
+      <c r="E72" s="3">
         <v>19720800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17674400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18047000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19233700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>17720300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18197900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19034300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17756600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>15202300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15804000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15308800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15874300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16784800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>17007300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15925300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14682900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15438900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>17177700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18111900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>44028300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>22532700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22193000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22722500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23734900</v>
+      </c>
+      <c r="E76" s="3">
         <v>24275400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23626800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23374600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23790800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22735600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22987500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22760000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21057400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19417300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19923900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18073100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18067300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18724100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18968100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17741300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15759200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16606100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>18624400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19535800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>21402800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20190400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20687400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>22301400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,117 +7534,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7481,86 +7675,89 @@
       <c r="J81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L81" s="3">
         <v>792100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>611200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>263600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>357500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-197900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>508500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>493000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2022400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-354100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>171600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>469700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>825800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>393100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>536100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>681400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>788200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>647300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>576300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>818200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>596000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>656300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>525400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>731700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>555300</v>
+      </c>
+      <c r="E83" s="3">
         <v>541300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>514800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>543400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>550200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>522200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>503000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>540500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>515200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>482100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>460700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>435800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>444600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>461700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>442800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>435700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>498300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>516900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>565200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>589000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>627500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>642000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>648500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>644800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>479300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>503300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>444400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>465300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>489800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>473600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>440100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>440600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>428800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,88 +8434,91 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1452500</v>
+      </c>
+      <c r="E89" s="3">
         <v>760500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>515700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>850100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1681000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1259200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>806300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>901400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1025800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>913600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>138100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>399400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>416000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>180000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>644200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1553400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1323100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>691700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>564600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1895100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>694900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>888100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1172900</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -8325,8 +8541,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,88 +8582,89 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-543800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-454400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-361100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-599100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-616800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-392100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-376300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-620900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-196600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-349000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-376900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-364000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-325900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-566700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-626200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-678600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-523100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8467,8 +8687,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,88 +8901,91 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-511800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-502100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-645700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-695800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-476100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-334600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-602900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-430700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-276600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-491600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-352700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-598100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-175200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2055000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-292400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-382600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-522200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-44100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-358100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8779,8 +9008,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8843,57 +9076,57 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3">
         <v>-700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-376900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-4100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-393400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-430900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-293600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-273700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-5900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-490000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-528100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-572200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8921,8 +9154,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,88 +9475,91 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-207900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-511900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-763600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-756300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-257000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-573600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-129200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-323900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-288400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-595700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-645100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-892400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-210100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-526400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-326200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-385600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-724900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1947000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-568400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-230900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1278300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -9337,88 +9582,91 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-160500</v>
+      </c>
+      <c r="E101" s="3">
         <v>21500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>299400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>12100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-370400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>114100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>427100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>324900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-346800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>105400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>391200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>262000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>110000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-57400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>316500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>28100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-53300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>82200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-164300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>102700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-89500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-56300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>67800</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -9441,88 +9689,91 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>958500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-649200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-78600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-411900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>567700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>230900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>641900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-612000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-392400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-722700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-430700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-740900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2689400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1095400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>252500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2338300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-690300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1329100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>564100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-648100</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
@@ -9543,6 +9794,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,155 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,86 +836,89 @@
       <c r="K8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="3">
         <v>8045300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6957900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6708500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5916300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5800300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5820400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5756600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5156000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5065500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5774300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4752500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6217800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8048800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8122100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8168200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8151300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,86 +946,89 @@
       <c r="K9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="3">
         <v>4924000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4264200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4114800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3615000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3318300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3396300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3395600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3069100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2818700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3709400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3230500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3894700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5024300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4951200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5149100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5094700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1046,86 +1056,89 @@
       <c r="K10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="3">
         <v>3121400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2693700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2593700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2301300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2482000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2424100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2361000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2086900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2246800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2064900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1522000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2323200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>3024500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3170900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3019100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3056600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,86 +1206,89 @@
       <c r="K12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="3">
         <v>216200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>179000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>184100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>175100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>157300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>163000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>168300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>159200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>126200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>173000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>186300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>229200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>252500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>235800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>252200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>243000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>269400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>238200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>228100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>220800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>241900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>216700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>232200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>215600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1377,8 +1394,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1406,86 +1426,89 @@
       <c r="K14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="3">
         <v>36300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>85700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>49900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>39800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>487000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>682000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>383400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>47500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>190200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>41600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>100300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-103500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3">
         <v>99800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>9300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>58400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>39200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1513,86 +1536,89 @@
       <c r="K15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3">
         <v>187900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>173000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>165700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>154300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>158200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>161700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>161900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>156500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>159000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>171800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>179100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>193000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>312700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>310900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>200000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>203500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>85000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>84700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>79500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>78600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>80500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>76300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>73000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>72800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>71300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,8 +1653,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1656,86 +1683,89 @@
       <c r="K17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="3">
         <v>7093500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6107900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6126500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5334400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5037600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5098300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5071600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4565000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4771800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5669200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5164900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5873400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7408900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6921500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7573700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7348300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1763,86 +1793,89 @@
       <c r="K18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M18" s="3">
         <v>951900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>850100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>582100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>581900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>762800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>722100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>684900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>591000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>293700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>105100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-412500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>344400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>640000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1200600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>594400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>803000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1058100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>904800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>908100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>978800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>874100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>888200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>855800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,8 +1913,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1909,86 +1943,89 @@
       <c r="K20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="3">
         <v>-77100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-33000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>56400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>32100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>13800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>17500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>23500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-23300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-24000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>76900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>18700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>109100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>19900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>231400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>77600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>25400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>47400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2016,86 +2053,89 @@
       <c r="K21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="3">
         <v>1390000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1299100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1068500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1074100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1239400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1197600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1145300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1050200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>795700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>631400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>129400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>909400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1339200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1831800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1442400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2123,86 +2163,89 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
         <v>28800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>31800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>32800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>57400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>66700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>59900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>27700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>34100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>31600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>38200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>28500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>19500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2230,86 +2273,89 @@
       <c r="K23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3">
         <v>846000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>792000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>586800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>618200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>773800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>715000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>683500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>596000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>278300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>90600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-467600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>287500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>659500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1153400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>546500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>749100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>890600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>843500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>927100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>885100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>801000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2337,86 +2383,89 @@
       <c r="K24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3">
         <v>212800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>144600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>224100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>176800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>178100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>172500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>130600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>123500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>154300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-54500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>117800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>184000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>311900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>138400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>192000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>447300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>269000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>226900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>242800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>331900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>307100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>212300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>255800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>298900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,8 +2571,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2551,86 +2603,89 @@
       <c r="K26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="3">
         <v>633200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>647400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>362700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>441400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>799600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>536900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>511000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>465400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>154800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-63700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-413100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>169800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>475500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>841500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>408100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>557100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>695400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>808300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>663700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>600600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>840100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>620100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>672800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>545200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>755300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2658,86 +2713,89 @@
       <c r="K27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M27" s="3">
         <v>626600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>635400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>351700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>434400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>789800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>527900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>448400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>148300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-76400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>147700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>469700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>825800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>393100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>536100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>681400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>788200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>647300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>576300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>818200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>596000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>656300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>525400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>731700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,50 +2933,50 @@
       <c r="K29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="3">
         <v>165500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-24200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-88100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-76900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-987700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-19400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-7500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1574000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-142300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>60300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>46600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>23900</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,8 +3231,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3193,86 +3263,89 @@
       <c r="K32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="3">
         <v>77100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>33000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-56400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-13800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-17500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-23500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>23300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>24000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-76900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>24800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>33000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>36800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3300,86 +3373,89 @@
       <c r="K33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M33" s="3">
         <v>792100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>611200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>263600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>357500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-197900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>508500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>493000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2022400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-354100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>171600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>469700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>825800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>393100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>536100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>681400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>788200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>647300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>576300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>818200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>596000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>656300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>525400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>731700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,8 +3561,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3514,198 +3593,204 @@
       <c r="K35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="3">
         <v>792100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>611200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>263600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>357500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-197900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>508500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>493000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2022400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-354100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>171600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>469700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>825800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>393100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>536100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>681400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>788200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>647300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>576300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>818200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>596000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>656300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>525400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>731700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,115 +3868,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3951100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4495200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3883400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4035300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4377200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5140400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4316800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4215700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3889200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3684200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3346700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4182100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4506600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5410400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6130200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7004500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8436200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5941300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5150000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5362800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3123800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3943900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2740700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3982700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3636300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3919,834 +4009,858 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>107300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>146200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>63000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>65700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>80900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>54100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>51600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>45100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>53300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>51500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>86200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>155300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1369700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1356600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1323100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1240800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6598000</v>
+        <v>6466400</v>
       </c>
       <c r="E43" s="3">
+        <v>6917300</v>
+      </c>
+      <c r="F43" s="3">
         <v>6885100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6600300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6486700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7081000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6943800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6937100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7074300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6720900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6234400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5941600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5292500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5094900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5021400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4848000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4560700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4894700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5247200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5166800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5957200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>11999600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5330100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5120200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5535200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6196600</v>
+      </c>
+      <c r="E44" s="3">
         <v>6012500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6580400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6290700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6231700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6161800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6525300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6833900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6939500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6285700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6016500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5727200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4807600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4329100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4487800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4166700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3725300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3600800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4021000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5073500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5496700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>11174200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5646400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5756300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6145500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1108400</v>
+        <v>1148900</v>
       </c>
       <c r="E45" s="3">
+        <v>422400</v>
+      </c>
+      <c r="F45" s="3">
         <v>1175700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1110100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1049500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>388100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>989900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1070700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1093800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1041700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1030100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1232300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>911400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>836800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>635600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>649000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>587400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>569600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>679500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>648300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>643800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>780500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1290500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1233600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1217000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17763000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18214200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18524700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18036300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18145000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19135900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18775800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19057400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18996800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17839800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16774000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17146200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15583800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15752000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16329200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16719800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17354700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15059700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15149100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16337500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15376800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17476700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16364300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17415900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17774800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>299800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1469900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1726500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1675400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1754900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1658200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1527400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1458100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1613300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1018200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>991400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1107900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1065600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1145100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1145500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1050000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1009800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1054200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1276800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1505300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2990000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1752500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1842600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2137000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13784900</v>
+      </c>
+      <c r="E48" s="3">
         <v>13795100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14208000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13743900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14035000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14597100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13522800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13776800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13997300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13191400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11939700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12426800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11674800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11829900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12035900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12457000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12007200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12331000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13384700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>15078000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15667800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>31118800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13721000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13711500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14610900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2391600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2314700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2449000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2405800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2459600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2489000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2358800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2276000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2295100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2103900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1948300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1972300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1826000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1787000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1807800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1487700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1428300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1576900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1642100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1787900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1829400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3799400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1743200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1768700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>861500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>957700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>954200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>903400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>891800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>949500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>992600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>988400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>656000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>657700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,19 +5076,22 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3">
+        <v>1152400</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -4979,95 +5099,98 @@
       <c r="H52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>1078400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1084900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1110900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>994800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>923600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>785600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>797700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>746000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>730400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>798900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>893400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>901800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1805500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1353500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1388500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>998600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>934800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>965000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36035600</v>
+      </c>
+      <c r="E54" s="3">
         <v>36404500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37559200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36463500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36966900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38505500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36895700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37288300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37574600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35231600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32738300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33764200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31145100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31429500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32103700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32607800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32586200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>30707800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32029000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>35373500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35281000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>38963600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34934500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>36127200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36842700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3361400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3884400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3551700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3727700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3708000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4251100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3580400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3653900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3864900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4313200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3627300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3655800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3255900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3551900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3032400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3076400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2733400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3079600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2599700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2589600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3128200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5968100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1835100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2026300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2185100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1224600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1306800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1485700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1318000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1995700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2265700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2267800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2324600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1638200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1929500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1139600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1039500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1302700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1407200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1552700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1560400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2710100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2550400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2969700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3632300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1617000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2949000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1745500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2089300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2235600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2280500</v>
+        <v>2547100</v>
       </c>
       <c r="E59" s="3">
+        <v>1825900</v>
+      </c>
+      <c r="F59" s="3">
         <v>2693900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2489000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2403000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1971100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2810500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2626300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2624300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2232300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2532900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2690700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2342100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2071700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2121400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2131300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2479300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2006000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2082500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1936300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2027200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6356000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3969500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4052700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4241900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7133100</v>
+      </c>
+      <c r="E60" s="3">
         <v>7471700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7731300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7534600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8106600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8965200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8658600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8604800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8127400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7709200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7299800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7386100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6900800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7030800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6706400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6768200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7922700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7636000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7651900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8158200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>6772400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8156500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>7550100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8168300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8662700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3374800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3321900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3549000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3354600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3474300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3623500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3445300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3520800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4397200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4283200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3957800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4174500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4008900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4165300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4321900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4445000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4555600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4825000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5152000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5627300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5787000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5978000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4133900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4137000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2442500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>345000</v>
+      </c>
+      <c r="E62" s="3">
         <v>394000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>417200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>410000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>416600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>450000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>428800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>460400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>448000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1850500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1753800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1952700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1847700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1853700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2048700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2108100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2041900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2155300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2277400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2570900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2755700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4777500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2594100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2650800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2918600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11970600</v>
+      </c>
+      <c r="E66" s="3">
         <v>12320500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12939500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12515000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13243900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14347300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13816000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13955500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14444400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14174200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13321000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13840300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13072000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13362200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13379600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13639700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14844900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14948600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15423000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16749200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15745300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17560800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14744100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15439800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14541300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19213000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18247200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19720800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17674400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18047000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19233700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17720300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18197900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19034300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17756600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>15202300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15804000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15308800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15874300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16784800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17007300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15925300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14682900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15438900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>17177700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18111900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>44028300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>22532700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22193000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22722500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23721100</v>
+      </c>
+      <c r="E76" s="3">
         <v>23734900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>24275400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23626800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23374600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23790800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22735600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22987500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22760000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21057400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19417300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19923900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18073100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18067300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18724100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18968100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17741300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15759200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16606100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>18624400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>19535800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>21402800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>20190400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20687400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>22301400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,120 +7726,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7678,86 +7873,89 @@
       <c r="K81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M81" s="3">
         <v>792100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>611200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>263600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>357500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-197900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>508500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>493000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2022400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-354100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>171600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>469700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>825800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>393100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>536100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>681400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>788200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>647300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>576300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>818200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>596000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>656300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>525400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>731700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>562400</v>
+      </c>
+      <c r="E83" s="3">
         <v>555300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>541300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>514800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>543400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>550200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>522200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>503000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>540500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>515200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>482100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>460700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>435800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>444600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>461700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>442800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>435700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>498300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>516900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>565200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>589000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>627500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>642000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>648500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>644800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>479300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>503300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>444400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>465300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>489800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>473600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>440100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>440600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>428800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,91 +8651,94 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1134400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1452500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>760500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>515700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>850100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1681000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1259200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>806300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>901400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1025800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>913600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>138100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>399400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>416000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>180000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>644200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1553400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1323100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>691700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>564600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1895100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>694900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>888100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1172900</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AD89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -8544,8 +8761,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,91 +8803,92 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-511400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-543800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-454400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-361100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-599100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-616800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-392100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-376300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-620900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-196600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-349000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-376900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-364000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-325900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-566700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-626200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-678600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8690,8 +8911,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,91 +9131,94 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-524800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-511800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-502100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-645700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-695800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-476100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-334600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-602900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-430700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-276600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-491600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-352700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-598100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-175200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2055000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-292400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-382600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-522200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-44100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-358100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9011,8 +9241,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,13 +9283,14 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
+      <c r="D96" s="3">
+        <v>474500</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>10</v>
@@ -9079,57 +9313,57 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
         <v>-700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-376900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-4100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-393400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-430900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-6100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-293600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-273700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-5900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-490000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-528100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-572200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -9157,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,91 +9721,94 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1125700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-207900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-511900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-763600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-756300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-257000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-573600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-129200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-323900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-288400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-595700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-645100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-892400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-526400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-326200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-385600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-724900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1947000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-568400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-230900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1278300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -9585,91 +9831,94 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-160500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>21500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>299400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-370400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>114100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>427100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>324900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-346800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>105400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>391200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>262000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>110000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-32400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-57400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>316500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>28100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-53300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>82200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-164300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>102700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-89500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-56300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>67800</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
+      <c r="AD101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE101" s="3">
         <v>0</v>
@@ -9692,91 +9941,94 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-769000</v>
+      </c>
+      <c r="E102" s="3">
         <v>958500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-649200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-411900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>567700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>230900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>641900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-612000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-392400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-722700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-430700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-740900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2689400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1095400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>252500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2338300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-690300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1329100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>564100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-648100</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AD102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -9797,6 +10049,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,86 +843,89 @@
       <c r="L8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="3">
         <v>8045300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6957900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6708500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5916300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5800300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5820400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5756600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5156000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5065500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5774300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4752500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6217800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8048800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8122100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8168200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8151300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,86 +956,89 @@
       <c r="L9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="3">
         <v>4924000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4264200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4114800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3615000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3318300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3396300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3395600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3069100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2818700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3709400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3230500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3894700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5024300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4951200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5149100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5094700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,86 +1069,89 @@
       <c r="L10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="3">
         <v>3121400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2693700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2593700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2301300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2482000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2424100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2361000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2086900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2246800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2064900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1522000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2323200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>3024500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3170900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3019100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3056600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,86 +1223,89 @@
       <c r="L12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
         <v>216200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>179000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>184100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>175100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>157300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>163000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>168300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>159200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>126200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>173000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>186300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>229200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>252500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>235800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>252200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>243000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>269400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>238200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>228100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>220800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>241900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>216700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>232200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>207300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>215600</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1397,8 +1414,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1429,86 +1449,89 @@
       <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3">
         <v>36300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>85700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>49900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>39800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>487000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>682000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>383400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>47500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>190200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>41600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-103500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AF14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>99800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>58400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>39200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1539,86 +1562,89 @@
       <c r="L15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="3">
         <v>187900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>173000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>165700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>154300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>158200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>161700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>161900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>156500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>159000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>171800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>179100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>193000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>312700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>310900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>200000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>203500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>85000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>84700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>79500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>78600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>80500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>76300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>72800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>71300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,8 +1680,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1686,86 +1713,89 @@
       <c r="L17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" s="3">
         <v>7093500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6107900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6126500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5334400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5037600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5098300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5071600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4565000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4771800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5669200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5164900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5873400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7408900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6921500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7573700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7348300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1796,86 +1826,89 @@
       <c r="L18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="3">
         <v>951900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>850100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>582100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>581900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>762800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>722100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>684900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>591000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>293700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>105100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-412500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>344400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>640000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1200600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>594400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>803000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1058100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>904800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>908100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>978800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>874100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>888200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>855800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,8 +1947,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1946,86 +1980,89 @@
       <c r="L20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="3">
         <v>-77100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-33000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>56400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>32100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>13800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>17500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>23500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-23300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>76900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>18700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>109100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>19900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>231400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>77600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>25400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>47400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2056,86 +2093,89 @@
       <c r="L21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N21" s="3">
         <v>1390000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1299100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1068500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1074100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1239400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1197600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1145300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1050200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>795700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>631400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>129400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>909400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1339200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1831800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1442400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2166,86 +2206,89 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>28800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>32800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>57400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>66700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>34100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>31600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>38200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>28500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>17900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>19500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2276,86 +2319,89 @@
       <c r="L23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="3">
         <v>846000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>792000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>586800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>618200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>773800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>715000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>683500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>596000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>278300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>90600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-467600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>287500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>659500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1153400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>546500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>749100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>890600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>843500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>927100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>885100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>801000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2386,86 +2432,89 @@
       <c r="L24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" s="3">
         <v>212800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>144600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>224100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>176800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-25800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>178100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>172500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>130600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>123500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>154300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-54500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>117800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>184000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>311900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>138400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>192000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>447300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>269000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>226900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>242800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>331900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>307100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>212300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>255800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>298900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,8 +2623,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2606,86 +2658,89 @@
       <c r="L26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="3">
         <v>633200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>647400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>362700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>441400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>799600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>536900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>511000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>465400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>154800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-63700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-413100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>169800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>475500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>841500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>408100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>557100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>695400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>808300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>663700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>600600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>840100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>620100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>672800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>545200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>755300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2716,86 +2771,89 @@
       <c r="L27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" s="3">
         <v>626600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>635400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>351700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>434400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>789800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>527900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>448400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>148300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-76400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>147700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>469700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>825800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>393100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>536100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>681400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>788200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>647300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>576300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>818200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>596000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>656300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>525400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>731700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,50 +2997,50 @@
       <c r="L29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N29" s="3">
         <v>165500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-24200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-88100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-76900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-987700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-19400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-7500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1574000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-142300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>60300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>46600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>23900</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,8 +3301,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3266,86 +3336,89 @@
       <c r="L32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="3">
         <v>77100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>33000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-32100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-13800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-17500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-23500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>23300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>24000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-76900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>24800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>33000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>36800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3376,86 +3449,89 @@
       <c r="L33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="3">
         <v>792100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>611200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>263600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>357500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-197900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>508500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>493000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2022400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-354100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>171600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>469700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>825800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>393100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>536100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>681400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>788200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>647300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>576300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>818200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>596000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>656300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>525400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>731700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,8 +3640,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3596,201 +3675,207 @@
       <c r="L35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N35" s="3">
         <v>792100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>611200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>263600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>357500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-197900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>508500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>493000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2022400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-354100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>171600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>469700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>825800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>393100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>536100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>681400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>788200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>647300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>576300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>818200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>596000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>656300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>525400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>731700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,118 +3955,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3951100</v>
-      </c>
-      <c r="E41" s="3">
+        <v>4788600</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3">
         <v>4495200</v>
       </c>
-      <c r="F41" s="3">
-        <v>3883400</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="3">
         <v>4035300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4377200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5140400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4316800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4215700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3889200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3684200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3346700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4182100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4506600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5410400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6130200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7004500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8436200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5941300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5150000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5362800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3123800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3943900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2740700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3982700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3636300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4012,855 +4102,879 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>107300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>146200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>63000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>65700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>80900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>54100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>51600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>45100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>53300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>51500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>86200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>155300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1369700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1356600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1323100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1240800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6466400</v>
-      </c>
-      <c r="E43" s="3">
+        <v>6827800</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="3">
         <v>6917300</v>
       </c>
-      <c r="F43" s="3">
-        <v>6885100</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="3">
         <v>6600300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6486700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7081000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6943800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6937100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7074300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6720900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6234400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5941600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5292500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5094900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5021400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4848000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4560700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4894700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5247200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5166800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5957200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>11999600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5330100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5120200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5535200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6196600</v>
-      </c>
-      <c r="E44" s="3">
+        <v>6356000</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3">
         <v>6012500</v>
       </c>
-      <c r="F44" s="3">
-        <v>6580400</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3">
         <v>6290700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6231700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6161800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6525300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6833900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6939500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6285700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6016500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5727200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4807600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4329100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4487800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4166700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3725300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3600800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4021000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5073500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5496700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>11174200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5646400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5756300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6145500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1148900</v>
-      </c>
-      <c r="E45" s="3">
+        <v>1423900</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
         <v>422400</v>
       </c>
-      <c r="F45" s="3">
-        <v>1175700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="3">
         <v>1110100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1049500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>388100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>989900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1070700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1093800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1041700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1030100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1232300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>911400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>836800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>635600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>649000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>587400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>569600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>679500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>648300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>643800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>780500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1290500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1233600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1217000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>17763000</v>
-      </c>
-      <c r="E46" s="3">
+        <v>19396200</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3">
         <v>18214200</v>
       </c>
-      <c r="F46" s="3">
-        <v>18524700</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="3">
         <v>18036300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18145000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19135900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18775800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19057400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18996800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17839800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16774000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17146200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15583800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15752000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16329200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16719800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17354700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15059700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15149100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16337500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15376800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17476700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16364300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17415900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17774800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>299800</v>
-      </c>
-      <c r="E47" s="3">
+        <v>1450900</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3">
         <v>1469900</v>
       </c>
-      <c r="F47" s="3">
-        <v>1726500</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3">
         <v>1675400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1754900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1658200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1527400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1458100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1613300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1018200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>991400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1107900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1065600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1137000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1145100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1145500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1050000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1009800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1054200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1276800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1505300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2990000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1752500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1842600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2137000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13784900</v>
-      </c>
-      <c r="E48" s="3">
+        <v>14004200</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="3">
         <v>13795100</v>
       </c>
-      <c r="F48" s="3">
-        <v>14208000</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="3">
         <v>13743900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14035000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14597100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13522800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13776800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13997300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13191400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11939700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12426800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11674800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11829900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12035900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12457000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12007200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12331000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13384700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>15078000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15667800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>31118800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13721000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13711500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14610900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2391600</v>
-      </c>
-      <c r="E49" s="3">
+        <v>2464300</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="3">
         <v>2314700</v>
       </c>
-      <c r="F49" s="3">
-        <v>2449000</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49" s="3">
         <v>2405800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2459600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2489000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2358800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2276000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2295100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2103900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1948300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1972300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1826000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1787000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1807800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1487700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1428300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1576900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1642100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1787900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1829400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3799400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1743200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1768700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>861500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>957700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>954200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>903400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>891800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>949500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>992600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>988400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>656000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>657700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,19 +5196,22 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1152400</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -5102,95 +5222,98 @@
       <c r="I52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>1078400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1084900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1110900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>994800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>923600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>785600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>797700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>746000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>730400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>798900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>893400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>901800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1805500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1353500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1388500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>998600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>934800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>965000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36035600</v>
-      </c>
-      <c r="E54" s="3">
+        <v>37990700</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="3">
         <v>36404500</v>
       </c>
-      <c r="F54" s="3">
-        <v>37559200</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" s="3">
         <v>36463500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36966900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38505500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36895700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37288300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37574600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35231600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32738300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33764200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31145100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31429500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32103700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32607800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32586200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>30707800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32029000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>35373500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35281000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>38963600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34934500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>36127200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36842700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3361400</v>
-      </c>
-      <c r="E57" s="3">
+        <v>3510700</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="3">
         <v>3884400</v>
       </c>
-      <c r="F57" s="3">
-        <v>3551700</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="3">
         <v>3727700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3708000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4251100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3580400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3653900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3864900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4313200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3627300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3655800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3255900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3551900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3032400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3076400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2733400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3079600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2599700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2589600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3128200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5968100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1835100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2026300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2185100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1224600</v>
-      </c>
-      <c r="E58" s="3">
+        <v>1315100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="3">
         <v>1306800</v>
       </c>
-      <c r="F58" s="3">
-        <v>1485700</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="3">
         <v>1318000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1995700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2265700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2267800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2324600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1638200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1929500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1139600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1039500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1302700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1407200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1552700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1560400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2710100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2550400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2969700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3632300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1617000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2949000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1745500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2089300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2235600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2547100</v>
-      </c>
-      <c r="E59" s="3">
+        <v>2725400</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
         <v>1825900</v>
       </c>
-      <c r="F59" s="3">
-        <v>2693900</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="3">
         <v>2489000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2403000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1971100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2810500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2626300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2624300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2232300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2532900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2690700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2342100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2071700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2121400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2131300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2479300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2006000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2082500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1936300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2027200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6356000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3969500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4052700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4241900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7133100</v>
-      </c>
-      <c r="E60" s="3">
+        <v>7551300</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="3">
         <v>7471700</v>
       </c>
-      <c r="F60" s="3">
-        <v>7731300</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="3">
         <v>7534600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8106600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8965200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8658600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8604800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8127400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7709200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7299800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7386100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6900800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7030800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6706400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6768200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7922700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7636000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7651900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>8158200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>6772400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>8156500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>7550100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8168300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8662700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3374800</v>
+        <v>4198300</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>3321900</v>
       </c>
-      <c r="F61" s="3">
-        <v>3549000</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>3354600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3474300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3623500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3445300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3520800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4397200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4283200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3957800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4174500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4008900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4165300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4321900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4445000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4555600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4825000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5152000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5627300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5787000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5978000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4133900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4137000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2442500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>345000</v>
-      </c>
-      <c r="E62" s="3">
+        <v>585100</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3">
         <v>394000</v>
       </c>
-      <c r="F62" s="3">
-        <v>417200</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="3">
         <v>410000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>416600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>450000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>428800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>460400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>448000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1850500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1753800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1952700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1847700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1853700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2048700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2108100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2041900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2155300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2277400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2570900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2755700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4777500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2594100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2650800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2918600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11970600</v>
-      </c>
-      <c r="E66" s="3">
+        <v>13470300</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="3">
         <v>12320500</v>
       </c>
-      <c r="F66" s="3">
-        <v>12939500</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="3">
         <v>12515000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13243900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14347300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13816000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13955500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14444400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14174200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13321000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13840300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13072000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13362200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13379600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13639700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14844900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14948600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>15423000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16749200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15745300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17560800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>14744100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15439800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14541300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19213000</v>
-      </c>
-      <c r="E72" s="3">
+        <v>20217500</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="3">
         <v>18247200</v>
       </c>
-      <c r="F72" s="3">
-        <v>19720800</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="3">
         <v>17674400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18047000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19233700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17720300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18197900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19034300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17756600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>15202300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15804000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15308800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15874300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16784800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>17007300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15925300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14682900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15438900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>17177700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18111900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>44028300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>22532700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22193000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22722500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>23721100</v>
-      </c>
-      <c r="E76" s="3">
+        <v>24161100</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="3">
         <v>23734900</v>
       </c>
-      <c r="F76" s="3">
-        <v>24275400</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H76" s="3">
         <v>23626800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23374600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23790800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22735600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22987500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22760000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21057400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19417300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19923900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18073100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18067300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18724100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18968100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17741300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15759200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16606100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18624400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>19535800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>21402800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>20190400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20687400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>22301400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,123 +7918,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7876,86 +8071,89 @@
       <c r="L81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N81" s="3">
         <v>792100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>611200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>263600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>357500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-197900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>508500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>493000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2022400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-354100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>171600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>469700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>825800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>393100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>536100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>681400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>788200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>647300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>576300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>818200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>596000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>656300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>525400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>731700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>544700</v>
+      </c>
+      <c r="E83" s="3">
         <v>562400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>555300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>541300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>514800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>543400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>550200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>522200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>503000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>540500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>515200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>482100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>460700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>435800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>444600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>461700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>442800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>435700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>498300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>516900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>565200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>589000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>627500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>642000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>648500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>644800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>479300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>503300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>444400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>465300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>489800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>473600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>440100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>440600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>428800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,94 +8868,97 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1134400</v>
-      </c>
-      <c r="E89" s="3">
+        <v>757200</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="3">
         <v>1452500</v>
       </c>
-      <c r="F89" s="3">
-        <v>760500</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" s="3">
         <v>515700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>850100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1681000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1259200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>806300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>901400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1025800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>913600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>138100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>399400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>22200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>416000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>180000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>644200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1553400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1323100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>691700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>564600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1895100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>694900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>888100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1172900</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
@@ -8764,8 +8981,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,94 +9024,95 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-511400</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-328000</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="3">
         <v>-543800</v>
       </c>
-      <c r="F91" s="3">
-        <v>-454400</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H91" s="3">
         <v>-361100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-599100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-616800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-392100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-376300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-620900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-196600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-349000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-376900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-364000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-325900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-566700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-626200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-678600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -8914,8 +9135,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,94 +9361,97 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-524800</v>
-      </c>
-      <c r="E94" s="3">
+        <v>-293200</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="3">
         <v>-511800</v>
       </c>
-      <c r="F94" s="3">
-        <v>-502100</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="3">
         <v>-31100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-645700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-695800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-476100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-334600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-602900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-430700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-276600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-491600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-352700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-598100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-175200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2055000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-100500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-292400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-382600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-522200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-44100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-358100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -9244,8 +9474,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,13 +9517,14 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>474500</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>10</v>
@@ -9316,57 +9550,57 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3">
         <v>-700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-376900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-4100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-393400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-430900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-6100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-293600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-273700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-5900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-490000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-528100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-572200</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -9394,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,94 +9967,97 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1125700</v>
-      </c>
-      <c r="E100" s="3">
+        <v>223300</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="3">
         <v>-207900</v>
       </c>
-      <c r="F100" s="3">
-        <v>-511900</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="3">
         <v>-763600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-756300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-257000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-573600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-129200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-323900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-288400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-595700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-645100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-892400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-210100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-526400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-326200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-385600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-724900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1947000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-568400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-230900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1278300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -9834,94 +10080,97 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E101" s="3">
         <v>139900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-160500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>21500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>299400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-370400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>114100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>427100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>324900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-346800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>105400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>391200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>262000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>110000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-32400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-57400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>316500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>28100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-53300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>82200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-164300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>102700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-56300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>67800</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AE101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -9944,94 +10193,97 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-769000</v>
+        <v>703400</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>958500</v>
       </c>
-      <c r="F102" s="3">
-        <v>-649200</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-78600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-411900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>567700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>230900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>641900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-612000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-392400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-722700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-430700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-740900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2689400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1095400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>252500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2338300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-690300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1329100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>564100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-648100</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF102" s="3">
         <v>0</v>
@@ -10052,6 +10304,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -9524,26 +9524,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
+      <c r="D96" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>700</v>
+      </c>
+      <c r="F96" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G96" s="3">
+        <v>447300</v>
+      </c>
+      <c r="H96" s="3">
+        <v>600</v>
+      </c>
+      <c r="I96" s="3">
+        <v>457700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>5500</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>10</v>

--- a/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BRDCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>BRDCY</t>
   </si>
@@ -656,164 +656,168 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -847,86 +851,89 @@
       <c r="M8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" s="3">
         <v>8045300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6957900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6708500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5916300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5800300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5820400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5756600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5156000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5065500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5774300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4752500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6217800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8048800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8122100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8168200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8151300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>9212700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8349700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8322400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7816100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8862300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8318900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8054200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7556300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7913900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7080300</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -960,86 +967,89 @@
       <c r="M9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="3">
         <v>4924000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4264200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4114800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3615000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3318300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3396300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3395600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3069100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2818700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3709400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3230500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3894700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5024300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4951200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5149100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5094700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5770100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5275700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5136800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4767700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5507100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5290700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4957100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4610500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4741000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4175500</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1073,86 +1083,89 @@
       <c r="M10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="3">
         <v>3121400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2693700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2593700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2301300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2482000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2424100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2361000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2086900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2246800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2064900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1522000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2323200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>3024500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>3170900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3019100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3056600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3442500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3074000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3185600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3048400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3355200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3028200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3097100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2945800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3172900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>2904900</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1192,8 +1205,9 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1227,86 +1241,89 @@
       <c r="M12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3">
         <v>216200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>179000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>184100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>175100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>157300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>163000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>168300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>159200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>126200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>173000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>186300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>229200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>252500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>235800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>252200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>243000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>269400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>238200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>228100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>220800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>241900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>216700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>232200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>207300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>215600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>204000</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1418,8 +1435,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1453,86 +1473,89 @@
       <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="3">
         <v>36300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>85700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>49900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>26900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>39800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>487000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>682000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>383400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>47500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>190200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>41600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-103500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-280400</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AG14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="3">
         <v>99800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>58400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>39200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>95700</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1566,86 +1589,89 @@
       <c r="M15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="3">
         <v>187900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>173000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>165700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>154300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>158200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>161700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>161900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>156500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>159000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>171800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>179100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>193000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>312700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>310900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>200000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>203500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>85000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>84700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>79500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>78600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>80500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>76300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>73000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>72800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>71300</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>70300</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1682,8 +1708,9 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1717,86 +1744,89 @@
       <c r="M17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3">
         <v>7093500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6107900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6126500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5334400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5037600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5098300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5071600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4565000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4771800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5669200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5164900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5873400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7408900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6921500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7573700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7348300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8154600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7219900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7417600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6908000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7883500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7444900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7166000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6700500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6887600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6189800</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1830,86 +1860,89 @@
       <c r="M18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="3">
         <v>951900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>850100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>582100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>581900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>762800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>722100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>684900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>591000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>293700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>105100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-412500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>344400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>640000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1200600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>594400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>803000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1058100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1129800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>904800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>908100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>978800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>874100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>888200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>855800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1026300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>890500</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1949,8 +1982,9 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1984,86 +2018,89 @@
       <c r="M20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3">
         <v>-77100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-33000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>56400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>32100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>13800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>17500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>23500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>9400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>76900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>18700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>109100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-33000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>231400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>77600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>25400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-36800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>47400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-18200</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2097,86 +2134,89 @@
       <c r="M21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3">
         <v>1390000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1299100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1068500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1074100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1239400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1197600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1145300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1050200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>795700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>631400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>129400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>909400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1339200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1831800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1238200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1442400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1646500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1608300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1369100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1340400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1700000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1425200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1353700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1259500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1502500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1297500</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2210,86 +2250,89 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3">
         <v>28800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>31800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>32800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>57400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>59900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>66700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>59900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>27700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>34100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>31600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>38200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>28500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>17900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>19500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2323,86 +2366,89 @@
       <c r="M23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O23" s="3">
         <v>846000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>792000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>586800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>618200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>773800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>715000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>683500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>596000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>278300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>90600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-467600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>287500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>659500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1153400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>546500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>749100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1142600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1077300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>890600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>843500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1172000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>927100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>885100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>801000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1054200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>848500</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2436,86 +2482,89 @@
       <c r="M24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O24" s="3">
         <v>212800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>144600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>224100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>176800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-25800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>178100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>172500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>130600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>123500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>154300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-54500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>117800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>184000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>311900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>138400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>192000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>447300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>269000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>226900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>242800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>331900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>307100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>212300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>255800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>298900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>298600</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2627,8 +2676,11 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2662,86 +2714,89 @@
       <c r="M26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O26" s="3">
         <v>633200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>647400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>362700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>441400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>799600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>536900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>511000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>465400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>154800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-63700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-413100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>169800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>475500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>841500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>408100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>557100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>695400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>808300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>663700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>600600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>840100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>620100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>672800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>545200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>755300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>549900</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2775,86 +2830,89 @@
       <c r="M27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" s="3">
         <v>626600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>635400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>351700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>434400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>789800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>527900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>448400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>148300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-76400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-400700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>147700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>469700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>825800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>393100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>536100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>681400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>788200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>647300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>576300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>818200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>596000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>656300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>525400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>731700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2966,8 +3024,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3001,50 +3062,50 @@
       <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="3">
         <v>165500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-24200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-88100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-76900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-987700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-19400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1574000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-142300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>60300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>46600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>23900</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -3079,8 +3140,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3192,8 +3256,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3305,8 +3372,11 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3340,86 +3410,89 @@
       <c r="M32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O32" s="3">
         <v>77100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>33000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-56400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-32100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-13800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-17500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-23500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-9400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>23300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>24000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-76900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-109100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>24800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>33000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-231400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-77600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-25400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>36800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3453,86 +3526,89 @@
       <c r="M33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3">
         <v>792100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>611200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>263600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>357500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-197900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>508500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>493000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2022400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-354100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>171600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>469700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>825800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>393100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>536100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>681400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>788200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>647300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>576300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>818200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>596000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>656300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>525400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>731700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3644,8 +3720,11 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3679,204 +3758,210 @@
       <c r="M35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="3">
         <v>792100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>611200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>263600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>357500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-197900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>508500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>493000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2022400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-354100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>171600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>469700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>825800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>393100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>536100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>681400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>788200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>647300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>576300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>818200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>596000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>656300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>525400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>731700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3916,8 +4001,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3957,121 +4043,125 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4552700</v>
+      </c>
+      <c r="E41" s="3">
         <v>4788600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4495200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4035300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4377200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5140400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4316800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4215700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4316800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4215700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3889200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3684200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3346700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4182100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4506600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5410400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6130200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7004500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8436200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5941300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5150000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5362800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3123800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3943900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2740700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3982700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3636300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4157200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3618500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3839700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3842000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4627500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3814400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4267500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3099000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4284300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3141800</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4106,876 +4196,900 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>107300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>146200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>63000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>65700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>80900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>54100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>51600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>45100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>53300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>51500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>86200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>155300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1369700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1356600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1323100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1240800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1452400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1538000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1440600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1170800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2004000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1762800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1563400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1328400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1487500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1346800</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7263300</v>
+      </c>
+      <c r="E43" s="3">
         <v>6827800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6917300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6600300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6486700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7081000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6943800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6937100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6943800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6937100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7074300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6720900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6234400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5941600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5292500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5094900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5021400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4848000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4560700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4894700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5247200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5166800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5957200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>11999600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5330100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5120200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5535200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5472300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5235300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4915100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4979300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4396600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4227700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3849600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3759800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3894300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3356000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5647500</v>
+      </c>
+      <c r="E44" s="3">
         <v>6356000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6012500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6290700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6231700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6161800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6525300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6833900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6525300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6833900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6939500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6285700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6016500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5727200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4807600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4329100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4487800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4166700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3725300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3600800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4021000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5073500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5496700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11174200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5646400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5756300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6145500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5826700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6012000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5542800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5444800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5335200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5557500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5631700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5198100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4944200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4617000</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>493500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1423900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>422400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1110100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1049500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>388100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>989900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1070700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>989900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1070700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1093800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1041700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1030100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1232300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>911400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>836800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>635600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>649000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>587400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>569600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>679500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>648300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>643800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>780500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1290500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1233600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1217000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1145000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1780200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1605900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1554400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1599400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1782100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1801500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1521500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1552300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1529300</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18261500</v>
+      </c>
+      <c r="E46" s="3">
         <v>19396200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18214200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18036300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18145000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19135900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18775800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19057400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18775800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19057400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18996800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>17839800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16774000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17146200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15583800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15752000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16329200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16719800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17354700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15059700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15149100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16337500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15376800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17476700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16364300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17415900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17774800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18053400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18184000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>17344100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16991400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>17962800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>17144600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>17113800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>14906800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>16162500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>13990900</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1464500</v>
+      </c>
+      <c r="E47" s="3">
         <v>1450900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1469900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1675400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1754900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1658200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1527400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1458100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1527400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1458100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1613300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1018200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>991400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1107900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1065600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1137000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1145100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1145500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1050000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1009800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1054200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1276800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1505300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2990000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1752500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1842600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2137000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2062100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2715400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2197500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2397300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2506000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2589900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2498300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2378500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2322300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2025500</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13846900</v>
+      </c>
+      <c r="E48" s="3">
         <v>14004200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13795100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13743900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14035000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14597100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13522800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13776800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13522800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13776800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13997300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13191400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11939700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12426800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11674800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11829900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12035900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12457000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12007200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12331000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13384700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>15078000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15667800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31118800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13721000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13711500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14610900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13861400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13471900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12947700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12817300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13316300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12869100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12797900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12444100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12853700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>11547300</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2355800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2464300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2314700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2405800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2459600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2489000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2358800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2276000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2358800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2276000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2295100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2103900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1948300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1972300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1826000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1787000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1807800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1487700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1428300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1576900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1642100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1787900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1829400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3799400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1743200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1768700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>861500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>957700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>954200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>903400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>891800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>949500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>992600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>988400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>656000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>657700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>570300</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5087,8 +5201,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5200,16 +5317,19 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>0</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>10</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>10</v>
@@ -5220,101 +5340,104 @@
       <c r="H52" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>1078400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1084900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1110900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>994800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>923600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>785600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>797700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>746000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>730400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>798900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>893400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>901800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1805500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1353500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1388500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1458400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1317400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1118100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1054100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1038900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1055100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1022800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>998600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>934800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>965000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>942100</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5426,121 +5549,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36659100</v>
+      </c>
+      <c r="E54" s="3">
         <v>37990700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36404500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>36463500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36966900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38505500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36895700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37288300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36895700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37288300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>37574600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35231600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32738300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33764200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31145100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31429500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32103700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32607800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32586200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>30707800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32029000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>35373500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>35281000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>38963600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34934500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>36127200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36842700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>36252100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>36443600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34446800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>34136600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>35789700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>34619000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>34397000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>31320200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>32961200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>29076100</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5580,8 +5709,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5621,686 +5751,705 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3831000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3510700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3884400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3727700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3708000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4251100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3580400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3653900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3580400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3653900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3864900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4313200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3627300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3655800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3255900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3551900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3032400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3076400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2733400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3079600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2599700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2589600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3128200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5968100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1835100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2026300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2185100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2208700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2243400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2116200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1950300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2103600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2025600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2021500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1854200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1735000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1541900</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1044900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1315100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1306800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1318000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1995700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2265700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2267800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2324600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2267800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2324600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1638200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1929500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1139600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1039500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1302700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1407200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1552700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1560400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2710100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2550400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2969700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3632300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1617000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2949000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1745500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2089300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2235600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2774400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2216500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1276800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1618000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1434900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1467800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1607300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1067600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3107800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1596600</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1713000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2725400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1825900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2489000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2403000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1971100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2810500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2626300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2810500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2626300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2624300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2232300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2532900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2690700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2342100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2071700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2121400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2131300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2479300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2006000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2082500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1936300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2027200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>6356000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3969500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4052700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4241900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4382200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3976300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3814200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3884900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4692900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4226900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3933500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3658000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4252700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3205600</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7124400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7551300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7471700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7534600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8106600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8965200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8658600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8604800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8658600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8604800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8127400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7709200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7299800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7386100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6900800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7030800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6706400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6768200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7922700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7636000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>7651900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>8158200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6772400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8156500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>7550100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8168300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8662700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8374400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8436100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7207200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>7453300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8231300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>7720400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>7562300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6579800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>7538000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>6344100</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4229800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4198300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3321900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3354600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3474300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3623500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3445300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3520800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3445300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3520800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4397200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4283200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3957800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4174500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4008900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4165300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4321900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4445000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4555600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4825000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5152000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5627300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5787000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5978000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4133900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4137000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2442500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2031700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1989500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2684500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2665900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2714700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2646700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2640600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1438000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1481900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1404300</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>510200</v>
+      </c>
+      <c r="E62" s="3">
         <v>585100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>394000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>410000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>416600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>450000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>428800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>460400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>428800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>460400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>448000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1850500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1753800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1952700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1847700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1853700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2048700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2108100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2041900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2155300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2277400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2570900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2755700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4777500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2594100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2650800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2918600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2848700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3083300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2898400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2955800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>3122900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3026900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>3025700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2934900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3133100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>2861500</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6412,8 +6561,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6525,8 +6677,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6638,121 +6793,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12933500</v>
+      </c>
+      <c r="E66" s="3">
         <v>13470300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12320500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12515000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13243900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14347300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13816000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13955500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13816000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13955500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14444400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14174200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13321000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13840300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13072000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13362200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13379600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13639700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14844900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14948600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15423000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16749200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>15745300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17560800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>14744100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15439800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14541300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13766400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13999700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13266900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>13552900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14583900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>13891000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13721500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>11424400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>12677000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>11064600</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6792,8 +6953,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6905,8 +7067,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7018,8 +7183,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7131,8 +7299,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7244,121 +7415,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19478200</v>
+      </c>
+      <c r="E72" s="3">
         <v>20217500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18247200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17674400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18047000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19233700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17720300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18197900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>17720300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18197900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19034300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17756600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15202300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15804000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15308800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15874300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>16784800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17007300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15925300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14682900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15438900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17177700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18111900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>44028300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>22532700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>22193000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>22722500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22336800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>21311700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>20630000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>19983000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>21211900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>20394100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>20283300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19252000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>19213200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>18542900</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7470,8 +7647,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7583,8 +7763,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7696,121 +7879,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23355100</v>
+      </c>
+      <c r="E76" s="3">
         <v>24161100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23734900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>23626800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23374600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23790800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22735600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22987500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22735600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22987500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22760000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21057400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19417300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19923900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18073100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18067300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18724100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>18968100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17741300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15759200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16606100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>18624400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>19535800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>21402800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>20190400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>20687400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>22301400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>22485700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>22443800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>21179900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>20583800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>21205800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>20728000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>20675500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>19895800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>20284200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>18011600</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7922,126 +8111,132 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8075,86 +8270,89 @@
       <c r="M81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O81" s="3">
         <v>792100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>611200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>263600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>357500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-197900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>508500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>493000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2022400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-354100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>171600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>469700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>825800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>393100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>536100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>681400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>788200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>647300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>576300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>818200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>596000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>656300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>525400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>731700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>529600</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8194,121 +8392,125 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>562400</v>
+      </c>
+      <c r="E83" s="3">
         <v>555300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>541300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>514800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>543400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>550200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>522200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>503000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>522200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>503000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>540500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>515200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>482100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>460700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>435800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>444600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>461700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>442800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>435700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>498300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>516900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>565200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>589000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>627500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>642000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>648500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>644800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>479300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>503300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>444400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>465300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>489800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>473600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>440100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>440600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>428800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>425200</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8420,8 +8622,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8533,8 +8738,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8646,8 +8854,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8759,8 +8970,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8872,97 +9086,100 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1535100</v>
+      </c>
+      <c r="E89" s="3">
         <v>757200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1452500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>515700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>850100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1681000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1259200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>806300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1259200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>806300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>901400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1025800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>913600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>138100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>399400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>416000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>180000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>644200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1553400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1323100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>691700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>564600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1895100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>694900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>888100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1172900</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
+      <c r="AF89" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
@@ -8985,8 +9202,11 @@
       <c r="AM89" s="3">
         <v>0</v>
       </c>
+      <c r="AN89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9026,97 +9246,98 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-433600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-328000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-543800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-361100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-599100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-616800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-392100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-376300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-392100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-376300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-620900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-85398000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55869000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41907000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-71552000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-55048000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-45318000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-196600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-349000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-376900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-364000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-325900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-566700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-626200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-678600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-523100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-680800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
+      <c r="AF91" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
@@ -9139,8 +9360,11 @@
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9252,8 +9476,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9365,97 +9592,100 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-312000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-293200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-511800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-645700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-695800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-476100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-334600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-476100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-334600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-602900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-430700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1035300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-276600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-491600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-352700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-598100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-175200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2055000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-292400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-382600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-522200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-44100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-358100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1335900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-694000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AF94" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
@@ -9478,8 +9708,11 @@
       <c r="AM94" s="3">
         <v>0</v>
       </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9519,92 +9752,93 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>600</v>
+      </c>
+      <c r="E96" s="3">
         <v>5900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>447300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>457700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5500</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="3">
         <v>-700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-376900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-393400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-430900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-6100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-293600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-273700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-490000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-528100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-572200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9632,8 +9866,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9745,8 +9982,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9858,8 +10098,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9971,97 +10214,100 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-392200</v>
+      </c>
+      <c r="E100" s="3">
         <v>223300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-207900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-763600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-756300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-257000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-573600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-129200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-573600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-129200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-323900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-288400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-595700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-645100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-892400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-210100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-526400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1688400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-326200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-385600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-724900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1947000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-568400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-230900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1732100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1278300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1194800</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
+      <c r="AF100" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG100" s="3">
         <v>0</v>
@@ -10084,97 +10330,100 @@
       <c r="AM100" s="3">
         <v>0</v>
       </c>
+      <c r="AN100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-160500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>21500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>299400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>12100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-370400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>114100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>427100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>114100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>427100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>324900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-346800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>105400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>391200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>262000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>110000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-32400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-57400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>316500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>28100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-53300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>82200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-164300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>102700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-89500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-56300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>67800</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
+      <c r="AF101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG101" s="3">
         <v>0</v>
@@ -10197,97 +10446,100 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1028100</v>
+      </c>
+      <c r="E102" s="3">
         <v>703400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>958500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-411900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>567700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>230900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>641900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>230900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>641900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-40200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-612000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-392400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-722700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-430700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-740900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1741100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2689400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1095400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>252500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2338300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-690300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1329100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1274100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>564100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-648100</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
+      <c r="AF102" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AG102" s="3">
         <v>0</v>
@@ -10308,6 +10560,9 @@
         <v>0</v>
       </c>
       <c r="AM102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="3">
         <v>0</v>
       </c>
     </row>
